--- a/database/event/1617/event_1617_evp_summary.xlsx
+++ b/database/event/1617/event_1617_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2318</v>
+        <v>6.7749</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8451</v>
+        <v>6.3545</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0961</v>
+        <v>2.2552</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2318</v>
+        <v>6.7749</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5052</v>
+        <v>2.0483</v>
       </c>
       <c r="G2" t="n">
         <v>4.7267</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5052</v>
+        <v>2.0483</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5122</v>
+        <v>2.0655</v>
       </c>
       <c r="J2" t="n">
         <v>4.7267</v>
@@ -529,7 +529,7 @@
         <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>6.2389</v>
+        <v>6.7922</v>
       </c>
       <c r="N2" t="n">
         <v>279</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6461</v>
+        <v>5.7795</v>
       </c>
       <c r="C3" t="n">
-        <v>5.2957</v>
+        <v>5.4208</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8595</v>
+        <v>1.8586</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6461</v>
+        <v>5.7795</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1275</v>
+        <v>1.2609</v>
       </c>
       <c r="G3" t="n">
         <v>4.5186</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1275</v>
+        <v>1.2609</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1275</v>
+        <v>1.2609</v>
       </c>
       <c r="J3" t="n">
         <v>4.5186</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>5.646100000000001</v>
+        <v>5.779500000000001</v>
       </c>
       <c r="N3" t="n">
         <v>261</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.7651</v>
+        <v>4.089</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5315</v>
+        <v>3.8353</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0997</v>
+        <v>1.1851</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7651</v>
+        <v>4.089</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4102</v>
+        <v>1.7814</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3549</v>
+        <v>2.3076</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4102</v>
+        <v>1.7814</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4102</v>
+        <v>1.7814</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3549</v>
+        <v>2.3076</v>
       </c>
       <c r="K4" t="n">
         <v>47</v>
@@ -621,7 +621,7 @@
         <v>214</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7651</v>
+        <v>4.089</v>
       </c>
       <c r="N4" t="n">
         <v>261</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7479</v>
+        <v>3.99</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5153</v>
+        <v>3.7424</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0927</v>
+        <v>1.1457</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7479</v>
+        <v>3.99</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4403</v>
+        <v>1.6351</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3076</v>
+        <v>2.3549</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4403</v>
+        <v>1.6351</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4403</v>
+        <v>1.6351</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3076</v>
+        <v>2.3549</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>214</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7479</v>
+        <v>3.99</v>
       </c>
       <c r="N5" t="n">
         <v>261</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6277</v>
+        <v>3.6219</v>
       </c>
       <c r="C6" t="n">
-        <v>3.4026</v>
+        <v>3.3971</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0441</v>
+        <v>0.9991</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6277</v>
+        <v>3.6219</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5374</v>
+        <v>1.5316</v>
       </c>
       <c r="G6" t="n">
         <v>2.0903</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5374</v>
+        <v>1.5316</v>
       </c>
       <c r="I6" t="n">
         <v>1.5445</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.753</v>
+        <v>3.107</v>
       </c>
       <c r="C7" t="n">
-        <v>2.5822</v>
+        <v>2.9142</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6908</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>2.753</v>
+        <v>3.107</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5023</v>
+        <v>0.8563</v>
       </c>
       <c r="G7" t="n">
         <v>2.2507</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5023</v>
+        <v>0.8563</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5023</v>
+        <v>0.8563</v>
       </c>
       <c r="J7" t="n">
         <v>2.2507</v>
@@ -759,7 +759,7 @@
         <v>214</v>
       </c>
       <c r="M7" t="n">
-        <v>2.753</v>
+        <v>3.107</v>
       </c>
       <c r="N7" t="n">
         <v>261</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.6728</v>
+        <v>2.8684</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5069</v>
+        <v>2.6904</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6584</v>
+        <v>0.6989</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6728</v>
+        <v>2.8684</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4867</v>
+        <v>2.2754</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1861</v>
+        <v>0.593</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4867</v>
+        <v>2.2754</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4983</v>
+        <v>2.2754</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1861</v>
+        <v>0.593</v>
       </c>
       <c r="K8" t="n">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="L8" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6844</v>
+        <v>2.8684</v>
       </c>
       <c r="N8" t="n">
-        <v>173</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.3373</v>
+        <v>2.6741</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1923</v>
+        <v>2.5082</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5229</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3373</v>
+        <v>2.6741</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9661</v>
+        <v>1.3029</v>
       </c>
       <c r="G9" t="n">
         <v>1.3712</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9661</v>
+        <v>1.3029</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9661</v>
+        <v>1.3029</v>
       </c>
       <c r="J9" t="n">
         <v>1.3712</v>
@@ -851,7 +851,7 @@
         <v>214</v>
       </c>
       <c r="M9" t="n">
-        <v>2.3373</v>
+        <v>2.6741</v>
       </c>
       <c r="N9" t="n">
         <v>261</v>
@@ -860,369 +860,369 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2115</v>
+        <v>2.672</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0743</v>
+        <v>2.5062</v>
       </c>
       <c r="D10" t="n">
-        <v>0.472</v>
+        <v>0.6206</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2115</v>
+        <v>2.672</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6185</v>
+        <v>2.4859</v>
       </c>
       <c r="G10" t="n">
-        <v>0.593</v>
+        <v>0.1861</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6185</v>
+        <v>2.4859</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6185</v>
+        <v>2.5068</v>
       </c>
       <c r="J10" t="n">
-        <v>0.593</v>
+        <v>0.1861</v>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="L10" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2115</v>
+        <v>2.6929</v>
       </c>
       <c r="N10" t="n">
-        <v>119</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5316</v>
+        <v>2.1095</v>
       </c>
       <c r="C11" t="n">
-        <v>1.4366</v>
+        <v>1.9786</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1974</v>
+        <v>0.3965</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5316</v>
+        <v>2.1095</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7795</v>
+        <v>2.5343</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3111</v>
+        <v>-0.4248</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7795</v>
+        <v>2.5343</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7831</v>
+        <v>2.5556</v>
       </c>
       <c r="J11" t="n">
-        <v>2.3111</v>
+        <v>-0.4248</v>
       </c>
       <c r="K11" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="L11" t="n">
-        <v>151</v>
+        <v>68</v>
       </c>
       <c r="M11" t="n">
-        <v>1.528</v>
+        <v>2.1308</v>
       </c>
       <c r="N11" t="n">
-        <v>279</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5191</v>
+        <v>2.0624</v>
       </c>
       <c r="C12" t="n">
-        <v>1.4248</v>
+        <v>1.9344</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1923</v>
+        <v>0.3778</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5191</v>
+        <v>2.0624</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9439</v>
+        <v>2.4728</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4248</v>
+        <v>-0.4104</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9439</v>
+        <v>2.4728</v>
       </c>
       <c r="I12" t="n">
-        <v>1.953</v>
+        <v>2.4728</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4248</v>
+        <v>-0.4104</v>
       </c>
       <c r="K12" t="n">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="L12" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5282</v>
+        <v>2.0624</v>
       </c>
       <c r="N12" t="n">
-        <v>173</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4706</v>
+        <v>1.9281</v>
       </c>
       <c r="C13" t="n">
-        <v>1.3793</v>
+        <v>1.8084</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1727</v>
+        <v>0.3242</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4706</v>
+        <v>1.9281</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4706</v>
+        <v>2.5045</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.5764</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4706</v>
+        <v>2.5045</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4706</v>
+        <v>2.5045</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.5764</v>
       </c>
       <c r="K13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4706</v>
+        <v>1.9281</v>
       </c>
       <c r="N13" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2335</v>
+        <v>1.73</v>
       </c>
       <c r="C14" t="n">
-        <v>1.157</v>
+        <v>1.6226</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0769</v>
+        <v>0.2453</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2335</v>
+        <v>1.73</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5817</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6518</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5817</v>
+        <v>1.73</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5844</v>
+        <v>1.73</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6518</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="L14" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2362</v>
+        <v>1.73</v>
       </c>
       <c r="N14" t="n">
-        <v>287</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2255</v>
+        <v>1.6017</v>
       </c>
       <c r="C15" t="n">
-        <v>1.1494</v>
+        <v>1.5023</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0737</v>
+        <v>0.1942</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2255</v>
+        <v>1.6017</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6359</v>
+        <v>1.6017</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4104</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6359</v>
+        <v>1.6017</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6359</v>
+        <v>1.6017</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4104</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2255</v>
+        <v>1.6017</v>
       </c>
       <c r="N15" t="n">
-        <v>94</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.0021</v>
+        <v>1.5947</v>
       </c>
       <c r="C16" t="n">
-        <v>0.9399</v>
+        <v>1.4957</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0165</v>
+        <v>0.1914</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0021</v>
+        <v>1.5947</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0021</v>
+        <v>0.9429</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.6518</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0021</v>
+        <v>0.9429</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0021</v>
+        <v>0.9508</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.6518</v>
       </c>
       <c r="K16" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0021</v>
+        <v>1.6026</v>
       </c>
       <c r="N16" t="n">
-        <v>132</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9805</v>
+        <v>1.5345</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9197</v>
+        <v>1.4393</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0253</v>
+        <v>0.1674</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9805</v>
+        <v>1.5345</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5569</v>
+        <v>-0.7766</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5764</v>
+        <v>2.3111</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5569</v>
+        <v>-0.7766</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5569</v>
+        <v>-0.7831</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5764</v>
+        <v>2.3111</v>
       </c>
       <c r="K17" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="L17" t="n">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9804999999999999</v>
+        <v>1.528</v>
       </c>
       <c r="N17" t="n">
-        <v>115</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9641</v>
+        <v>1.4162</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9043</v>
+        <v>1.3283</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0319</v>
+        <v>0.1203</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9641</v>
+        <v>1.4162</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7571</v>
+        <v>3.2092</v>
       </c>
       <c r="G18" t="n">
         <v>-1.793</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7571</v>
+        <v>3.2092</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7699</v>
+        <v>3.2362</v>
       </c>
       <c r="J18" t="n">
         <v>-1.793</v>
@@ -1265,7 +1265,7 @@
         <v>91</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9768999999999999</v>
+        <v>1.4432</v>
       </c>
       <c r="N18" t="n">
         <v>194</v>
@@ -1274,81 +1274,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9488</v>
+        <v>1.3271</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8899</v>
+        <v>1.2447</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0381</v>
+        <v>0.0848</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9488</v>
+        <v>1.3271</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9488</v>
+        <v>1.5667</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.2396</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9488</v>
+        <v>1.5667</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9488</v>
+        <v>1.5799</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.2396</v>
       </c>
       <c r="K19" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9488</v>
+        <v>1.3403</v>
       </c>
       <c r="N19" t="n">
-        <v>46</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8922</v>
+        <v>0.9857</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8368</v>
+        <v>0.9245</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0609</v>
+        <v>-0.0512</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8922</v>
+        <v>0.9857</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1513</v>
+        <v>1.7777</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0435</v>
+        <v>-0.792</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1513</v>
+        <v>1.7777</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.152</v>
+        <v>1.7927</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0435</v>
+        <v>-0.792</v>
       </c>
       <c r="K20" t="n">
         <v>103</v>
@@ -1357,7 +1357,7 @@
         <v>91</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8915000000000001</v>
+        <v>1.0007</v>
       </c>
       <c r="N20" t="n">
         <v>194</v>
@@ -1366,127 +1366,127 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8439</v>
+        <v>0.9488</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7915</v>
+        <v>0.8899</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0804</v>
+        <v>-0.0659</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8439</v>
+        <v>0.9488</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8439</v>
+        <v>0.9488</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8439</v>
+        <v>0.9488</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8439</v>
+        <v>0.9488</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8439</v>
+        <v>0.9488</v>
       </c>
       <c r="N21" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7597</v>
+        <v>0.9326</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7126</v>
+        <v>0.8747</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1145</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7597</v>
+        <v>0.9326</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9993</v>
+        <v>0.9326</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2396</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9993</v>
+        <v>0.9326</v>
       </c>
       <c r="I22" t="n">
-        <v>1.004</v>
+        <v>0.9326</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2396</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="L22" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7644</v>
+        <v>0.9326</v>
       </c>
       <c r="N22" t="n">
-        <v>287</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7507</v>
+        <v>0.8928</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.8374</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1181</v>
+        <v>-0.0882</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7507</v>
+        <v>0.8928</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5427</v>
+        <v>-0.1507</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.792</v>
+        <v>1.0435</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5427</v>
+        <v>-0.1507</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5499</v>
+        <v>-0.152</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.792</v>
+        <v>1.0435</v>
       </c>
       <c r="K23" t="n">
         <v>103</v>
@@ -1495,7 +1495,7 @@
         <v>91</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7579</v>
+        <v>0.8915000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>194</v>
@@ -1504,737 +1504,737 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7439</v>
+        <v>0.8719</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6977</v>
+        <v>0.8178</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1208</v>
+        <v>-0.0965</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7439</v>
+        <v>0.8719</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1889</v>
+        <v>0.8719</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.445</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1889</v>
+        <v>0.8719</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1991</v>
+        <v>0.8719</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.445</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="L24" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7541</v>
+        <v>0.8719</v>
       </c>
       <c r="N24" t="n">
-        <v>279</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5041</v>
+        <v>0.8333</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4728</v>
+        <v>0.7816</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2177</v>
+        <v>-0.1119</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5041</v>
+        <v>0.8333</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5041</v>
+        <v>1.2019</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.3686</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5041</v>
+        <v>1.2019</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5041</v>
+        <v>1.2019</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.3686</v>
       </c>
       <c r="K25" t="n">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5041</v>
+        <v>0.8332999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4979</v>
+        <v>0.7912</v>
       </c>
       <c r="C26" t="n">
-        <v>0.467</v>
+        <v>0.7421</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2202</v>
+        <v>-0.1287</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4979</v>
+        <v>0.7912</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4979</v>
+        <v>1.2537</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.4625</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4979</v>
+        <v>1.2537</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4979</v>
+        <v>1.2537</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.4625</v>
       </c>
       <c r="K26" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4979</v>
+        <v>0.7912</v>
       </c>
       <c r="N26" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3724</v>
+        <v>0.7357</v>
       </c>
       <c r="C27" t="n">
-        <v>0.3493</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2709</v>
+        <v>-0.1508</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3724</v>
+        <v>0.7357</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3724</v>
+        <v>2.1807</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1.445</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3724</v>
+        <v>2.1807</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3724</v>
+        <v>2.1991</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-1.445</v>
       </c>
       <c r="K27" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3724</v>
+        <v>0.7541</v>
       </c>
       <c r="N27" t="n">
-        <v>133</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.301</v>
+        <v>0.5041</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2823</v>
+        <v>0.4728</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2998</v>
+        <v>-0.2431</v>
       </c>
       <c r="E28" t="n">
-        <v>0.301</v>
+        <v>0.5041</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.99</v>
+        <v>0.5041</v>
       </c>
       <c r="G28" t="n">
-        <v>1.291</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.99</v>
+        <v>0.5041</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9946</v>
+        <v>0.5041</v>
       </c>
       <c r="J28" t="n">
-        <v>1.291</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L28" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2963999999999999</v>
+        <v>0.5041</v>
       </c>
       <c r="N28" t="n">
-        <v>279</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2939</v>
+        <v>0.4979</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2757</v>
+        <v>0.467</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3026</v>
+        <v>-0.2455</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2939</v>
+        <v>0.4979</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1553</v>
+        <v>0.4979</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4492</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1553</v>
+        <v>0.4979</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.156</v>
+        <v>0.4979</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4492</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="L29" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2932</v>
+        <v>0.4979</v>
       </c>
       <c r="N29" t="n">
-        <v>194</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2752</v>
+        <v>0.3724</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2581</v>
+        <v>0.3493</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3102</v>
+        <v>-0.2955</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2752</v>
+        <v>0.3724</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6438</v>
+        <v>0.3724</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3686</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6438</v>
+        <v>0.3724</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6438</v>
+        <v>0.3724</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3686</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="L30" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2752000000000001</v>
+        <v>0.3724</v>
       </c>
       <c r="N30" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.2537</v>
+        <v>0.3047</v>
       </c>
       <c r="C31" t="n">
-        <v>0.238</v>
+        <v>0.2858</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3189</v>
+        <v>-0.3225</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2537</v>
+        <v>0.3047</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2537</v>
+        <v>-0.9863</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.291</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2537</v>
+        <v>-0.9863</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2537</v>
+        <v>-0.9946</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1.291</v>
       </c>
       <c r="K31" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2537</v>
+        <v>0.2963999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>132</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2476</v>
+        <v>0.2945</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2322</v>
+        <v>0.2762</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3213</v>
+        <v>-0.3266</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2476</v>
+        <v>0.2945</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1689</v>
+        <v>-0.1547</v>
       </c>
       <c r="G32" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.4492</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1689</v>
+        <v>-0.1547</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1689</v>
+        <v>-0.156</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.4492</v>
       </c>
       <c r="K32" t="n">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="L32" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2476</v>
+        <v>0.2932</v>
       </c>
       <c r="N32" t="n">
-        <v>94</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.153</v>
+        <v>0.2537</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1435</v>
+        <v>0.238</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3596</v>
+        <v>-0.3428</v>
       </c>
       <c r="E33" t="n">
-        <v>0.153</v>
+        <v>0.2537</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3498</v>
+        <v>0.2537</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1968</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3498</v>
+        <v>0.2537</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3498</v>
+        <v>0.2537</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.1968</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="L33" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.153</v>
+        <v>0.2537</v>
       </c>
       <c r="N33" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0915</v>
+        <v>0.2476</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0858</v>
+        <v>0.2322</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3844</v>
+        <v>-0.3453</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0915</v>
+        <v>0.2476</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0915</v>
+        <v>0.1689</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0915</v>
+        <v>0.1689</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0915</v>
+        <v>0.1689</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M34" t="n">
-        <v>0.0915</v>
+        <v>0.2476</v>
       </c>
       <c r="N34" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.048</v>
+        <v>0.232</v>
       </c>
       <c r="C35" t="n">
-        <v>0.045</v>
+        <v>0.2176</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.402</v>
+        <v>-0.3515</v>
       </c>
       <c r="E35" t="n">
-        <v>0.048</v>
+        <v>0.232</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4983</v>
+        <v>0.4288</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.4503</v>
+        <v>-0.1968</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4983</v>
+        <v>0.4288</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4983</v>
+        <v>0.4288</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.4503</v>
+        <v>-0.1968</v>
       </c>
       <c r="K35" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L35" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M35" t="n">
-        <v>0.04800000000000004</v>
+        <v>0.232</v>
       </c>
       <c r="N35" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0095</v>
+        <v>0.1441</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0089</v>
+        <v>0.1352</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4175</v>
+        <v>-0.3865</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0095</v>
+        <v>0.1441</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2298</v>
+        <v>0.1441</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.2203</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2298</v>
+        <v>0.1441</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2309</v>
+        <v>0.1441</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.2203</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="L36" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0106</v>
+        <v>0.1441</v>
       </c>
       <c r="N36" t="n">
-        <v>194</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.0058</v>
+        <v>0.0915</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0054</v>
+        <v>0.0858</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4237</v>
+        <v>-0.4075</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.0058</v>
+        <v>0.0915</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.0058</v>
+        <v>0.0915</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.0058</v>
+        <v>0.0915</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0058</v>
+        <v>0.0915</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0058</v>
+        <v>0.0915</v>
       </c>
       <c r="N37" t="n">
-        <v>132</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.0483</v>
+        <v>0.048</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0453</v>
+        <v>0.045</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4409</v>
+        <v>-0.4248</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.0483</v>
+        <v>0.048</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0483</v>
+        <v>0.4983</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.4503</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0483</v>
+        <v>0.4983</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.0483</v>
+        <v>0.4983</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.4503</v>
       </c>
       <c r="K38" t="n">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0483</v>
+        <v>0.04800000000000004</v>
       </c>
       <c r="N38" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.0512</v>
+        <v>0.0086</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.048</v>
+        <v>0.0081</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.442</v>
+        <v>-0.4405</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.0512</v>
+        <v>0.0086</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4113</v>
+        <v>0.2289</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4625</v>
+        <v>-0.2203</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4113</v>
+        <v>0.2289</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4113</v>
+        <v>0.2309</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4625</v>
+        <v>-0.2203</v>
       </c>
       <c r="K39" t="n">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="L39" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.05120000000000002</v>
+        <v>0.0106</v>
       </c>
       <c r="N39" t="n">
-        <v>94</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40">
@@ -2250,7 +2250,7 @@
         <v>-0.0925</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4612</v>
+        <v>-0.4832</v>
       </c>
       <c r="E40" t="n">
         <v>-0.09859999999999999</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.1177</v>
+        <v>-0.1188</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1104</v>
+        <v>-0.1114</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4689</v>
+        <v>-0.4912</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1177</v>
+        <v>-0.1188</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2954</v>
+        <v>0.2943</v>
       </c>
       <c r="G41" t="n">
         <v>-0.4131</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2954</v>
+        <v>0.2943</v>
       </c>
       <c r="I41" t="n">
         <v>0.2968</v>
@@ -2342,7 +2342,7 @@
         <v>-0.1319</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4782</v>
+        <v>-0.4999</v>
       </c>
       <c r="E42" t="n">
         <v>-0.1406</v>
@@ -2388,7 +2388,7 @@
         <v>-0.1358</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.4799</v>
+        <v>-0.5016</v>
       </c>
       <c r="E43" t="n">
         <v>-0.1448</v>
@@ -2434,7 +2434,7 @@
         <v>-0.139</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.4812</v>
+        <v>-0.503</v>
       </c>
       <c r="E44" t="n">
         <v>-0.1482</v>
@@ -2480,7 +2480,7 @@
         <v>-0.1564</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.4887</v>
+        <v>-0.5104</v>
       </c>
       <c r="E45" t="n">
         <v>-0.1668</v>
@@ -2516,78 +2516,78 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1949</v>
+        <v>-0.1947</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1828</v>
+        <v>-0.1826</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5001</v>
+        <v>-0.5215</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1949</v>
+        <v>-0.1947</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1949</v>
+        <v>-0.1947</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1949</v>
+        <v>-0.1947</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1949</v>
+        <v>-0.1947</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1949</v>
+        <v>-0.1947</v>
       </c>
       <c r="N46" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.2377</v>
+        <v>-0.1949</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.2229</v>
+        <v>-0.1828</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5174</v>
+        <v>-0.5216</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.2377</v>
+        <v>-0.1949</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.2377</v>
+        <v>-0.1949</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.2377</v>
+        <v>-0.1949</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2377</v>
+        <v>-0.1949</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.2377</v>
+        <v>-0.1949</v>
       </c>
       <c r="N47" t="n">
         <v>61</v>
@@ -2608,32 +2608,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2879</v>
+        <v>-0.2377</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.27</v>
+        <v>-0.2229</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5377</v>
+        <v>-0.5386</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.2879</v>
+        <v>-0.2377</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.2879</v>
+        <v>-0.2377</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.2879</v>
+        <v>-0.2377</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2879</v>
+        <v>-0.2377</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.2879</v>
+        <v>-0.2377</v>
       </c>
       <c r="N48" t="n">
         <v>61</v>
@@ -2654,7 +2654,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -2664,252 +2664,252 @@
         <v>-0.27</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5377</v>
+        <v>-0.5586</v>
       </c>
       <c r="E49" t="n">
         <v>-0.2879</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7121</v>
+        <v>-0.2879</v>
       </c>
       <c r="G49" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7121</v>
+        <v>-0.2879</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7154</v>
+        <v>-0.2879</v>
       </c>
       <c r="J49" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="L49" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.2846</v>
+        <v>-0.2879</v>
       </c>
       <c r="N49" t="n">
-        <v>173</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.3018</v>
+        <v>-0.2906</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.2831</v>
+        <v>-0.2726</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5433</v>
+        <v>-0.5597</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.3018</v>
+        <v>-0.2906</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.3018</v>
+        <v>0.7094</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.3018</v>
+        <v>0.7094</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3018</v>
+        <v>0.7154</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K50" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.3018</v>
+        <v>-0.2846</v>
       </c>
       <c r="N50" t="n">
-        <v>61</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3615</v>
+        <v>-0.3018</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.3391</v>
+        <v>-0.2831</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5674</v>
+        <v>-0.5641</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3615</v>
+        <v>-0.3018</v>
       </c>
       <c r="F51" t="n">
-        <v>1.2995</v>
+        <v>-0.3018</v>
       </c>
       <c r="G51" t="n">
-        <v>-1.661</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.2995</v>
+        <v>-0.3018</v>
       </c>
       <c r="I51" t="n">
-        <v>1.3055</v>
+        <v>-0.3018</v>
       </c>
       <c r="J51" t="n">
-        <v>-1.661</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="L51" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3554999999999999</v>
+        <v>-0.3018</v>
       </c>
       <c r="N51" t="n">
-        <v>287</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3804</v>
+        <v>-0.3664</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3568</v>
+        <v>-0.3437</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.575</v>
+        <v>-0.5899</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.3804</v>
+        <v>-0.3664</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.3804</v>
+        <v>1.2946</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1.661</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.3804</v>
+        <v>1.2946</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.3804</v>
+        <v>1.3055</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-1.661</v>
       </c>
       <c r="K52" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.3804</v>
+        <v>-0.3554999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>106</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.4472</v>
+        <v>-0.3803</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4194</v>
+        <v>-0.3567</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.602</v>
+        <v>-0.5954</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.4472</v>
+        <v>-0.3803</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.4472</v>
+        <v>-0.3803</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.4472</v>
+        <v>-0.3803</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.4472</v>
+        <v>-0.3803</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.4472</v>
+        <v>-0.3803</v>
       </c>
       <c r="N53" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.4504</v>
+        <v>-0.4472</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4224</v>
+        <v>-0.4194</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.6221</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.4504</v>
+        <v>-0.4472</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.4504</v>
+        <v>-0.4472</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.4504</v>
+        <v>-0.4472</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4504</v>
+        <v>-0.4472</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.4504</v>
+        <v>-0.4472</v>
       </c>
       <c r="N54" t="n">
         <v>46</v>
@@ -2930,93 +2930,93 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4511</v>
+        <v>-0.4504</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4231</v>
+        <v>-0.4224</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6036</v>
+        <v>-0.6233</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4511</v>
+        <v>-0.4504</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4511</v>
+        <v>-0.4504</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4511</v>
+        <v>-0.4504</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4511</v>
+        <v>-0.4504</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.4511</v>
+        <v>-0.4504</v>
       </c>
       <c r="N55" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4561</v>
+        <v>-0.4511</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4278</v>
+        <v>-0.4231</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6056</v>
+        <v>-0.6236</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4561</v>
+        <v>-0.4511</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4561</v>
+        <v>-0.4511</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4561</v>
+        <v>-0.4511</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4561</v>
+        <v>-0.4511</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4561</v>
+        <v>-0.4511</v>
       </c>
       <c r="N56" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57">
@@ -3032,7 +3032,7 @@
         <v>-0.4631</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6208</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="E57" t="n">
         <v>-0.4937</v>
@@ -3078,7 +3078,7 @@
         <v>-0.61</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6841</v>
+        <v>-0.703</v>
       </c>
       <c r="E58" t="n">
         <v>-0.6504</v>
@@ -3124,7 +3124,7 @@
         <v>-0.6107</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6844</v>
+        <v>-0.7033</v>
       </c>
       <c r="E59" t="n">
         <v>-0.6511</v>
@@ -3170,7 +3170,7 @@
         <v>-0.7433999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7416</v>
+        <v>-0.7597</v>
       </c>
       <c r="E60" t="n">
         <v>-0.7926</v>
@@ -3216,7 +3216,7 @@
         <v>-0.7563</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7471</v>
+        <v>-0.7651</v>
       </c>
       <c r="E61" t="n">
         <v>-0.8063</v>
@@ -3262,7 +3262,7 @@
         <v>-0.7713</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7536</v>
+        <v>-0.7715</v>
       </c>
       <c r="E62" t="n">
         <v>-0.8223</v>
@@ -3308,7 +3308,7 @@
         <v>-0.8241000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7763</v>
+        <v>-0.7939000000000001</v>
       </c>
       <c r="E63" t="n">
         <v>-0.8786</v>
@@ -3354,7 +3354,7 @@
         <v>-0.9233</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.819</v>
+        <v>-0.8361</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9844000000000001</v>
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1101</v>
+        <v>-1.1097</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.0412</v>
+        <v>-1.0408</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8698</v>
+        <v>-0.886</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.1101</v>
+        <v>-1.1097</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.1101</v>
+        <v>-0.1097</v>
       </c>
       <c r="G65" t="n">
         <v>-1</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1101</v>
+        <v>-0.1097</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1101</v>
+        <v>-0.1097</v>
       </c>
       <c r="J65" t="n">
         <v>-1</v>
@@ -3427,7 +3427,7 @@
         <v>59</v>
       </c>
       <c r="M65" t="n">
-        <v>-1.1101</v>
+        <v>-1.1097</v>
       </c>
       <c r="N65" t="n">
         <v>115</v>
@@ -3446,7 +3446,7 @@
         <v>-1.0867</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8894</v>
+        <v>-0.9055</v>
       </c>
       <c r="E66" t="n">
         <v>-1.1586</v>
@@ -3492,7 +3492,7 @@
         <v>-1.1065</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8979</v>
+        <v>-0.9139</v>
       </c>
       <c r="E67" t="n">
         <v>-1.1797</v>
@@ -3538,7 +3538,7 @@
         <v>-1.1286</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9075</v>
+        <v>-0.9233</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2033</v>
@@ -3584,7 +3584,7 @@
         <v>-1.1823</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9306</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="E69" t="n">
         <v>-1.2605</v>
@@ -3630,7 +3630,7 @@
         <v>-1.2263</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9495</v>
+        <v>-0.9648</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3074</v>
@@ -3676,7 +3676,7 @@
         <v>-1.2477</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9588</v>
+        <v>-0.9739</v>
       </c>
       <c r="E71" t="n">
         <v>-1.3303</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3935</v>
+        <v>-1.3887</v>
       </c>
       <c r="C72" t="n">
-        <v>-1.307</v>
+        <v>-1.3025</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9843</v>
+        <v>-0.9972</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3935</v>
+        <v>-1.3887</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.29</v>
+        <v>-1.2852</v>
       </c>
       <c r="G72" t="n">
         <v>-0.1035</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.29</v>
+        <v>-1.2852</v>
       </c>
       <c r="I72" t="n">
         <v>-1.296</v>
@@ -3768,7 +3768,7 @@
         <v>-1.4784</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0581</v>
+        <v>-1.0719</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5762</v>
@@ -3814,7 +3814,7 @@
         <v>-1.5631</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0946</v>
+        <v>-1.1078</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6665</v>
@@ -3860,7 +3860,7 @@
         <v>-1.5643</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0951</v>
+        <v>-1.1084</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6678</v>
@@ -3906,7 +3906,7 @@
         <v>-1.6179</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1182</v>
+        <v>-1.1311</v>
       </c>
       <c r="E76" t="n">
         <v>-1.7249</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.7489</v>
+        <v>-1.7456</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.6404</v>
+        <v>-1.6373</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1279</v>
+        <v>-1.1394</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.7489</v>
+        <v>-1.7456</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.8791</v>
+        <v>-0.8758</v>
       </c>
       <c r="G77" t="n">
         <v>-0.8698</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.8791</v>
+        <v>-0.8758</v>
       </c>
       <c r="I77" t="n">
         <v>-0.8832</v>
@@ -3998,7 +3998,7 @@
         <v>-1.783</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1893</v>
+        <v>-1.2013</v>
       </c>
       <c r="E78" t="n">
         <v>-1.901</v>
@@ -4044,7 +4044,7 @@
         <v>-2.0261</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.294</v>
+        <v>-1.3045</v>
       </c>
       <c r="E79" t="n">
         <v>-2.1602</v>
@@ -4090,7 +4090,7 @@
         <v>-2.6652</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5693</v>
+        <v>-1.576</v>
       </c>
       <c r="E80" t="n">
         <v>-2.8415</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.1712</v>
+        <v>-3.1631</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.9744</v>
+        <v>-2.9668</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7025</v>
+        <v>-1.7041</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.1712</v>
+        <v>-3.1631</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1712</v>
+        <v>-2.1631</v>
       </c>
       <c r="G81" t="n">
         <v>-1</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1712</v>
+        <v>-2.1631</v>
       </c>
       <c r="I81" t="n">
         <v>-2.1813</v>

--- a/database/event/1617/event_1617_evp_summary.xlsx
+++ b/database/event/1617/event_1617_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7749</v>
+        <v>6.0043</v>
       </c>
       <c r="C2" t="n">
-        <v>6.3545</v>
+        <v>5.6317</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2552</v>
+        <v>2.0726</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7749</v>
+        <v>6.0043</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0483</v>
+        <v>2.0764</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7267</v>
+        <v>3.9279</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0483</v>
+        <v>2.0764</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0655</v>
+        <v>2.1618</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7267</v>
+        <v>3.9279</v>
       </c>
       <c r="K2" t="n">
         <v>128</v>
@@ -529,7 +529,7 @@
         <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7922</v>
+        <v>6.089700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>279</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7795</v>
+        <v>5.2392</v>
       </c>
       <c r="C3" t="n">
-        <v>5.4208</v>
+        <v>4.9141</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8586</v>
+        <v>1.7272</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7795</v>
+        <v>5.2392</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2609</v>
+        <v>1.3724</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5186</v>
+        <v>3.8668</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2609</v>
+        <v>1.3724</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2609</v>
+        <v>1.3724</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5186</v>
+        <v>3.8668</v>
       </c>
       <c r="K3" t="n">
         <v>47</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>5.779500000000001</v>
+        <v>5.2392</v>
       </c>
       <c r="N3" t="n">
         <v>261</v>
@@ -584,81 +584,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.089</v>
+        <v>4.0521</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8353</v>
+        <v>3.8006</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1851</v>
+        <v>1.1913</v>
       </c>
       <c r="E4" t="n">
-        <v>4.089</v>
+        <v>4.0521</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7814</v>
+        <v>2.2984</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3076</v>
+        <v>1.7538</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7814</v>
+        <v>2.2984</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7814</v>
+        <v>2.3929</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3076</v>
+        <v>1.7538</v>
       </c>
       <c r="K4" t="n">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="L4" t="n">
-        <v>214</v>
+        <v>157</v>
       </c>
       <c r="M4" t="n">
-        <v>4.089</v>
+        <v>4.1467</v>
       </c>
       <c r="N4" t="n">
-        <v>261</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.99</v>
+        <v>3.4761</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7424</v>
+        <v>3.2604</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1457</v>
+        <v>0.9313</v>
       </c>
       <c r="E5" t="n">
-        <v>3.99</v>
+        <v>3.4761</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6351</v>
+        <v>1.8238</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3549</v>
+        <v>1.6523</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6351</v>
+        <v>1.8238</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6351</v>
+        <v>1.8238</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3549</v>
+        <v>1.6523</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>214</v>
       </c>
       <c r="M5" t="n">
-        <v>3.99</v>
+        <v>3.4761</v>
       </c>
       <c r="N5" t="n">
         <v>261</v>
@@ -676,507 +676,507 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6219</v>
+        <v>3.431</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3971</v>
+        <v>3.2181</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9991</v>
+        <v>0.9109</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6219</v>
+        <v>3.431</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5316</v>
+        <v>1.7284</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0903</v>
+        <v>1.7026</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5316</v>
+        <v>1.7284</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5445</v>
+        <v>1.7284</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0903</v>
+        <v>1.7026</v>
       </c>
       <c r="K6" t="n">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="L6" t="n">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6348</v>
+        <v>3.431</v>
       </c>
       <c r="N6" t="n">
-        <v>287</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.107</v>
+        <v>2.8202</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9142</v>
+        <v>2.6452</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.6352</v>
       </c>
       <c r="E7" t="n">
-        <v>3.107</v>
+        <v>2.8202</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8563</v>
+        <v>2.1666</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2507</v>
+        <v>0.6536</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8563</v>
+        <v>2.1666</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8563</v>
+        <v>2.1666</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2507</v>
+        <v>0.6536</v>
       </c>
       <c r="K7" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L7" t="n">
-        <v>214</v>
+        <v>62</v>
       </c>
       <c r="M7" t="n">
-        <v>3.107</v>
+        <v>2.8202</v>
       </c>
       <c r="N7" t="n">
-        <v>261</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8684</v>
+        <v>2.5819</v>
       </c>
       <c r="C8" t="n">
-        <v>2.6904</v>
+        <v>2.4217</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6989</v>
+        <v>0.5276</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8684</v>
+        <v>2.5819</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2754</v>
+        <v>0.8929</v>
       </c>
       <c r="G8" t="n">
-        <v>0.593</v>
+        <v>1.689</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2754</v>
+        <v>0.8929</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2754</v>
+        <v>0.8929</v>
       </c>
       <c r="J8" t="n">
-        <v>0.593</v>
+        <v>1.689</v>
       </c>
       <c r="K8" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8684</v>
+        <v>2.5819</v>
       </c>
       <c r="N8" t="n">
-        <v>119</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.6741</v>
+        <v>2.5097</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5082</v>
+        <v>2.354</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.495</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6741</v>
+        <v>2.5097</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3029</v>
+        <v>2.3607</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3712</v>
+        <v>0.149</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3029</v>
+        <v>2.3607</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3029</v>
+        <v>2.4578</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3712</v>
+        <v>0.149</v>
       </c>
       <c r="K9" t="n">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="L9" t="n">
-        <v>214</v>
+        <v>68</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6741</v>
+        <v>2.6068</v>
       </c>
       <c r="N9" t="n">
-        <v>261</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.672</v>
+        <v>2.3137</v>
       </c>
       <c r="C10" t="n">
-        <v>2.5062</v>
+        <v>2.1701</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6206</v>
+        <v>0.4065</v>
       </c>
       <c r="E10" t="n">
-        <v>2.672</v>
+        <v>2.3137</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4859</v>
+        <v>1.3428</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1861</v>
+        <v>0.9709</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4859</v>
+        <v>1.3428</v>
       </c>
       <c r="I10" t="n">
-        <v>2.5068</v>
+        <v>1.3428</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1861</v>
+        <v>0.9709</v>
       </c>
       <c r="K10" t="n">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="L10" t="n">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6929</v>
+        <v>2.3137</v>
       </c>
       <c r="N10" t="n">
-        <v>173</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1095</v>
+        <v>2.1377</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9786</v>
+        <v>2.005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3965</v>
+        <v>0.3271</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1095</v>
+        <v>2.1377</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5343</v>
+        <v>2.1377</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4248</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5343</v>
+        <v>2.1377</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5556</v>
+        <v>2.1377</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4248</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="L11" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1308</v>
+        <v>2.1377</v>
       </c>
       <c r="N11" t="n">
-        <v>173</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0624</v>
+        <v>2.0979</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9344</v>
+        <v>1.9677</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3778</v>
+        <v>0.3091</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0624</v>
+        <v>2.0979</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4728</v>
+        <v>2.4226</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4104</v>
+        <v>-0.3247</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4728</v>
+        <v>2.4226</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4728</v>
+        <v>2.5222</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4104</v>
+        <v>-0.3247</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0624</v>
+        <v>2.1975</v>
       </c>
       <c r="N12" t="n">
-        <v>94</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9281</v>
+        <v>2.0233</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8084</v>
+        <v>1.8977</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3242</v>
+        <v>0.2754</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9281</v>
+        <v>2.0233</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5045</v>
+        <v>2.925</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5764</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5045</v>
+        <v>3.063</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5045</v>
+        <v>3.189</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5764</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="L13" t="n">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9281</v>
+        <v>2.2873</v>
       </c>
       <c r="N13" t="n">
-        <v>115</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.73</v>
+        <v>2.0221</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6226</v>
+        <v>1.8966</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2453</v>
+        <v>0.2749</v>
       </c>
       <c r="E14" t="n">
-        <v>1.73</v>
+        <v>2.0221</v>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>2.3093</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.2872</v>
       </c>
       <c r="H14" t="n">
-        <v>1.73</v>
+        <v>2.3093</v>
       </c>
       <c r="I14" t="n">
-        <v>1.73</v>
+        <v>2.3093</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.2872</v>
       </c>
       <c r="K14" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>1.73</v>
+        <v>2.0221</v>
       </c>
       <c r="N14" t="n">
-        <v>52</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6017</v>
+        <v>1.9217</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5023</v>
+        <v>1.8024</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1942</v>
+        <v>0.2295</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6017</v>
+        <v>1.9217</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6017</v>
+        <v>2.2852</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.3635</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6017</v>
+        <v>2.2852</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6017</v>
+        <v>2.2852</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.3635</v>
       </c>
       <c r="K15" t="n">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6017</v>
+        <v>1.9217</v>
       </c>
       <c r="N15" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5947</v>
+        <v>1.845</v>
       </c>
       <c r="C16" t="n">
-        <v>1.4957</v>
+        <v>1.7305</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1914</v>
+        <v>0.1949</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5947</v>
+        <v>1.845</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9429</v>
+        <v>1.845</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6518</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9429</v>
+        <v>1.845</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9508</v>
+        <v>1.845</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6518</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L16" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6026</v>
+        <v>1.845</v>
       </c>
       <c r="N16" t="n">
-        <v>287</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5345</v>
+        <v>1.7574</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4393</v>
+        <v>1.6483</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1674</v>
+        <v>0.1554</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5345</v>
+        <v>1.7574</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7766</v>
+        <v>-0.2187</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3111</v>
+        <v>1.9761</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7766</v>
+        <v>-0.2187</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7831</v>
+        <v>-0.2277</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3111</v>
+        <v>1.9761</v>
       </c>
       <c r="K17" t="n">
         <v>128</v>
@@ -1219,7 +1219,7 @@
         <v>151</v>
       </c>
       <c r="M17" t="n">
-        <v>1.528</v>
+        <v>1.7484</v>
       </c>
       <c r="N17" t="n">
         <v>279</v>
@@ -1228,265 +1228,265 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4162</v>
+        <v>1.5894</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3283</v>
+        <v>1.4908</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1203</v>
+        <v>0.0795</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4162</v>
+        <v>1.5894</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2092</v>
+        <v>1.052</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.793</v>
+        <v>0.5374</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2092</v>
+        <v>1.052</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2362</v>
+        <v>1.0953</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.793</v>
+        <v>0.5374</v>
       </c>
       <c r="K18" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L18" t="n">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4432</v>
+        <v>1.6327</v>
       </c>
       <c r="N18" t="n">
-        <v>194</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3271</v>
+        <v>1.5869</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2447</v>
+        <v>1.4884</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0848</v>
+        <v>0.0784</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3271</v>
+        <v>1.5869</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5667</v>
+        <v>3.165</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2396</v>
+        <v>-1.5781</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5667</v>
+        <v>3.5901</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5799</v>
+        <v>3.7377</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2396</v>
+        <v>-1.5781</v>
       </c>
       <c r="K19" t="n">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="L19" t="n">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3403</v>
+        <v>2.1596</v>
       </c>
       <c r="N19" t="n">
-        <v>287</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9857</v>
+        <v>1.4303</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9245</v>
+        <v>1.3415</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0512</v>
+        <v>0.0077</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9857</v>
+        <v>1.4303</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7777</v>
+        <v>1.6564</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.792</v>
+        <v>-0.2261</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7777</v>
+        <v>1.6564</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7927</v>
+        <v>1.7245</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.792</v>
+        <v>-0.2261</v>
       </c>
       <c r="K20" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L20" t="n">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0007</v>
+        <v>1.4984</v>
       </c>
       <c r="N20" t="n">
-        <v>194</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9488</v>
+        <v>1.1848</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8899</v>
+        <v>1.1113</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0659</v>
+        <v>-0.1031</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9488</v>
+        <v>1.1848</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9488</v>
+        <v>1.1848</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9488</v>
+        <v>1.1848</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9488</v>
+        <v>1.1848</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9488</v>
+        <v>1.1848</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9326</v>
+        <v>1.1021</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8747</v>
+        <v>1.0337</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1405</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9326</v>
+        <v>1.1021</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9326</v>
+        <v>1.1021</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9326</v>
+        <v>1.1021</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9326</v>
+        <v>1.1021</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.9326</v>
+        <v>1.1021</v>
       </c>
       <c r="N22" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8928</v>
+        <v>1.069</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8374</v>
+        <v>1.0027</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0882</v>
+        <v>-0.1554</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8928</v>
+        <v>1.069</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1507</v>
+        <v>1.7539</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0435</v>
+        <v>-0.6849</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1507</v>
+        <v>1.7539</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.152</v>
+        <v>1.826</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0435</v>
+        <v>-0.6849</v>
       </c>
       <c r="K23" t="n">
         <v>103</v>
@@ -1495,7 +1495,7 @@
         <v>91</v>
       </c>
       <c r="M23" t="n">
-        <v>0.8915000000000001</v>
+        <v>1.1411</v>
       </c>
       <c r="N23" t="n">
         <v>194</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8719</v>
+        <v>0.9283</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8178</v>
+        <v>0.8707</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0965</v>
+        <v>-0.2189</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8719</v>
+        <v>0.9283</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8719</v>
+        <v>0.9283</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8719</v>
+        <v>0.9283</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8719</v>
+        <v>0.9283</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8719</v>
+        <v>0.9283</v>
       </c>
       <c r="N24" t="n">
         <v>132</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8333</v>
+        <v>0.8663</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7816</v>
+        <v>0.8125</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1119</v>
+        <v>-0.2469</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8333</v>
+        <v>0.8663</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2019</v>
+        <v>1.1143</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3686</v>
+        <v>-0.248</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2019</v>
+        <v>1.1143</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2019</v>
+        <v>1.1143</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3686</v>
+        <v>-0.248</v>
       </c>
       <c r="K25" t="n">
         <v>57</v>
@@ -1587,7 +1587,7 @@
         <v>62</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8332999999999999</v>
+        <v>0.8663000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>119</v>
@@ -1596,124 +1596,124 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7912</v>
+        <v>0.7922</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7421</v>
+        <v>0.743</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1287</v>
+        <v>-0.2804</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7912</v>
+        <v>0.7922</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2537</v>
+        <v>0.2679</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4625</v>
+        <v>0.5243</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2537</v>
+        <v>0.2679</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2537</v>
+        <v>0.2789</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4625</v>
+        <v>0.5243</v>
       </c>
       <c r="K26" t="n">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="L26" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7912</v>
+        <v>0.8031999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>94</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7357</v>
+        <v>0.7843</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7356</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1508</v>
+        <v>-0.2839</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7357</v>
+        <v>0.7843</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1807</v>
+        <v>1.1082</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.445</v>
+        <v>-0.3239</v>
       </c>
       <c r="H27" t="n">
-        <v>2.1807</v>
+        <v>1.1082</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1991</v>
+        <v>1.1082</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.445</v>
+        <v>-0.3239</v>
       </c>
       <c r="K27" t="n">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="L27" t="n">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7541</v>
+        <v>0.7843</v>
       </c>
       <c r="N27" t="n">
-        <v>279</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5041</v>
+        <v>0.6408</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4728</v>
+        <v>0.601</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.2431</v>
+        <v>-0.3487</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5041</v>
+        <v>0.6408</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5041</v>
+        <v>0.6408</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5041</v>
+        <v>0.6408</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5041</v>
+        <v>0.6408</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5041</v>
+        <v>0.6408</v>
       </c>
       <c r="N28" t="n">
         <v>133</v>
@@ -1734,185 +1734,185 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4979</v>
+        <v>0.6276</v>
       </c>
       <c r="C29" t="n">
-        <v>0.467</v>
+        <v>0.5887</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2455</v>
+        <v>-0.3547</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4979</v>
+        <v>0.6276</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4979</v>
+        <v>0.6276</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4979</v>
+        <v>0.6276</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4979</v>
+        <v>0.6276</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.4979</v>
+        <v>0.6276</v>
       </c>
       <c r="N29" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3724</v>
+        <v>0.5158</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3493</v>
+        <v>0.4838</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2955</v>
+        <v>-0.4052</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3724</v>
+        <v>0.5158</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3724</v>
+        <v>0.5158</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3724</v>
+        <v>0.5158</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3724</v>
+        <v>0.5158</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3724</v>
+        <v>0.5158</v>
       </c>
       <c r="N30" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3047</v>
+        <v>0.4514</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2858</v>
+        <v>0.4234</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3225</v>
+        <v>-0.4342</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3047</v>
+        <v>0.4514</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.9863</v>
+        <v>0.31</v>
       </c>
       <c r="G31" t="n">
-        <v>1.291</v>
+        <v>0.1414</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.9863</v>
+        <v>0.31</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.9946</v>
+        <v>0.31</v>
       </c>
       <c r="J31" t="n">
-        <v>1.291</v>
+        <v>0.1414</v>
       </c>
       <c r="K31" t="n">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="L31" t="n">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2963999999999999</v>
+        <v>0.4514</v>
       </c>
       <c r="N31" t="n">
-        <v>279</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.2945</v>
+        <v>0.4353</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2762</v>
+        <v>0.4083</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3266</v>
+        <v>-0.4415</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2945</v>
+        <v>0.4353</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1547</v>
+        <v>0.4353</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4492</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1547</v>
+        <v>0.4353</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.156</v>
+        <v>0.4353</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4492</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L32" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2932</v>
+        <v>0.4353</v>
       </c>
       <c r="N32" t="n">
-        <v>194</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2537</v>
+        <v>0.4222</v>
       </c>
       <c r="C33" t="n">
-        <v>0.238</v>
+        <v>0.396</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3428</v>
+        <v>-0.4474</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2537</v>
+        <v>0.4222</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2537</v>
+        <v>0.4222</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2537</v>
+        <v>0.4222</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2537</v>
+        <v>0.4222</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2537</v>
+        <v>0.4222</v>
       </c>
       <c r="N33" t="n">
         <v>132</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.2476</v>
+        <v>0.3907</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2322</v>
+        <v>0.3665</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.3453</v>
+        <v>-0.4616</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2476</v>
+        <v>0.3907</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1689</v>
+        <v>0.5012</v>
       </c>
       <c r="G34" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.1105</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1689</v>
+        <v>0.5012</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1689</v>
+        <v>0.5012</v>
       </c>
       <c r="J34" t="n">
-        <v>0.07870000000000001</v>
+        <v>-0.1105</v>
       </c>
       <c r="K34" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L34" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2476</v>
+        <v>0.3907</v>
       </c>
       <c r="N34" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.232</v>
+        <v>0.379</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2176</v>
+        <v>0.3555</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3515</v>
+        <v>-0.4669</v>
       </c>
       <c r="E35" t="n">
-        <v>0.232</v>
+        <v>0.379</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4288</v>
+        <v>0.1257</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1968</v>
+        <v>0.2533</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4288</v>
+        <v>0.1257</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4288</v>
+        <v>0.1309</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1968</v>
+        <v>0.2533</v>
       </c>
       <c r="K35" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="L35" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="M35" t="n">
-        <v>0.232</v>
+        <v>0.3842</v>
       </c>
       <c r="N35" t="n">
-        <v>119</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.1441</v>
+        <v>0.3722</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1352</v>
+        <v>0.3491</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.3865</v>
+        <v>-0.47</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1441</v>
+        <v>0.3722</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1441</v>
+        <v>0.3722</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1441</v>
+        <v>0.3722</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1441</v>
+        <v>0.3722</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.1441</v>
+        <v>0.3722</v>
       </c>
       <c r="N36" t="n">
         <v>106</v>
@@ -2102,81 +2102,81 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0915</v>
+        <v>0.3637</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0858</v>
+        <v>0.3411</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4075</v>
+        <v>-0.4738</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0915</v>
+        <v>0.3637</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0915</v>
+        <v>-0.7542</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.1179</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0915</v>
+        <v>-0.7542</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0915</v>
+        <v>-0.7852</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1.1179</v>
       </c>
       <c r="K37" t="n">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0915</v>
+        <v>0.3326999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>99</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.048</v>
+        <v>0.2986</v>
       </c>
       <c r="C38" t="n">
-        <v>0.045</v>
+        <v>0.2801</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4248</v>
+        <v>-0.5032</v>
       </c>
       <c r="E38" t="n">
-        <v>0.048</v>
+        <v>0.2986</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4983</v>
+        <v>0.4727</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4503</v>
+        <v>-0.1741</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4983</v>
+        <v>0.4727</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4983</v>
+        <v>0.4727</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.4503</v>
+        <v>-0.1741</v>
       </c>
       <c r="K38" t="n">
         <v>44</v>
@@ -2185,7 +2185,7 @@
         <v>50</v>
       </c>
       <c r="M38" t="n">
-        <v>0.04800000000000004</v>
+        <v>0.2986</v>
       </c>
       <c r="N38" t="n">
         <v>94</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0086</v>
+        <v>0.2906</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0081</v>
+        <v>0.2726</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4405</v>
+        <v>-0.5068</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0086</v>
+        <v>0.2906</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2289</v>
+        <v>0.595</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.2203</v>
+        <v>-0.3044</v>
       </c>
       <c r="H39" t="n">
-        <v>0.2289</v>
+        <v>0.595</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2309</v>
+        <v>0.595</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.2203</v>
+        <v>-0.3044</v>
       </c>
       <c r="K39" t="n">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="L39" t="n">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="M39" t="n">
-        <v>0.0106</v>
+        <v>0.2906</v>
       </c>
       <c r="N39" t="n">
-        <v>194</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.2634</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.0925</v>
+        <v>0.2471</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.4832</v>
+        <v>-0.5191</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.2634</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3415</v>
+        <v>0.2458</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.4401</v>
+        <v>0.0176</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3415</v>
+        <v>0.2458</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3415</v>
+        <v>0.2559</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.4401</v>
+        <v>0.0176</v>
       </c>
       <c r="K40" t="n">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="L40" t="n">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.09859999999999997</v>
+        <v>0.2735</v>
       </c>
       <c r="N40" t="n">
-        <v>94</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-0.1188</v>
+        <v>0.219</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1114</v>
+        <v>0.2054</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4912</v>
+        <v>-0.5391</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.1188</v>
+        <v>0.219</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2943</v>
+        <v>0.3575</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.4131</v>
+        <v>-0.1385</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2943</v>
+        <v>0.3575</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2968</v>
+        <v>0.3722</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.4131</v>
+        <v>-0.1385</v>
       </c>
       <c r="K41" t="n">
         <v>105</v>
@@ -2323,7 +2323,7 @@
         <v>68</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.1163</v>
+        <v>0.2337</v>
       </c>
       <c r="N41" t="n">
         <v>173</v>
@@ -2332,553 +2332,553 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Hyper</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-0.1406</v>
+        <v>0.1717</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.1319</v>
+        <v>0.161</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.4999</v>
+        <v>-0.5605</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.1406</v>
+        <v>0.1717</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1406</v>
+        <v>1.5214</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-1.3497</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1406</v>
+        <v>1.5214</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1406</v>
+        <v>1.584</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>-1.3497</v>
       </c>
       <c r="K42" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1406</v>
+        <v>0.2343000000000002</v>
       </c>
       <c r="N42" t="n">
-        <v>55</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-0.1448</v>
+        <v>0.1079</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.1358</v>
+        <v>0.1012</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5016</v>
+        <v>-0.5893</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1448</v>
+        <v>0.1079</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.2797</v>
+        <v>0.1079</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1349</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.2797</v>
+        <v>0.1079</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2797</v>
+        <v>0.1079</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1349</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="L43" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.1448</v>
+        <v>0.1079</v>
       </c>
       <c r="N43" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-0.1482</v>
+        <v>0.0521</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.139</v>
+        <v>0.0489</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.503</v>
+        <v>-0.6145</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.1482</v>
+        <v>0.0521</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.1482</v>
+        <v>0.0521</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1482</v>
+        <v>0.0521</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1482</v>
+        <v>0.0521</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.1482</v>
+        <v>0.0521</v>
       </c>
       <c r="N44" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>seang@res</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.1668</v>
+        <v>0.0334</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.1564</v>
+        <v>0.0313</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.5104</v>
+        <v>-0.6229</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.1668</v>
+        <v>0.0334</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1668</v>
+        <v>0.0334</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.1668</v>
+        <v>0.0334</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1668</v>
+        <v>0.0334</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.1668</v>
+        <v>0.0334</v>
       </c>
       <c r="N45" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.1947</v>
+        <v>-0.001</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.1826</v>
+        <v>-0.0009</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5215</v>
+        <v>-0.6385</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.1947</v>
+        <v>-0.001</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1947</v>
+        <v>-0.2001</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.1991</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1947</v>
+        <v>-0.2001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1947</v>
+        <v>-0.2001</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.1991</v>
       </c>
       <c r="K46" t="n">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.1947</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Hyper</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.1949</v>
+        <v>-0.0227</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.1828</v>
+        <v>-0.0213</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.5216</v>
+        <v>-0.6483</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1949</v>
+        <v>-0.0227</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1949</v>
+        <v>-0.0227</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.1949</v>
+        <v>-0.0227</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.1949</v>
+        <v>-0.0227</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1949</v>
+        <v>-0.0227</v>
       </c>
       <c r="N47" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.2377</v>
+        <v>-0.0437</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.2229</v>
+        <v>-0.041</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.5386</v>
+        <v>-0.6577</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.2377</v>
+        <v>-0.0437</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.2377</v>
+        <v>-0.0437</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.2377</v>
+        <v>-0.0437</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2377</v>
+        <v>-0.0437</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.2377</v>
+        <v>-0.0437</v>
       </c>
       <c r="N48" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>seang@res</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.2879</v>
+        <v>-0.05</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.27</v>
+        <v>-0.0469</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.5586</v>
+        <v>-0.6606</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.2879</v>
+        <v>-0.05</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.2879</v>
+        <v>-0.05</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.2879</v>
+        <v>-0.05</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2879</v>
+        <v>-0.05</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.2879</v>
+        <v>-0.05</v>
       </c>
       <c r="N49" t="n">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.2906</v>
+        <v>-0.1035</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.2726</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5597</v>
+        <v>-0.6847</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.2906</v>
+        <v>-0.1035</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7094</v>
+        <v>-0.1035</v>
       </c>
       <c r="G50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.7094</v>
+        <v>-0.1035</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7154</v>
+        <v>-0.1035</v>
       </c>
       <c r="J50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L50" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.2846</v>
+        <v>-0.1035</v>
       </c>
       <c r="N50" t="n">
-        <v>173</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.3018</v>
+        <v>-0.1145</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.2831</v>
+        <v>-0.1074</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5641</v>
+        <v>-0.6897</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3018</v>
+        <v>-0.1145</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3018</v>
+        <v>0.8855</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3018</v>
+        <v>0.8855</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3018</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K51" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3018</v>
+        <v>-0.07809999999999995</v>
       </c>
       <c r="N51" t="n">
-        <v>61</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.3664</v>
+        <v>-0.1422</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.3437</v>
+        <v>-0.1334</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5899</v>
+        <v>-0.7022</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.3664</v>
+        <v>-0.1422</v>
       </c>
       <c r="F52" t="n">
-        <v>1.2946</v>
+        <v>-0.1422</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.661</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.2946</v>
+        <v>-0.1422</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3055</v>
+        <v>-0.1422</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.661</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="L52" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.3554999999999999</v>
+        <v>-0.1422</v>
       </c>
       <c r="N52" t="n">
-        <v>287</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3803</v>
+        <v>-0.2411</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.3567</v>
+        <v>-0.2261</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5954</v>
+        <v>-0.7469</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3803</v>
+        <v>-0.2411</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3803</v>
+        <v>-0.2411</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3803</v>
+        <v>-0.2411</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3803</v>
+        <v>-0.2411</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3803</v>
+        <v>-0.2411</v>
       </c>
       <c r="N53" t="n">
-        <v>106</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54">
@@ -2888,28 +2888,28 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.4472</v>
+        <v>-0.2541</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4194</v>
+        <v>-0.2383</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6221</v>
+        <v>-0.7527</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.4472</v>
+        <v>-0.2541</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.4472</v>
+        <v>-0.2541</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.4472</v>
+        <v>-0.2541</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4472</v>
+        <v>-0.2541</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.4472</v>
+        <v>-0.2541</v>
       </c>
       <c r="N54" t="n">
         <v>46</v>
@@ -2930,93 +2930,93 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.4504</v>
+        <v>-0.2802</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4224</v>
+        <v>-0.2628</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6233</v>
+        <v>-0.7645</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.4504</v>
+        <v>-0.2802</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4504</v>
+        <v>0.3571</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-0.6373</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4504</v>
+        <v>0.3571</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.4504</v>
+        <v>0.3571</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>-0.6373</v>
       </c>
       <c r="K55" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.4504</v>
+        <v>-0.2802</v>
       </c>
       <c r="N55" t="n">
-        <v>46</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4511</v>
+        <v>-0.3265</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4231</v>
+        <v>-0.3062</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6236</v>
+        <v>-0.7854</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4511</v>
+        <v>-0.3265</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4511</v>
+        <v>-0.3265</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4511</v>
+        <v>-0.3265</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4511</v>
+        <v>-0.3265</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4511</v>
+        <v>-0.3265</v>
       </c>
       <c r="N56" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57">
@@ -3026,31 +3026,31 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4937</v>
+        <v>-0.4105</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4631</v>
+        <v>-0.385</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.8233</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4937</v>
+        <v>-0.4105</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.0202</v>
+        <v>-0.9663</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5265</v>
+        <v>0.5558</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.0202</v>
+        <v>-0.9663</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0202</v>
+        <v>-0.9663</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5265</v>
+        <v>0.5558</v>
       </c>
       <c r="K57" t="n">
         <v>56</v>
@@ -3059,7 +3059,7 @@
         <v>59</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4937</v>
+        <v>-0.4105000000000001</v>
       </c>
       <c r="N57" t="n">
         <v>115</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.6504</v>
+        <v>-0.4686</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.61</v>
+        <v>-0.4395</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.703</v>
+        <v>-0.8496</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.6504</v>
+        <v>-0.4686</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.6504</v>
+        <v>-0.4686</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.6504</v>
+        <v>-0.4686</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.6504</v>
+        <v>-0.4686</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.6504</v>
+        <v>-0.4686</v>
       </c>
       <c r="N58" t="n">
         <v>52</v>
@@ -3114,47 +3114,47 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6511</v>
+        <v>-0.4995</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.6107</v>
+        <v>-0.4685</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.7033</v>
+        <v>-0.8635</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6511</v>
+        <v>-0.4995</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3106</v>
+        <v>-0.4995</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.9617</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3106</v>
+        <v>-0.4995</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3106</v>
+        <v>-0.4995</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.9617</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="L59" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6511</v>
+        <v>-0.4995</v>
       </c>
       <c r="N59" t="n">
-        <v>119</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60">
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.7926</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-0.4817</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.7597</v>
+        <v>-0.8699</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.7926</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.7926</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.7926</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7926</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.7926</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="N60" t="n">
         <v>55</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.8063</v>
+        <v>-0.5183</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.7563</v>
+        <v>-0.4861</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7651</v>
+        <v>-0.872</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.8063</v>
+        <v>-0.5183</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.8063</v>
+        <v>-0.5183</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.8063</v>
+        <v>-0.5183</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8063</v>
+        <v>-0.5183</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.8063</v>
+        <v>-0.5183</v>
       </c>
       <c r="N61" t="n">
         <v>55</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.8223</v>
+        <v>-0.547</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.7713</v>
+        <v>-0.5131</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7715</v>
+        <v>-0.885</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8223</v>
+        <v>-0.547</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.8223</v>
+        <v>-0.547</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.8223</v>
+        <v>-0.547</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.8223</v>
+        <v>-0.547</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.8223</v>
+        <v>-0.547</v>
       </c>
       <c r="N62" t="n">
         <v>61</v>
@@ -3298,47 +3298,47 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.8786</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.6302</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.9413</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.8786</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.9169</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0383</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.9169</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.9169</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>0.0383</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="L63" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.8786</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.6771</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.9233</v>
+        <v>-0.6351</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8361</v>
+        <v>-0.9437</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.6771</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.6771</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.6771</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.6771</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.6771</v>
       </c>
       <c r="N64" t="n">
         <v>52</v>
@@ -3390,93 +3390,93 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-1.1097</v>
+        <v>-0.7565</v>
       </c>
       <c r="C65" t="n">
-        <v>-1.0408</v>
+        <v>-0.7096</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.886</v>
+        <v>-0.9795</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.1097</v>
+        <v>-0.7565</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.1097</v>
+        <v>-0.8111</v>
       </c>
       <c r="G65" t="n">
-        <v>-1</v>
+        <v>0.0546</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.1097</v>
+        <v>-0.8111</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1097</v>
+        <v>-0.8445</v>
       </c>
       <c r="J65" t="n">
-        <v>-1</v>
+        <v>0.0546</v>
       </c>
       <c r="K65" t="n">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="L65" t="n">
-        <v>59</v>
+        <v>157</v>
       </c>
       <c r="M65" t="n">
-        <v>-1.1097</v>
+        <v>-0.7899</v>
       </c>
       <c r="N65" t="n">
-        <v>115</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>DavCost</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.1586</v>
+        <v>-0.8098</v>
       </c>
       <c r="C66" t="n">
-        <v>-1.0867</v>
+        <v>-0.7595</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9055</v>
+        <v>-1.0036</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.1586</v>
+        <v>-0.8098</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.1586</v>
+        <v>-0.8098</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.1586</v>
+        <v>-0.8098</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.1586</v>
+        <v>-0.8098</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.1586</v>
+        <v>-0.8098</v>
       </c>
       <c r="N66" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1797</v>
+        <v>-0.8165</v>
       </c>
       <c r="C67" t="n">
-        <v>-1.1065</v>
+        <v>-0.7658</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9139</v>
+        <v>-1.0066</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.1797</v>
+        <v>-0.8165</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.1797</v>
+        <v>-0.8165</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.1797</v>
+        <v>-0.8165</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.1797</v>
+        <v>-0.8165</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.1797</v>
+        <v>-0.8165</v>
       </c>
       <c r="N67" t="n">
         <v>46</v>
@@ -3528,492 +3528,492 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DavCost</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2033</v>
+        <v>-0.8435</v>
       </c>
       <c r="C68" t="n">
-        <v>-1.1286</v>
+        <v>-0.7912</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9233</v>
+        <v>-1.0188</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2033</v>
+        <v>-0.8435</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.2033</v>
+        <v>-0.8435</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.2033</v>
+        <v>-0.8435</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.2033</v>
+        <v>-0.8435</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.2033</v>
+        <v>-0.8435</v>
       </c>
       <c r="N68" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2605</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="C69" t="n">
-        <v>-1.1823</v>
+        <v>-0.8571</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-1.0505</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2605</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.2605</v>
+        <v>-0.9204</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.0066</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.2605</v>
+        <v>-0.9204</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2605</v>
+        <v>-0.9204</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>0.0066</v>
       </c>
       <c r="K69" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.2605</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.3074</v>
+        <v>-0.968</v>
       </c>
       <c r="C70" t="n">
-        <v>-1.2263</v>
+        <v>-0.9079</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9648</v>
+        <v>-1.075</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.3074</v>
+        <v>-0.968</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.3074</v>
+        <v>-0.968</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.3074</v>
+        <v>-0.968</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.3074</v>
+        <v>-0.968</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.3074</v>
+        <v>-0.968</v>
       </c>
       <c r="N70" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.3303</v>
+        <v>-1.0033</v>
       </c>
       <c r="C71" t="n">
-        <v>-1.2477</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9739</v>
+        <v>-1.091</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3303</v>
+        <v>-1.0033</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.3303</v>
+        <v>-0.1145</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>-0.8888</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.3303</v>
+        <v>-0.1145</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.3303</v>
+        <v>-0.1145</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>-0.8888</v>
       </c>
       <c r="K71" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.3303</v>
+        <v>-1.0033</v>
       </c>
       <c r="N71" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3887</v>
+        <v>-1.0151</v>
       </c>
       <c r="C72" t="n">
-        <v>-1.3025</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9972</v>
+        <v>-1.0963</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3887</v>
+        <v>-1.0151</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.2852</v>
+        <v>-1.0151</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.1035</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.2852</v>
+        <v>-1.0151</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.296</v>
+        <v>-1.0151</v>
       </c>
       <c r="J72" t="n">
-        <v>-0.1035</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="L72" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.3995</v>
+        <v>-1.0151</v>
       </c>
       <c r="N72" t="n">
-        <v>287</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5762</v>
+        <v>-1.1369</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.4784</v>
+        <v>-1.0663</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0719</v>
+        <v>-1.1513</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5762</v>
+        <v>-1.1369</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.5762</v>
+        <v>-0.4312</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-0.7057</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.5762</v>
+        <v>-0.4312</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.5762</v>
+        <v>-0.4489</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-0.7057</v>
       </c>
       <c r="K73" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.5762</v>
+        <v>-1.1546</v>
       </c>
       <c r="N73" t="n">
-        <v>133</v>
+        <v>279</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.6665</v>
+        <v>-1.1922</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.5631</v>
+        <v>-1.1182</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1078</v>
+        <v>-1.1762</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.6665</v>
+        <v>-1.1922</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.6665</v>
+        <v>-1.1922</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.6665</v>
+        <v>-1.1922</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.6665</v>
+        <v>-1.1922</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.6665</v>
+        <v>-1.1922</v>
       </c>
       <c r="N74" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.6678</v>
+        <v>-1.1967</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.5643</v>
+        <v>-1.1224</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1084</v>
+        <v>-1.1783</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.6678</v>
+        <v>-1.1967</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3195</v>
+        <v>-1.1967</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.3483</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.3195</v>
+        <v>-1.1967</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.3195</v>
+        <v>-1.1967</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.3483</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="L75" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.6678</v>
+        <v>-1.1967</v>
       </c>
       <c r="N75" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.7249</v>
+        <v>-1.3538</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.6179</v>
+        <v>-1.2698</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1311</v>
+        <v>-1.2492</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.7249</v>
+        <v>-1.3538</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.7249</v>
+        <v>-1.212</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.7249</v>
+        <v>-1.212</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.7249</v>
+        <v>-1.212</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="K76" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.7249</v>
+        <v>-1.3538</v>
       </c>
       <c r="N76" t="n">
-        <v>52</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.7456</v>
+        <v>-1.5514</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.6373</v>
+        <v>-1.4551</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1394</v>
+        <v>-1.3384</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.7456</v>
+        <v>-1.5514</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.8758</v>
+        <v>-1.5514</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.8698</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.8758</v>
+        <v>-1.5514</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.8832</v>
+        <v>-1.5514</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.8698</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="L77" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.753</v>
+        <v>-1.5514</v>
       </c>
       <c r="N77" t="n">
-        <v>279</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>denis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.901</v>
+        <v>-1.597</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.783</v>
+        <v>-1.4979</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2013</v>
+        <v>-1.359</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.901</v>
+        <v>-1.597</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.901</v>
+        <v>-1.597</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.901</v>
+        <v>-1.597</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.901</v>
+        <v>-1.597</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.901</v>
+        <v>-1.597</v>
       </c>
       <c r="N78" t="n">
         <v>132</v>
@@ -4034,32 +4034,32 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>denis</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.1602</v>
+        <v>-1.8411</v>
       </c>
       <c r="C79" t="n">
-        <v>-2.0261</v>
+        <v>-1.7268</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3045</v>
+        <v>-1.4692</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.1602</v>
+        <v>-1.8411</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.1602</v>
+        <v>-1.8411</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.1602</v>
+        <v>-1.8411</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.1602</v>
+        <v>-1.8411</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.1602</v>
+        <v>-1.8411</v>
       </c>
       <c r="N79" t="n">
         <v>132</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.8415</v>
+        <v>-2.1265</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.6652</v>
+        <v>-1.9945</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.576</v>
+        <v>-1.598</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.8415</v>
+        <v>-2.1265</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.8415</v>
+        <v>-2.1265</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.8415</v>
+        <v>-2.1265</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.8415</v>
+        <v>-2.1265</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.8415</v>
+        <v>-2.1265</v>
       </c>
       <c r="N80" t="n">
         <v>133</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.1631</v>
+        <v>-2.8168</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.9668</v>
+        <v>-2.642</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7041</v>
+        <v>-1.9097</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.1631</v>
+        <v>-2.8168</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1631</v>
+        <v>-1.8301</v>
       </c>
       <c r="G81" t="n">
-        <v>-1</v>
+        <v>-0.9867</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1631</v>
+        <v>-1.8301</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.1813</v>
+        <v>-1.9054</v>
       </c>
       <c r="J81" t="n">
-        <v>-1</v>
+        <v>-0.9867</v>
       </c>
       <c r="K81" t="n">
         <v>105</v>
@@ -4163,7 +4163,7 @@
         <v>68</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.1813</v>
+        <v>-2.8921</v>
       </c>
       <c r="N81" t="n">
         <v>173</v>
@@ -4269,10 +4269,10 @@
         <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3362</v>
+        <v>1.2184</v>
       </c>
       <c r="J2" t="n">
-        <v>40.086</v>
+        <v>36.552</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.83</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5075</v>
+        <v>-0.4999</v>
       </c>
       <c r="J3" t="n">
-        <v>-15.225</v>
+        <v>-14.997</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.75</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.7045</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.819</v>
+        <v>-21.135</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.66</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-28.383</v>
+        <v>-27.837</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.06</v>
+        <v>-1.0496</v>
       </c>
       <c r="J6" t="n">
-        <v>-31.8</v>
+        <v>-31.488</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7069</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>21.207</v>
+        <v>26.265</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6361</v>
+        <v>0.7796</v>
       </c>
       <c r="J8" t="n">
-        <v>19.083</v>
+        <v>23.388</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1065</v>
+        <v>-0.0463</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.195</v>
+        <v>-1.389</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1065</v>
+        <v>-0.0463</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.195</v>
+        <v>-1.389</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5747</v>
+        <v>-0.3753</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.241</v>
+        <v>-11.259</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>2.01</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0064</v>
+        <v>1.7053</v>
       </c>
       <c r="J12" t="n">
-        <v>42.1344</v>
+        <v>35.8113</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.51</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1559</v>
+        <v>1.1192</v>
       </c>
       <c r="J13" t="n">
-        <v>24.2739</v>
+        <v>23.5032</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0293</v>
+        <v>1.0451</v>
       </c>
       <c r="J14" t="n">
-        <v>21.6153</v>
+        <v>21.9471</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0781</v>
+        <v>0.0057</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.6401</v>
+        <v>0.1197</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5201</v>
+        <v>-0.4438</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.9221</v>
+        <v>-9.319800000000001</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2003</v>
+        <v>0.1907</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2063</v>
+        <v>4.0047</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3381</v>
+        <v>-0.2703</v>
       </c>
       <c r="J18" t="n">
-        <v>-7.1001</v>
+        <v>-5.6763</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.55</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6269</v>
+        <v>-0.427</v>
       </c>
       <c r="J19" t="n">
-        <v>-13.1649</v>
+        <v>-8.967000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6965</v>
+        <v>-0.4739</v>
       </c>
       <c r="J20" t="n">
-        <v>-14.6265</v>
+        <v>-9.9519</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7498</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.7458</v>
+        <v>-10.7436</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.372</v>
+        <v>0.3858</v>
       </c>
       <c r="J22" t="n">
-        <v>7.068</v>
+        <v>7.3302</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3933</v>
+        <v>-0.3012</v>
       </c>
       <c r="J23" t="n">
-        <v>-7.4727</v>
+        <v>-5.7228</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4492</v>
+        <v>-0.3284</v>
       </c>
       <c r="J24" t="n">
-        <v>-8.534800000000001</v>
+        <v>-6.2396</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6997</v>
+        <v>-0.4757</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.2943</v>
+        <v>-9.0383</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.34</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-0.6264</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.1513</v>
+        <v>-11.9016</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>2.03</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9214</v>
+        <v>1.4491</v>
       </c>
       <c r="J27" t="n">
-        <v>36.5066</v>
+        <v>27.5329</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.98</v>
       </c>
       <c r="I28" t="n">
-        <v>1.876</v>
+        <v>1.3925</v>
       </c>
       <c r="J28" t="n">
-        <v>35.644</v>
+        <v>26.4575</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4656</v>
+        <v>0.473</v>
       </c>
       <c r="J29" t="n">
-        <v>8.846399999999999</v>
+        <v>8.987</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.469</v>
+        <v>-0.3888</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.911</v>
+        <v>-7.3872</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6994</v>
+        <v>-0.6389</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.2886</v>
+        <v>-12.1391</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>0.84</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1024</v>
       </c>
       <c r="J32" t="n">
-        <v>-2.0526</v>
+        <v>-2.2528</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>0.61</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4508</v>
+        <v>-0.3553</v>
       </c>
       <c r="J33" t="n">
-        <v>-9.9176</v>
+        <v>-7.8166</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>0.57</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5181</v>
+        <v>-0.393</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.3982</v>
+        <v>-8.646000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.54</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5846</v>
+        <v>-0.4188</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.8612</v>
+        <v>-9.2136</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.19</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0662</v>
+        <v>-0.7567</v>
       </c>
       <c r="J36" t="n">
-        <v>-23.4564</v>
+        <v>-16.6474</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.68</v>
       </c>
       <c r="I37" t="n">
-        <v>1.4777</v>
+        <v>1.0459</v>
       </c>
       <c r="J37" t="n">
-        <v>32.5094</v>
+        <v>23.0098</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.62</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3649</v>
+        <v>0.9749</v>
       </c>
       <c r="J38" t="n">
-        <v>30.0278</v>
+        <v>21.4478</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.46</v>
       </c>
       <c r="I39" t="n">
-        <v>1.0409</v>
+        <v>0.7824</v>
       </c>
       <c r="J39" t="n">
-        <v>22.8998</v>
+        <v>17.2128</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>1.13</v>
       </c>
       <c r="I40" t="n">
-        <v>0.244</v>
+        <v>0.3356</v>
       </c>
       <c r="J40" t="n">
-        <v>5.368</v>
+        <v>7.3832</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>0.137</v>
+        <v>0.2288</v>
       </c>
       <c r="J41" t="n">
-        <v>3.014</v>
+        <v>5.0336</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5339</v>
+        <v>0.4221</v>
       </c>
       <c r="J42" t="n">
-        <v>13.8814</v>
+        <v>10.9746</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1614</v>
+        <v>0.1115</v>
       </c>
       <c r="J43" t="n">
-        <v>4.1964</v>
+        <v>2.899</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.8</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3516</v>
+        <v>-0.2254</v>
       </c>
       <c r="J44" t="n">
-        <v>-9.1416</v>
+        <v>-5.8604</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.73</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4547</v>
+        <v>-0.2939</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.8222</v>
+        <v>-7.6414</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6398</v>
+        <v>-0.4258</v>
       </c>
       <c r="J46" t="n">
-        <v>-16.6348</v>
+        <v>-11.0708</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.54</v>
       </c>
       <c r="I47" t="n">
-        <v>0.767</v>
+        <v>0.5397</v>
       </c>
       <c r="J47" t="n">
-        <v>19.942</v>
+        <v>14.0322</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.42</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6276</v>
+        <v>0.4605</v>
       </c>
       <c r="J48" t="n">
-        <v>16.3176</v>
+        <v>11.973</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1138</v>
+        <v>-0.0491</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.9588</v>
+        <v>-1.2766</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2284</v>
+        <v>-0.126</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.9384</v>
+        <v>-3.276</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3957</v>
+        <v>-0.2435</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.2882</v>
+        <v>-6.331</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4848</v>
+        <v>0.4004</v>
       </c>
       <c r="J52" t="n">
-        <v>22.3008</v>
+        <v>18.4184</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4567</v>
+        <v>0.3844</v>
       </c>
       <c r="J53" t="n">
-        <v>21.0082</v>
+        <v>17.6824</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4281</v>
+        <v>0.3682</v>
       </c>
       <c r="J54" t="n">
-        <v>19.6926</v>
+        <v>16.9372</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3686</v>
+        <v>0.3323</v>
       </c>
       <c r="J55" t="n">
-        <v>16.9556</v>
+        <v>15.2858</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.8605</v>
       </c>
       <c r="J56" t="n">
-        <v>-41.1562</v>
+        <v>-39.583</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4502</v>
+        <v>0.447</v>
       </c>
       <c r="J57" t="n">
-        <v>20.7092</v>
+        <v>20.562</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1096</v>
+        <v>0.1143</v>
       </c>
       <c r="J58" t="n">
-        <v>5.0416</v>
+        <v>5.2578</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0902</v>
       </c>
       <c r="J59" t="n">
-        <v>3.9974</v>
+        <v>4.1492</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0968</v>
+        <v>-0.0509</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.4528</v>
+        <v>-2.3414</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.442</v>
+        <v>-0.2797</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.332</v>
+        <v>-12.8662</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.75</v>
       </c>
       <c r="I62" t="n">
-        <v>1.613</v>
+        <v>1.1319</v>
       </c>
       <c r="J62" t="n">
-        <v>37.099</v>
+        <v>26.0337</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>1.3346</v>
+        <v>0.9542</v>
       </c>
       <c r="J63" t="n">
-        <v>30.6958</v>
+        <v>21.9466</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.53</v>
       </c>
       <c r="I64" t="n">
-        <v>1.1966</v>
+        <v>0.8698</v>
       </c>
       <c r="J64" t="n">
-        <v>27.5218</v>
+        <v>20.0054</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1.25</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5433</v>
+        <v>0.5174</v>
       </c>
       <c r="J65" t="n">
-        <v>12.4959</v>
+        <v>11.9002</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.76</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8565</v>
+        <v>-0.8135</v>
       </c>
       <c r="J66" t="n">
-        <v>-19.6995</v>
+        <v>-18.7105</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.03</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2064</v>
+        <v>0.1917</v>
       </c>
       <c r="J67" t="n">
-        <v>4.7472</v>
+        <v>4.4091</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2064</v>
+        <v>0.1917</v>
       </c>
       <c r="J68" t="n">
-        <v>4.7472</v>
+        <v>4.4091</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4223</v>
+        <v>-0.2918</v>
       </c>
       <c r="J69" t="n">
-        <v>-9.712899999999999</v>
+        <v>-6.7114</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.58</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6152</v>
+        <v>-0.4131</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.1496</v>
+        <v>-9.501300000000001</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.31</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.6636</v>
       </c>
       <c r="J71" t="n">
-        <v>-21.8293</v>
+        <v>-15.2628</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8118</v>
+        <v>0.7405</v>
       </c>
       <c r="J72" t="n">
-        <v>24.354</v>
+        <v>22.215</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0618</v>
+        <v>0.0448</v>
       </c>
       <c r="J73" t="n">
-        <v>1.854</v>
+        <v>1.344</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1372</v>
+        <v>-0.0843</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.116</v>
+        <v>-2.529</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.91</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1957</v>
+        <v>-0.1188</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.871</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.41</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8613</v>
+        <v>-0.5955</v>
       </c>
       <c r="J76" t="n">
-        <v>-25.839</v>
+        <v>-17.865</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.62</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5156</v>
+        <v>1.0588</v>
       </c>
       <c r="J77" t="n">
-        <v>45.468</v>
+        <v>31.764</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4845</v>
+        <v>0.4084</v>
       </c>
       <c r="J78" t="n">
-        <v>14.535</v>
+        <v>12.252</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3463</v>
+        <v>-0.2827</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.389</v>
+        <v>-8.481</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4635</v>
+        <v>-0.401</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.905</v>
+        <v>-12.03</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.82</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.5925</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.431</v>
+        <v>-17.775</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2721</v>
+        <v>0.2834</v>
       </c>
       <c r="J82" t="n">
-        <v>7.8909</v>
+        <v>8.2186</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>0.97</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0235</v>
+        <v>-0.0382</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.6815</v>
+        <v>-1.1078</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.84</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2853</v>
+        <v>-0.1847</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.2737</v>
+        <v>-5.3563</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3807</v>
+        <v>-0.2447</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.0403</v>
+        <v>-7.0963</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4535</v>
+        <v>-0.2933</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.1515</v>
+        <v>-8.505699999999999</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6699000000000001</v>
+        <v>0.5043</v>
       </c>
       <c r="J87" t="n">
-        <v>19.4271</v>
+        <v>14.6247</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5402</v>
+        <v>0.426</v>
       </c>
       <c r="J88" t="n">
-        <v>15.6658</v>
+        <v>12.354</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0654</v>
+        <v>-0.0527</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.8966</v>
+        <v>-1.5283</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4809</v>
+        <v>-0.4324</v>
       </c>
       <c r="J90" t="n">
-        <v>-13.9461</v>
+        <v>-12.5396</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7399</v>
+        <v>-0.6972</v>
       </c>
       <c r="J91" t="n">
-        <v>-21.4571</v>
+        <v>-20.2188</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3382</v>
+        <v>0.3562</v>
       </c>
       <c r="J92" t="n">
-        <v>8.793200000000001</v>
+        <v>9.261200000000001</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1509</v>
+        <v>-0.1041</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.9234</v>
+        <v>-2.7066</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.91</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.175</v>
+        <v>-0.115</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.55</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.87</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2499</v>
+        <v>-0.1578</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.4974</v>
+        <v>-4.1028</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4351</v>
+        <v>-0.2786</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.3126</v>
+        <v>-7.2436</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.4438</v>
+        <v>1.0098</v>
       </c>
       <c r="J97" t="n">
-        <v>37.5388</v>
+        <v>26.2548</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0048</v>
+        <v>0.0383</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.1248</v>
+        <v>0.9958</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2442</v>
+        <v>-0.1838</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.3492</v>
+        <v>-4.7788</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.403</v>
+        <v>-0.3407</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.478</v>
+        <v>-8.8582</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.403</v>
+        <v>-0.3407</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.478</v>
+        <v>-8.8582</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2537</v>
+        <v>0.2564</v>
       </c>
       <c r="J102" t="n">
-        <v>6.0888</v>
+        <v>6.1536</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>0.96</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0274</v>
+        <v>-0.0453</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.6576</v>
+        <v>-1.0872</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1605</v>
+        <v>-0.1294</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.852</v>
+        <v>-3.1056</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2994</v>
+        <v>-0.2003</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.1856</v>
+        <v>-4.8072</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.47</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7783</v>
+        <v>-0.5303</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.6792</v>
+        <v>-12.7272</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.75</v>
       </c>
       <c r="I107" t="n">
-        <v>1.6934</v>
+        <v>1.1843</v>
       </c>
       <c r="J107" t="n">
-        <v>40.6416</v>
+        <v>28.4232</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.22</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5997</v>
+        <v>0.4962</v>
       </c>
       <c r="J108" t="n">
-        <v>14.3928</v>
+        <v>11.9088</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3288</v>
+        <v>0.3655</v>
       </c>
       <c r="J109" t="n">
-        <v>7.8912</v>
+        <v>8.772</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>1.09</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2128</v>
+        <v>0.2768</v>
       </c>
       <c r="J110" t="n">
-        <v>5.1072</v>
+        <v>6.6432</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.8425</v>
+        <v>-0.799</v>
       </c>
       <c r="J111" t="n">
-        <v>-20.22</v>
+        <v>-19.176</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.67</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9952</v>
+        <v>0.9075</v>
       </c>
       <c r="J112" t="n">
-        <v>25.8752</v>
+        <v>23.595</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2853</v>
+        <v>-0.1847</v>
       </c>
       <c r="J113" t="n">
-        <v>-7.4178</v>
+        <v>-4.8022</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.77</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3957</v>
+        <v>-0.2545</v>
       </c>
       <c r="J114" t="n">
-        <v>-10.2882</v>
+        <v>-6.617</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.64</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5752</v>
+        <v>-0.3788</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.9552</v>
+        <v>-9.848800000000001</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7487</v>
+        <v>-0.5077</v>
       </c>
       <c r="J116" t="n">
-        <v>-19.4662</v>
+        <v>-13.2002</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.96</v>
       </c>
       <c r="I117" t="n">
-        <v>1.9167</v>
+        <v>1.449</v>
       </c>
       <c r="J117" t="n">
-        <v>49.8342</v>
+        <v>37.674</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.19</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.4565</v>
       </c>
       <c r="J118" t="n">
-        <v>13.9308</v>
+        <v>11.869</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1093</v>
+        <v>-0.0395</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.8418</v>
+        <v>-1.027</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2479</v>
+        <v>-0.1728</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.4454</v>
+        <v>-4.4928</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9479</v>
+        <v>-0.9165</v>
       </c>
       <c r="J121" t="n">
-        <v>-24.6454</v>
+        <v>-23.829</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2269</v>
+        <v>0.237</v>
       </c>
       <c r="J122" t="n">
-        <v>8.1684</v>
+        <v>8.532</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0885</v>
+        <v>0.0742</v>
       </c>
       <c r="J123" t="n">
-        <v>3.186</v>
+        <v>2.6712</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0271</v>
+        <v>0.0065</v>
       </c>
       <c r="J124" t="n">
-        <v>0.9756</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.213</v>
+        <v>-0.1296</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.668</v>
+        <v>-4.6656</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4022</v>
+        <v>-0.2539</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.4792</v>
+        <v>-9.1404</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.26</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7942</v>
+        <v>0.5843</v>
       </c>
       <c r="J127" t="n">
-        <v>28.5912</v>
+        <v>21.0348</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.15</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5174</v>
+        <v>0.4178</v>
       </c>
       <c r="J128" t="n">
-        <v>18.6264</v>
+        <v>15.0408</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3219</v>
+        <v>-0.2688</v>
       </c>
       <c r="J129" t="n">
-        <v>-11.5884</v>
+        <v>-9.6768</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3532</v>
+        <v>-0.2992</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.7152</v>
+        <v>-10.7712</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4131</v>
+        <v>-0.3581</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.8716</v>
+        <v>-12.8916</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.13</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3444</v>
+        <v>0.2861</v>
       </c>
       <c r="J132" t="n">
-        <v>8.609999999999999</v>
+        <v>7.1525</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1873</v>
+        <v>0.1304</v>
       </c>
       <c r="J133" t="n">
-        <v>4.6825</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2602</v>
+        <v>-0.1891</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.505</v>
+        <v>-4.7275</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.67</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.52</v>
+        <v>-0.3424</v>
       </c>
       <c r="J135" t="n">
-        <v>-13</v>
+        <v>-8.56</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.5462</v>
       </c>
       <c r="J136" t="n">
-        <v>-19.9725</v>
+        <v>-13.655</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.66</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8971</v>
+        <v>0.6161</v>
       </c>
       <c r="J137" t="n">
-        <v>22.4275</v>
+        <v>15.4025</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.27</v>
       </c>
       <c r="I138" t="n">
-        <v>0.435</v>
+        <v>0.3571</v>
       </c>
       <c r="J138" t="n">
-        <v>10.875</v>
+        <v>8.9275</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3495</v>
+        <v>0.3001</v>
       </c>
       <c r="J139" t="n">
-        <v>8.737500000000001</v>
+        <v>7.5025</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3391</v>
+        <v>-0.203</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.477499999999999</v>
+        <v>-5.075</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5415</v>
+        <v>-0.3503</v>
       </c>
       <c r="J141" t="n">
-        <v>-13.5375</v>
+        <v>-8.7575</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0111</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>25.2775</v>
+        <v>18.535</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.4</v>
       </c>
       <c r="I143" t="n">
-        <v>0.9896</v>
+        <v>0.7285</v>
       </c>
       <c r="J143" t="n">
-        <v>24.74</v>
+        <v>18.2125</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.3</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7612</v>
+        <v>0.5975</v>
       </c>
       <c r="J144" t="n">
-        <v>19.03</v>
+        <v>14.9375</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>1.23</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5631</v>
+        <v>0.5044</v>
       </c>
       <c r="J145" t="n">
-        <v>14.0775</v>
+        <v>12.61</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4626</v>
+        <v>-0.3864</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.565</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.08</v>
       </c>
       <c r="I147" t="n">
-        <v>0.2988</v>
+        <v>0.3127</v>
       </c>
       <c r="J147" t="n">
-        <v>7.47</v>
+        <v>7.8175</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1565</v>
+        <v>0.1286</v>
       </c>
       <c r="J148" t="n">
-        <v>3.9125</v>
+        <v>3.215</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.58</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.617</v>
+        <v>-0.4141</v>
       </c>
       <c r="J149" t="n">
-        <v>-15.425</v>
+        <v>-10.3525</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.53</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6831</v>
+        <v>-0.4607</v>
       </c>
       <c r="J150" t="n">
-        <v>-17.0775</v>
+        <v>-11.5175</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.49</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7341</v>
+        <v>-0.498</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.3525</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.75</v>
       </c>
       <c r="I152" t="n">
-        <v>1.5677</v>
+        <v>1.1108</v>
       </c>
       <c r="J152" t="n">
-        <v>28.2186</v>
+        <v>19.9944</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.74</v>
       </c>
       <c r="I153" t="n">
-        <v>1.5496</v>
+        <v>1.0993</v>
       </c>
       <c r="J153" t="n">
-        <v>27.8928</v>
+        <v>19.7874</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>1.61</v>
       </c>
       <c r="I154" t="n">
-        <v>1.3045</v>
+        <v>0.9493</v>
       </c>
       <c r="J154" t="n">
-        <v>23.481</v>
+        <v>17.0874</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>1.38</v>
       </c>
       <c r="I155" t="n">
-        <v>0.7911</v>
+        <v>0.6766</v>
       </c>
       <c r="J155" t="n">
-        <v>14.2398</v>
+        <v>12.1788</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3986</v>
+        <v>-0.3131</v>
       </c>
       <c r="J156" t="n">
-        <v>-7.1748</v>
+        <v>-5.6358</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>0.59</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.4054</v>
+        <v>-0.3367</v>
       </c>
       <c r="J157" t="n">
-        <v>-7.2972</v>
+        <v>-6.0606</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.4518</v>
+        <v>-0.3696</v>
       </c>
       <c r="J158" t="n">
-        <v>-8.132400000000001</v>
+        <v>-6.6528</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>0.45</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.6388</v>
+        <v>-0.4801</v>
       </c>
       <c r="J159" t="n">
-        <v>-11.4984</v>
+        <v>-8.6418</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>0.43</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.6904</v>
+        <v>-0.4971</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.4272</v>
+        <v>-8.947800000000001</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.18</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.0614</v>
+        <v>-0.7513</v>
       </c>
       <c r="J161" t="n">
-        <v>-19.1052</v>
+        <v>-13.5234</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4474</v>
+        <v>0.5132</v>
       </c>
       <c r="J162" t="n">
-        <v>11.185</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.08</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2602</v>
+        <v>0.2636</v>
       </c>
       <c r="J163" t="n">
-        <v>6.505</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3423</v>
+        <v>-0.2279</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.557499999999999</v>
+        <v>-5.6975</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.66</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5349</v>
+        <v>-0.3524</v>
       </c>
       <c r="J165" t="n">
-        <v>-13.3725</v>
+        <v>-8.81</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.41</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.5829</v>
       </c>
       <c r="J166" t="n">
-        <v>-21.1575</v>
+        <v>-14.5725</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>1.58</v>
       </c>
       <c r="I167" t="n">
-        <v>1.4141</v>
+        <v>1.2639</v>
       </c>
       <c r="J167" t="n">
-        <v>35.3525</v>
+        <v>31.5975</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5609</v>
+        <v>0.5496</v>
       </c>
       <c r="J168" t="n">
-        <v>14.0225</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2151</v>
+        <v>0.2612</v>
       </c>
       <c r="J169" t="n">
-        <v>5.3775</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1963</v>
+        <v>-0.1267</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.9075</v>
+        <v>-3.1675</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.82</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.6055</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.57</v>
+        <v>-15.1375</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.47</v>
       </c>
       <c r="I172" t="n">
-        <v>0.727</v>
+        <v>0.6417</v>
       </c>
       <c r="J172" t="n">
-        <v>18.902</v>
+        <v>16.6842</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.31</v>
       </c>
       <c r="I173" t="n">
-        <v>0.5312</v>
+        <v>0.4501</v>
       </c>
       <c r="J173" t="n">
-        <v>13.8112</v>
+        <v>11.7026</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.85</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3106</v>
+        <v>-0.1886</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.0756</v>
+        <v>-4.9036</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4951</v>
+        <v>-0.3179</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.8726</v>
+        <v>-8.2654</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5471</v>
+        <v>-0.3558</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.2246</v>
+        <v>-9.2508</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6188</v>
+        <v>0.574</v>
       </c>
       <c r="J177" t="n">
-        <v>16.0888</v>
+        <v>14.924</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I178" t="n">
-        <v>0.1122</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="J178" t="n">
-        <v>2.9172</v>
+        <v>1.7706</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3716</v>
+        <v>-0.2371</v>
       </c>
       <c r="J179" t="n">
-        <v>-9.6616</v>
+        <v>-6.1646</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4444</v>
+        <v>-0.286</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.5544</v>
+        <v>-7.436</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6173</v>
+        <v>-0.409</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.0498</v>
+        <v>-10.634</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5012</v>
+        <v>0.5911</v>
       </c>
       <c r="J182" t="n">
-        <v>12.0288</v>
+        <v>14.1864</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>0.93</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0524</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.2576</v>
+        <v>-1.6464</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>0.79</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2943</v>
+        <v>-0.222</v>
       </c>
       <c r="J184" t="n">
-        <v>-7.0632</v>
+        <v>-5.328</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-0.4745</v>
       </c>
       <c r="J185" t="n">
-        <v>-16.8744</v>
+        <v>-11.388</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.38</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.8728</v>
+        <v>-0.6034</v>
       </c>
       <c r="J186" t="n">
-        <v>-20.9472</v>
+        <v>-14.4816</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.91</v>
       </c>
       <c r="I187" t="n">
-        <v>1.9399</v>
+        <v>1.6382</v>
       </c>
       <c r="J187" t="n">
-        <v>46.5576</v>
+        <v>39.3168</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3356</v>
+        <v>0.4054</v>
       </c>
       <c r="J188" t="n">
-        <v>8.054399999999999</v>
+        <v>9.7296</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>1.11</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2524</v>
+        <v>0.3244</v>
       </c>
       <c r="J189" t="n">
-        <v>6.0576</v>
+        <v>7.7856</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1952</v>
+        <v>0.2678</v>
       </c>
       <c r="J190" t="n">
-        <v>4.6848</v>
+        <v>6.4272</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.88</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5375</v>
+        <v>-0.4669</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.9</v>
+        <v>-11.2056</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.17</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6069</v>
+        <v>0.5538</v>
       </c>
       <c r="J192" t="n">
-        <v>18.207</v>
+        <v>16.614</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.03</v>
       </c>
       <c r="I193" t="n">
-        <v>0.182</v>
+        <v>0.1372</v>
       </c>
       <c r="J193" t="n">
-        <v>5.46</v>
+        <v>4.116</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1332</v>
+        <v>-0.1247</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.996</v>
+        <v>-3.741</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2511</v>
+        <v>-0.2223</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.533</v>
+        <v>-6.669</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7556</v>
+        <v>-0.7159</v>
       </c>
       <c r="J196" t="n">
-        <v>-22.668</v>
+        <v>-21.477</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.59</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8334</v>
+        <v>1.0276</v>
       </c>
       <c r="J197" t="n">
-        <v>25.002</v>
+        <v>30.828</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.48</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7093</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>21.279</v>
+        <v>26.355</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.27</v>
+        <v>-0.156</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.1</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3463</v>
+        <v>-0.2092</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.389</v>
+        <v>-6.276</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5487</v>
+        <v>-0.3559</v>
       </c>
       <c r="J201" t="n">
-        <v>-16.461</v>
+        <v>-10.677</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>2.17</v>
       </c>
       <c r="I202" t="n">
-        <v>2.0593</v>
+        <v>1.8283</v>
       </c>
       <c r="J202" t="n">
-        <v>35.0081</v>
+        <v>31.0811</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.65</v>
       </c>
       <c r="I203" t="n">
-        <v>1.3327</v>
+        <v>1.2568</v>
       </c>
       <c r="J203" t="n">
-        <v>22.6559</v>
+        <v>21.3656</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.59</v>
       </c>
       <c r="I204" t="n">
-        <v>1.1988</v>
+        <v>1.19</v>
       </c>
       <c r="J204" t="n">
-        <v>20.3796</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.41</v>
       </c>
       <c r="I205" t="n">
-        <v>0.8158</v>
+        <v>0.9566</v>
       </c>
       <c r="J205" t="n">
-        <v>13.8686</v>
+        <v>16.2622</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1964</v>
+        <v>0.3015</v>
       </c>
       <c r="J206" t="n">
-        <v>3.3388</v>
+        <v>5.1255</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>0.64</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.2794</v>
+        <v>-0.2375</v>
       </c>
       <c r="J207" t="n">
-        <v>-4.7498</v>
+        <v>-4.0375</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.59</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.3564</v>
+        <v>-0.2999</v>
       </c>
       <c r="J208" t="n">
-        <v>-6.0588</v>
+        <v>-5.0983</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.43</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.6133</v>
+        <v>-0.482</v>
       </c>
       <c r="J209" t="n">
-        <v>-10.4261</v>
+        <v>-8.194000000000001</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.2</v>
       </c>
       <c r="I210" t="n">
-        <v>-1.0193</v>
+        <v>-0.717</v>
       </c>
       <c r="J210" t="n">
-        <v>-17.3281</v>
+        <v>-12.189</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.05</v>
       </c>
       <c r="I211" t="n">
-        <v>-1.222</v>
+        <v>-0.8882</v>
       </c>
       <c r="J211" t="n">
-        <v>-20.774</v>
+        <v>-15.0994</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6443</v>
+        <v>0.7855</v>
       </c>
       <c r="J212" t="n">
-        <v>22.5505</v>
+        <v>27.4925</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3176</v>
+        <v>0.3467</v>
       </c>
       <c r="J213" t="n">
-        <v>11.116</v>
+        <v>12.1345</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.79</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3813</v>
+        <v>-0.2411</v>
       </c>
       <c r="J214" t="n">
-        <v>-13.3455</v>
+        <v>-8.438499999999999</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4527</v>
+        <v>-0.2901</v>
       </c>
       <c r="J215" t="n">
-        <v>-15.8445</v>
+        <v>-10.1535</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6106</v>
+        <v>-0.4035</v>
       </c>
       <c r="J216" t="n">
-        <v>-21.371</v>
+        <v>-14.1225</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1251</v>
+        <v>1.0713</v>
       </c>
       <c r="J217" t="n">
-        <v>39.3785</v>
+        <v>37.4955</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.37</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0191</v>
+        <v>0.9936</v>
       </c>
       <c r="J218" t="n">
-        <v>35.6685</v>
+        <v>34.776</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.03</v>
       </c>
       <c r="I219" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.1161</v>
       </c>
       <c r="J219" t="n">
-        <v>2.8385</v>
+        <v>4.0635</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6937</v>
+        <v>-0.6421</v>
       </c>
       <c r="J220" t="n">
-        <v>-24.2795</v>
+        <v>-22.4735</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8357</v>
+        <v>-0.7948</v>
       </c>
       <c r="J221" t="n">
-        <v>-29.2495</v>
+        <v>-27.818</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6103</v>
+        <v>0.5288</v>
       </c>
       <c r="J222" t="n">
-        <v>17.0884</v>
+        <v>14.8064</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.33</v>
       </c>
       <c r="I223" t="n">
-        <v>0.5354</v>
+        <v>0.4579</v>
       </c>
       <c r="J223" t="n">
-        <v>14.9912</v>
+        <v>12.8212</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0235</v>
+        <v>0.04</v>
       </c>
       <c r="J224" t="n">
-        <v>0.658</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.002</v>
+        <v>0.0195</v>
       </c>
       <c r="J225" t="n">
-        <v>-0.056</v>
+        <v>0.546</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.61</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6434</v>
+        <v>-0.4272</v>
       </c>
       <c r="J226" t="n">
-        <v>-18.0152</v>
+        <v>-11.9616</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.1</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2791</v>
+        <v>0.2225</v>
       </c>
       <c r="J227" t="n">
-        <v>7.8148</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0969</v>
+        <v>-0.0868</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.7132</v>
+        <v>-2.4304</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.88</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1922</v>
+        <v>-0.1427</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.3816</v>
+        <v>-3.9956</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.78</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3744</v>
+        <v>-0.2423</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.4832</v>
+        <v>-6.7844</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.64</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5712</v>
+        <v>-0.3764</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.9936</v>
+        <v>-10.5392</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>0.89</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.0508</v>
+        <v>-0.0725</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.0668</v>
+        <v>-1.5225</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.85</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1173</v>
+        <v>-0.121</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.4633</v>
+        <v>-2.541</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.53</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.6438</v>
+        <v>-0.4406</v>
       </c>
       <c r="J234" t="n">
-        <v>-13.5198</v>
+        <v>-9.252599999999999</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.6582</v>
+        <v>-0.45</v>
       </c>
       <c r="J235" t="n">
-        <v>-13.8222</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.31</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.9323</v>
+        <v>-0.6494</v>
       </c>
       <c r="J236" t="n">
-        <v>-19.5783</v>
+        <v>-13.6374</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.65</v>
       </c>
       <c r="I237" t="n">
-        <v>1.4376</v>
+        <v>1.2912</v>
       </c>
       <c r="J237" t="n">
-        <v>30.1896</v>
+        <v>27.1152</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.57</v>
       </c>
       <c r="I238" t="n">
-        <v>1.2845</v>
+        <v>1.195</v>
       </c>
       <c r="J238" t="n">
-        <v>26.9745</v>
+        <v>25.095</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.38</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8796</v>
+        <v>0.9334</v>
       </c>
       <c r="J239" t="n">
-        <v>18.4716</v>
+        <v>19.6014</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.21</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4551</v>
+        <v>0.5532</v>
       </c>
       <c r="J240" t="n">
-        <v>9.5571</v>
+        <v>11.6172</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.99</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2295</v>
+        <v>-0.1412</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.8195</v>
+        <v>-2.9652</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.107</v>
+        <v>-0.1011</v>
       </c>
       <c r="J242" t="n">
-        <v>-2.354</v>
+        <v>-2.2242</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>0.91</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.107</v>
+        <v>-0.1011</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.354</v>
+        <v>-2.2242</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1952</v>
+        <v>-0.1567</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.2944</v>
+        <v>-3.4474</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3121</v>
+        <v>-0.2161</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.8662</v>
+        <v>-4.7542</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6613</v>
+        <v>-0.4431</v>
       </c>
       <c r="J246" t="n">
-        <v>-14.5486</v>
+        <v>-9.748200000000001</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4877</v>
+        <v>1.3141</v>
       </c>
       <c r="J247" t="n">
-        <v>32.7294</v>
+        <v>28.9102</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.38</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9871</v>
+        <v>0.9778</v>
       </c>
       <c r="J248" t="n">
-        <v>21.7162</v>
+        <v>21.5116</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6629</v>
+        <v>0.6606</v>
       </c>
       <c r="J249" t="n">
-        <v>14.5838</v>
+        <v>14.5332</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.95</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3189</v>
+        <v>-0.2433</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.0158</v>
+        <v>-5.3526</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.0352</v>
+        <v>-1.0145</v>
       </c>
       <c r="J251" t="n">
-        <v>-22.7744</v>
+        <v>-22.319</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>0.98</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0184</v>
+        <v>-0.0293</v>
       </c>
       <c r="J252" t="n">
-        <v>-0.5152</v>
+        <v>-0.8204</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>0.96</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.057</v>
       </c>
       <c r="J253" t="n">
-        <v>-1.7976</v>
+        <v>-1.596</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.95</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0859</v>
+        <v>-0.0696</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.4052</v>
+        <v>-1.9488</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.9</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1974</v>
+        <v>-0.1262</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.5272</v>
+        <v>-3.5336</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.83</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3173</v>
+        <v>-0.1996</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.884399999999999</v>
+        <v>-5.5888</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.36</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9843</v>
+        <v>0.9651</v>
       </c>
       <c r="J257" t="n">
-        <v>27.5604</v>
+        <v>27.0228</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.319</v>
+        <v>0.3235</v>
       </c>
       <c r="J258" t="n">
-        <v>8.932</v>
+        <v>9.058</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.06</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1727</v>
+        <v>0.2089</v>
       </c>
       <c r="J259" t="n">
-        <v>4.8356</v>
+        <v>5.8492</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.03</v>
       </c>
       <c r="I260" t="n">
-        <v>0.0653</v>
+        <v>0.1105</v>
       </c>
       <c r="J260" t="n">
-        <v>1.8284</v>
+        <v>3.094</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3524</v>
+        <v>-0.2866</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.8672</v>
+        <v>-8.024800000000001</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.48</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1543</v>
+        <v>1.1035</v>
       </c>
       <c r="J262" t="n">
-        <v>28.8575</v>
+        <v>27.5875</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.41</v>
       </c>
       <c r="I263" t="n">
-        <v>1.008</v>
+        <v>1.0081</v>
       </c>
       <c r="J263" t="n">
-        <v>25.2</v>
+        <v>25.2025</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8754</v>
+        <v>0.8915</v>
       </c>
       <c r="J264" t="n">
-        <v>21.885</v>
+        <v>22.2875</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.08</v>
       </c>
       <c r="I265" t="n">
-        <v>0.1537</v>
+        <v>0.2314</v>
       </c>
       <c r="J265" t="n">
-        <v>3.8425</v>
+        <v>5.785</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.96</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3133</v>
+        <v>-0.2308</v>
       </c>
       <c r="J266" t="n">
-        <v>-7.8325</v>
+        <v>-5.77</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3551</v>
+        <v>0.3879</v>
       </c>
       <c r="J267" t="n">
-        <v>8.8775</v>
+        <v>9.6975</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.2422</v>
+        <v>-0.1863</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.055</v>
+        <v>-4.6575</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.7</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.469</v>
+        <v>-0.3102</v>
       </c>
       <c r="J269" t="n">
-        <v>-11.725</v>
+        <v>-7.755</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4978</v>
+        <v>-0.3292</v>
       </c>
       <c r="J270" t="n">
-        <v>-12.445</v>
+        <v>-8.23</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.65</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.3575</v>
       </c>
       <c r="J271" t="n">
-        <v>-13.495</v>
+        <v>-8.9375</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.6</v>
       </c>
       <c r="I272" t="n">
-        <v>1.399</v>
+        <v>1.258</v>
       </c>
       <c r="J272" t="n">
-        <v>32.177</v>
+        <v>28.934</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.5</v>
       </c>
       <c r="I273" t="n">
-        <v>1.2036</v>
+        <v>1.1326</v>
       </c>
       <c r="J273" t="n">
-        <v>27.6828</v>
+        <v>26.0498</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.31</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7929</v>
+        <v>0.8065</v>
       </c>
       <c r="J274" t="n">
-        <v>18.2367</v>
+        <v>18.5495</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.1367</v>
+        <v>-0.058</v>
       </c>
       <c r="J275" t="n">
-        <v>-3.1441</v>
+        <v>-1.334</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7853</v>
+        <v>-0.735</v>
       </c>
       <c r="J276" t="n">
-        <v>-18.0619</v>
+        <v>-16.905</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.1276</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="J277" t="n">
-        <v>2.9348</v>
+        <v>2.1896</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.85</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.2105</v>
+        <v>-0.1666</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.8415</v>
+        <v>-3.8318</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.84</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.228</v>
+        <v>-0.1769</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.244</v>
+        <v>-4.0687</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.228</v>
+        <v>-0.1769</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.244</v>
+        <v>-4.0687</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.48</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.7597</v>
+        <v>-0.5163</v>
       </c>
       <c r="J281" t="n">
-        <v>-17.4731</v>
+        <v>-11.8749</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.79</v>
       </c>
       <c r="I282" t="n">
-        <v>1.7385</v>
+        <v>1.4848</v>
       </c>
       <c r="J282" t="n">
-        <v>38.247</v>
+        <v>32.6656</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.43</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0506</v>
+        <v>1.0383</v>
       </c>
       <c r="J283" t="n">
-        <v>23.1132</v>
+        <v>22.8426</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.02</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0429</v>
+        <v>0.0336</v>
       </c>
       <c r="J284" t="n">
-        <v>-0.9438</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.02</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.0429</v>
+        <v>0.0336</v>
       </c>
       <c r="J285" t="n">
-        <v>-0.9438</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>1.02</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.0429</v>
+        <v>0.0336</v>
       </c>
       <c r="J286" t="n">
-        <v>-0.9438</v>
+        <v>0.7392</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.19</v>
       </c>
       <c r="I287" t="n">
-        <v>0.4776</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J287" t="n">
-        <v>10.5072</v>
+        <v>12.364</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>0.8</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.253</v>
+        <v>-0.2054</v>
       </c>
       <c r="J288" t="n">
-        <v>-5.566</v>
+        <v>-4.5188</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>0.68</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.4681</v>
+        <v>-0.3187</v>
       </c>
       <c r="J289" t="n">
-        <v>-10.2982</v>
+        <v>-7.0114</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.55</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.6536</v>
+        <v>-0.4402</v>
       </c>
       <c r="J290" t="n">
-        <v>-14.3792</v>
+        <v>-9.6844</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.41</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.8304</v>
+        <v>-0.5705</v>
       </c>
       <c r="J291" t="n">
-        <v>-18.2688</v>
+        <v>-12.551</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.24</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4434</v>
+        <v>0.5148</v>
       </c>
       <c r="J292" t="n">
-        <v>12.8586</v>
+        <v>14.9292</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1785</v>
+        <v>0.1859</v>
       </c>
       <c r="J293" t="n">
-        <v>5.1765</v>
+        <v>5.3911</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.06</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1595</v>
+        <v>0.1639</v>
       </c>
       <c r="J294" t="n">
-        <v>4.6255</v>
+        <v>4.7531</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.84</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3217</v>
+        <v>-0.1972</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.3293</v>
+        <v>-5.7188</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.74</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4652</v>
+        <v>-0.2968</v>
       </c>
       <c r="J296" t="n">
-        <v>-13.4908</v>
+        <v>-8.607200000000001</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.22</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7425</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J297" t="n">
-        <v>21.5325</v>
+        <v>20.1289</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.18</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.5884</v>
       </c>
       <c r="J298" t="n">
-        <v>18.6354</v>
+        <v>17.0636</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.95</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.198</v>
+        <v>-0.1875</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.742</v>
+        <v>-5.4375</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.91</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3391</v>
+        <v>-0.3081</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.8339</v>
+        <v>-8.934900000000001</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.53</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.2592</v>
+        <v>-1.2693</v>
       </c>
       <c r="J301" t="n">
-        <v>-36.5168</v>
+        <v>-36.8097</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.73</v>
       </c>
       <c r="I302" t="n">
-        <v>1.028</v>
+        <v>1.2031</v>
       </c>
       <c r="J302" t="n">
-        <v>30.84</v>
+        <v>36.093</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.96</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0941</v>
+        <v>-0.0602</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.823</v>
+        <v>-1.806</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2328</v>
+        <v>-0.1412</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.984</v>
+        <v>-4.236</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4868</v>
+        <v>-0.313</v>
       </c>
       <c r="J305" t="n">
-        <v>-14.604</v>
+        <v>-9.390000000000001</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.7362</v>
+        <v>-0.4981</v>
       </c>
       <c r="J306" t="n">
-        <v>-22.086</v>
+        <v>-14.943</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.36</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0559</v>
+        <v>1.0187</v>
       </c>
       <c r="J307" t="n">
-        <v>31.677</v>
+        <v>30.561</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1446</v>
+        <v>0.1013</v>
       </c>
       <c r="J308" t="n">
-        <v>4.338</v>
+        <v>3.039</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>0.98</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.0885</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.247</v>
+        <v>-2.655</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1246</v>
+        <v>-0.1242</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.738</v>
+        <v>-3.726</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.52</v>
       </c>
       <c r="I311" t="n">
-        <v>-1.2824</v>
+        <v>-1.2959</v>
       </c>
       <c r="J311" t="n">
-        <v>-38.472</v>
+        <v>-38.877</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.15</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3641</v>
+        <v>0.401</v>
       </c>
       <c r="J312" t="n">
-        <v>9.8307</v>
+        <v>10.827</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.04</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1758</v>
+        <v>0.1589</v>
       </c>
       <c r="J313" t="n">
-        <v>4.7466</v>
+        <v>4.2903</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>0.89</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1648</v>
+        <v>-0.1305</v>
       </c>
       <c r="J314" t="n">
-        <v>-4.4496</v>
+        <v>-3.5235</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.581</v>
+        <v>-0.3839</v>
       </c>
       <c r="J315" t="n">
-        <v>-15.687</v>
+        <v>-10.3653</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.55</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6828</v>
+        <v>-0.4581</v>
       </c>
       <c r="J316" t="n">
-        <v>-18.4356</v>
+        <v>-12.3687</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.52</v>
       </c>
       <c r="I317" t="n">
-        <v>1.2983</v>
+        <v>1.187</v>
       </c>
       <c r="J317" t="n">
-        <v>35.0541</v>
+        <v>32.049</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.39</v>
       </c>
       <c r="I318" t="n">
-        <v>1.0318</v>
+        <v>1.0093</v>
       </c>
       <c r="J318" t="n">
-        <v>27.8586</v>
+        <v>27.2511</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.05</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1182</v>
+        <v>0.17</v>
       </c>
       <c r="J319" t="n">
-        <v>3.1914</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.99</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1528</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J320" t="n">
-        <v>-4.1256</v>
+        <v>-2.295</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.9617</v>
+        <v>-0.9322</v>
       </c>
       <c r="J321" t="n">
-        <v>-25.9659</v>
+        <v>-25.1694</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.25</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5171</v>
+        <v>0.6098</v>
       </c>
       <c r="J322" t="n">
-        <v>12.4104</v>
+        <v>14.6352</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.04</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1856</v>
+        <v>0.1687</v>
       </c>
       <c r="J323" t="n">
-        <v>4.4544</v>
+        <v>4.0488</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.74</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.4209</v>
+        <v>-0.2762</v>
       </c>
       <c r="J324" t="n">
-        <v>-10.1016</v>
+        <v>-6.6288</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.71</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.4649</v>
+        <v>-0.3049</v>
       </c>
       <c r="J325" t="n">
-        <v>-11.1576</v>
+        <v>-7.3176</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.4</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.8578</v>
+        <v>-0.592</v>
       </c>
       <c r="J326" t="n">
-        <v>-20.5872</v>
+        <v>-14.208</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.84</v>
       </c>
       <c r="I327" t="n">
-        <v>1.8402</v>
+        <v>1.5551</v>
       </c>
       <c r="J327" t="n">
-        <v>44.1648</v>
+        <v>37.3224</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.62</v>
       </c>
       <c r="I328" t="n">
-        <v>1.4436</v>
+        <v>1.2865</v>
       </c>
       <c r="J328" t="n">
-        <v>34.6464</v>
+        <v>30.876</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>1.13</v>
       </c>
       <c r="I329" t="n">
-        <v>0.3091</v>
+        <v>0.3793</v>
       </c>
       <c r="J329" t="n">
-        <v>7.4184</v>
+        <v>9.103199999999999</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.79</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.759</v>
+        <v>-0.7064</v>
       </c>
       <c r="J330" t="n">
-        <v>-18.216</v>
+        <v>-16.9536</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.8727</v>
+        <v>-0.832</v>
       </c>
       <c r="J331" t="n">
-        <v>-20.9448</v>
+        <v>-19.968</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.07</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1975</v>
+        <v>0.1985</v>
       </c>
       <c r="J332" t="n">
-        <v>5.7275</v>
+        <v>5.7565</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.07</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1975</v>
+        <v>0.1985</v>
       </c>
       <c r="J333" t="n">
-        <v>5.7275</v>
+        <v>5.7565</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.89</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2242</v>
+        <v>-0.1388</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.5018</v>
+        <v>-4.0252</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.85</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2916</v>
+        <v>-0.1812</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.4564</v>
+        <v>-5.2548</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3232</v>
+        <v>-0.2018</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.3728</v>
+        <v>-5.8522</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.33</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9366</v>
       </c>
       <c r="J337" t="n">
-        <v>27.9328</v>
+        <v>27.1614</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.19</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6325</v>
+        <v>0.5881</v>
       </c>
       <c r="J338" t="n">
-        <v>18.3425</v>
+        <v>17.0549</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.99</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0861</v>
+        <v>-0.0567</v>
       </c>
       <c r="J339" t="n">
-        <v>-2.4969</v>
+        <v>-1.6443</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.85</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.545</v>
+        <v>-0.4932</v>
       </c>
       <c r="J340" t="n">
-        <v>-15.805</v>
+        <v>-14.3028</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.72</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.8647</v>
+        <v>-0.829</v>
       </c>
       <c r="J341" t="n">
-        <v>-25.0763</v>
+        <v>-24.041</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.3938</v>
+        <v>1.2504</v>
       </c>
       <c r="J342" t="n">
-        <v>39.0264</v>
+        <v>35.0112</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.13</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3751</v>
+        <v>0.3977</v>
       </c>
       <c r="J343" t="n">
-        <v>10.5028</v>
+        <v>11.1356</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>1.04</v>
       </c>
       <c r="I344" t="n">
-        <v>0.0815</v>
+        <v>0.1361</v>
       </c>
       <c r="J344" t="n">
-        <v>2.282</v>
+        <v>3.8108</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>1.02</v>
       </c>
       <c r="I345" t="n">
-        <v>0.0068</v>
+        <v>0.0646</v>
       </c>
       <c r="J345" t="n">
-        <v>0.1904</v>
+        <v>1.8088</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.9</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4542</v>
+        <v>-0.3859</v>
       </c>
       <c r="J346" t="n">
-        <v>-12.7176</v>
+        <v>-10.8052</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.3</v>
       </c>
       <c r="I347" t="n">
-        <v>0.5725</v>
+        <v>0.6865</v>
       </c>
       <c r="J347" t="n">
-        <v>16.03</v>
+        <v>19.222</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>0.92</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1111</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.1108</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>0.85</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2506</v>
+        <v>-0.1719</v>
       </c>
       <c r="J349" t="n">
-        <v>-7.0168</v>
+        <v>-4.8132</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.72</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.4595</v>
+        <v>-0.2992</v>
       </c>
       <c r="J350" t="n">
-        <v>-12.866</v>
+        <v>-8.377599999999999</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.49</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.7563</v>
+        <v>-0.5135</v>
       </c>
       <c r="J351" t="n">
-        <v>-21.1764</v>
+        <v>-14.378</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.51</v>
       </c>
       <c r="I352" t="n">
-        <v>1.1696</v>
+        <v>1.1237</v>
       </c>
       <c r="J352" t="n">
-        <v>25.7312</v>
+        <v>24.7214</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.5</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1492</v>
+        <v>1.1114</v>
       </c>
       <c r="J353" t="n">
-        <v>25.2824</v>
+        <v>24.4508</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.28</v>
       </c>
       <c r="I354" t="n">
-        <v>0.6271</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="J354" t="n">
-        <v>13.7962</v>
+        <v>15.8466</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.28</v>
       </c>
       <c r="I355" t="n">
-        <v>0.6271</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="J355" t="n">
-        <v>13.7962</v>
+        <v>15.8466</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>1.18</v>
       </c>
       <c r="I356" t="n">
-        <v>0.3855</v>
+        <v>0.4809</v>
       </c>
       <c r="J356" t="n">
-        <v>8.481</v>
+        <v>10.5798</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.3</v>
       </c>
       <c r="I357" t="n">
-        <v>0.702</v>
+        <v>0.9346</v>
       </c>
       <c r="J357" t="n">
-        <v>15.444</v>
+        <v>20.5612</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>0.65</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.4176</v>
+        <v>-0.3274</v>
       </c>
       <c r="J358" t="n">
-        <v>-9.187200000000001</v>
+        <v>-7.2028</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.43</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.7737000000000001</v>
+        <v>-0.5305</v>
       </c>
       <c r="J359" t="n">
-        <v>-17.0214</v>
+        <v>-11.671</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.34</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.8903</v>
+        <v>-0.6169</v>
       </c>
       <c r="J360" t="n">
-        <v>-19.5866</v>
+        <v>-13.5718</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.26</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.9887</v>
+        <v>-0.6941000000000001</v>
       </c>
       <c r="J361" t="n">
-        <v>-21.7514</v>
+        <v>-15.2702</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.13</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3177</v>
+        <v>0.3426</v>
       </c>
       <c r="J362" t="n">
-        <v>9.2133</v>
+        <v>9.9354</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.05</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1796</v>
+        <v>0.1686</v>
       </c>
       <c r="J363" t="n">
-        <v>5.2084</v>
+        <v>4.8894</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>0.82</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.3216</v>
+        <v>-0.2059</v>
       </c>
       <c r="J364" t="n">
-        <v>-9.3264</v>
+        <v>-5.9711</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.3374</v>
+        <v>-0.2159</v>
       </c>
       <c r="J365" t="n">
-        <v>-9.784599999999999</v>
+        <v>-6.2611</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.65</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.5639</v>
+        <v>-0.3704</v>
       </c>
       <c r="J366" t="n">
-        <v>-16.3531</v>
+        <v>-10.7416</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.8077</v>
+        <v>0.7831</v>
       </c>
       <c r="J367" t="n">
-        <v>23.4233</v>
+        <v>22.7099</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.18</v>
       </c>
       <c r="I368" t="n">
-        <v>0.5607</v>
+        <v>0.5356</v>
       </c>
       <c r="J368" t="n">
-        <v>16.2603</v>
+        <v>15.5324</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.13</v>
       </c>
       <c r="I369" t="n">
-        <v>0.4213</v>
+        <v>0.4053</v>
       </c>
       <c r="J369" t="n">
-        <v>12.2177</v>
+        <v>11.7537</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.96</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.252</v>
+        <v>-0.1882</v>
       </c>
       <c r="J370" t="n">
-        <v>-7.308</v>
+        <v>-5.4578</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.9</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.4385</v>
+        <v>-0.3745</v>
       </c>
       <c r="J371" t="n">
-        <v>-12.7165</v>
+        <v>-10.8605</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.39</v>
       </c>
       <c r="I372" t="n">
-        <v>1.0718</v>
+        <v>1.034</v>
       </c>
       <c r="J372" t="n">
-        <v>36.4412</v>
+        <v>35.156</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.13</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4473</v>
+        <v>0.4151</v>
       </c>
       <c r="J373" t="n">
-        <v>15.2082</v>
+        <v>14.1134</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.97</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.1971</v>
+        <v>-0.1437</v>
       </c>
       <c r="J374" t="n">
-        <v>-6.7014</v>
+        <v>-4.8858</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.92</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3641</v>
+        <v>-0.3053</v>
       </c>
       <c r="J375" t="n">
-        <v>-12.3794</v>
+        <v>-10.3802</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.86</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.5342</v>
+        <v>-0.477</v>
       </c>
       <c r="J376" t="n">
-        <v>-18.1628</v>
+        <v>-16.218</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.21</v>
       </c>
       <c r="I377" t="n">
-        <v>0.4451</v>
+        <v>0.5102</v>
       </c>
       <c r="J377" t="n">
-        <v>15.1334</v>
+        <v>17.3468</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.137</v>
+        <v>-0.1106</v>
       </c>
       <c r="J378" t="n">
-        <v>-4.658</v>
+        <v>-3.7604</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.86</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.2413</v>
+        <v>-0.1631</v>
       </c>
       <c r="J379" t="n">
-        <v>-8.2042</v>
+        <v>-5.5454</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.72</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.4637</v>
+        <v>-0.3011</v>
       </c>
       <c r="J380" t="n">
-        <v>-15.7658</v>
+        <v>-10.2374</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.65</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.3676</v>
       </c>
       <c r="J381" t="n">
-        <v>-19.006</v>
+        <v>-12.4984</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.62</v>
       </c>
       <c r="I382" t="n">
-        <v>1.4182</v>
+        <v>1.2729</v>
       </c>
       <c r="J382" t="n">
-        <v>34.0368</v>
+        <v>30.5496</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.5</v>
       </c>
       <c r="I383" t="n">
-        <v>1.1842</v>
+        <v>1.1242</v>
       </c>
       <c r="J383" t="n">
-        <v>28.4208</v>
+        <v>26.9808</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.26</v>
       </c>
       <c r="I384" t="n">
-        <v>0.6223</v>
+        <v>0.6877</v>
       </c>
       <c r="J384" t="n">
-        <v>14.9352</v>
+        <v>16.5048</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>1.11</v>
       </c>
       <c r="I385" t="n">
-        <v>0.2305</v>
+        <v>0.3123</v>
       </c>
       <c r="J385" t="n">
-        <v>5.532</v>
+        <v>7.4952</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.9</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4974</v>
+        <v>-0.4221</v>
       </c>
       <c r="J386" t="n">
-        <v>-11.9376</v>
+        <v>-10.1304</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>0.86</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.142</v>
+        <v>-0.1347</v>
       </c>
       <c r="J387" t="n">
-        <v>-3.408</v>
+        <v>-3.2328</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>0.75</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.3202</v>
+        <v>-0.2508</v>
       </c>
       <c r="J388" t="n">
-        <v>-7.6848</v>
+        <v>-6.0192</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>0.71</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.3895</v>
+        <v>-0.2887</v>
       </c>
       <c r="J389" t="n">
-        <v>-9.348000000000001</v>
+        <v>-6.9288</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.68</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.4527</v>
+        <v>-0.3152</v>
       </c>
       <c r="J390" t="n">
-        <v>-10.8648</v>
+        <v>-7.5648</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.5</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.712</v>
+        <v>-0.4828</v>
       </c>
       <c r="J391" t="n">
-        <v>-17.088</v>
+        <v>-11.5872</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.6</v>
       </c>
       <c r="I392" t="n">
-        <v>1.4222</v>
+        <v>1.271</v>
       </c>
       <c r="J392" t="n">
-        <v>31.2884</v>
+        <v>27.962</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.2</v>
       </c>
       <c r="I393" t="n">
-        <v>0.5412</v>
+        <v>0.5614</v>
       </c>
       <c r="J393" t="n">
-        <v>11.9064</v>
+        <v>12.3508</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I394" t="n">
-        <v>0.3844</v>
+        <v>0.4391</v>
       </c>
       <c r="J394" t="n">
-        <v>8.456799999999999</v>
+        <v>9.6602</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>1.09</v>
       </c>
       <c r="I395" t="n">
-        <v>0.2118</v>
+        <v>0.2764</v>
       </c>
       <c r="J395" t="n">
-        <v>4.6596</v>
+        <v>6.0808</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.91</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.4452</v>
+        <v>-0.3717</v>
       </c>
       <c r="J396" t="n">
-        <v>-9.7944</v>
+        <v>-8.1774</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.18</v>
       </c>
       <c r="I397" t="n">
-        <v>0.4317</v>
+        <v>0.4923</v>
       </c>
       <c r="J397" t="n">
-        <v>9.497400000000001</v>
+        <v>10.8306</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>0.97</v>
       </c>
       <c r="I398" t="n">
-        <v>0.0145</v>
+        <v>-0.0216</v>
       </c>
       <c r="J398" t="n">
-        <v>0.319</v>
+        <v>-0.4752</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>0.79</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.3219</v>
+        <v>-0.2245</v>
       </c>
       <c r="J399" t="n">
-        <v>-7.0818</v>
+        <v>-4.939</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.58</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.6328</v>
+        <v>-0.4228</v>
       </c>
       <c r="J400" t="n">
-        <v>-13.9216</v>
+        <v>-9.301600000000001</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.46</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.7824</v>
+        <v>-0.5336</v>
       </c>
       <c r="J401" t="n">
-        <v>-17.2128</v>
+        <v>-11.7392</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.86</v>
       </c>
       <c r="I402" t="n">
-        <v>1.9221</v>
+        <v>1.6262</v>
       </c>
       <c r="J402" t="n">
-        <v>51.8967</v>
+        <v>43.9074</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3423</v>
+        <v>0.3489</v>
       </c>
       <c r="J403" t="n">
-        <v>9.242100000000001</v>
+        <v>9.420299999999999</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.03</v>
       </c>
       <c r="I404" t="n">
-        <v>0.0594</v>
+        <v>0.108</v>
       </c>
       <c r="J404" t="n">
-        <v>1.6038</v>
+        <v>2.916</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.7523</v>
+        <v>-0.7029</v>
       </c>
       <c r="J405" t="n">
-        <v>-20.3121</v>
+        <v>-18.9783</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.75</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.8222</v>
+        <v>-0.7788</v>
       </c>
       <c r="J406" t="n">
-        <v>-22.1994</v>
+        <v>-21.0276</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.08</v>
       </c>
       <c r="I407" t="n">
-        <v>0.2498</v>
+        <v>0.2521</v>
       </c>
       <c r="J407" t="n">
-        <v>6.7446</v>
+        <v>6.8067</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>0.88</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.1845</v>
+        <v>-0.1414</v>
       </c>
       <c r="J408" t="n">
-        <v>-4.9815</v>
+        <v>-3.8178</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>0.83</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.2873</v>
+        <v>-0.1915</v>
       </c>
       <c r="J409" t="n">
-        <v>-7.7571</v>
+        <v>-5.1705</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.8</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.3381</v>
+        <v>-0.2212</v>
       </c>
       <c r="J410" t="n">
-        <v>-9.1287</v>
+        <v>-5.9724</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.68</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.5147</v>
+        <v>-0.3371</v>
       </c>
       <c r="J411" t="n">
-        <v>-13.8969</v>
+        <v>-9.101699999999999</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.59</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4468</v>
+        <v>1.2856</v>
       </c>
       <c r="J412" t="n">
-        <v>37.6168</v>
+        <v>33.4256</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.23</v>
       </c>
       <c r="I413" t="n">
-        <v>0.6798</v>
+        <v>0.6563</v>
       </c>
       <c r="J413" t="n">
-        <v>17.6748</v>
+        <v>17.0638</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.11</v>
       </c>
       <c r="I414" t="n">
-        <v>0.345</v>
+        <v>0.3492</v>
       </c>
       <c r="J414" t="n">
-        <v>8.970000000000001</v>
+        <v>9.0792</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.89</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.472</v>
+        <v>-0.4071</v>
       </c>
       <c r="J415" t="n">
-        <v>-12.272</v>
+        <v>-10.5846</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.7</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.9341</v>
+        <v>-0.902</v>
       </c>
       <c r="J416" t="n">
-        <v>-24.2866</v>
+        <v>-23.452</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.11</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3004</v>
+        <v>0.3173</v>
       </c>
       <c r="J417" t="n">
-        <v>7.8104</v>
+        <v>8.2498</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.04</v>
       </c>
       <c r="I418" t="n">
-        <v>0.175</v>
+        <v>0.1581</v>
       </c>
       <c r="J418" t="n">
-        <v>4.55</v>
+        <v>4.1106</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.8</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.3381</v>
+        <v>-0.2212</v>
       </c>
       <c r="J419" t="n">
-        <v>-8.7906</v>
+        <v>-5.7512</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.68</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.5147</v>
+        <v>-0.3371</v>
       </c>
       <c r="J420" t="n">
-        <v>-13.3822</v>
+        <v>-8.7646</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.64</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.5684</v>
+        <v>-0.3748</v>
       </c>
       <c r="J421" t="n">
-        <v>-14.7784</v>
+        <v>-9.7448</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1617/event_1617_evp_summary.xlsx
+++ b/database/event/1617/event_1617_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0043</v>
+        <v>6.2863</v>
       </c>
       <c r="C2" t="n">
-        <v>5.6317</v>
+        <v>5.8962</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0726</v>
+        <v>2.2374</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0043</v>
+        <v>6.2863</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0764</v>
+        <v>2.0487</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9279</v>
+        <v>4.2376</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0764</v>
+        <v>2.0487</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1618</v>
+        <v>2.1015</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9279</v>
+        <v>4.2376</v>
       </c>
       <c r="K2" t="n">
         <v>128</v>
@@ -529,7 +529,7 @@
         <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>6.089700000000001</v>
+        <v>6.3391</v>
       </c>
       <c r="N2" t="n">
         <v>279</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2392</v>
+        <v>5.3897</v>
       </c>
       <c r="C3" t="n">
-        <v>4.9141</v>
+        <v>5.0552</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7272</v>
+        <v>1.8293</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2392</v>
+        <v>5.3897</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3724</v>
+        <v>1.3219</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8668</v>
+        <v>4.0678</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3724</v>
+        <v>1.3219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3724</v>
+        <v>1.3219</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8668</v>
+        <v>4.0678</v>
       </c>
       <c r="K3" t="n">
         <v>47</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2392</v>
+        <v>5.3897</v>
       </c>
       <c r="N3" t="n">
         <v>261</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0521</v>
+        <v>4.1984</v>
       </c>
       <c r="C4" t="n">
-        <v>3.8006</v>
+        <v>3.9379</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1913</v>
+        <v>1.287</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0521</v>
+        <v>4.1984</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2984</v>
+        <v>2.2177</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7538</v>
+        <v>1.9807</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2984</v>
+        <v>2.2177</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3929</v>
+        <v>2.2748</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7538</v>
+        <v>1.9807</v>
       </c>
       <c r="K4" t="n">
         <v>130</v>
@@ -621,7 +621,7 @@
         <v>157</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1467</v>
+        <v>4.2555</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.4761</v>
+        <v>3.8605</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2604</v>
+        <v>3.6209</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9313</v>
+        <v>1.1332</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4761</v>
+        <v>3.8605</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8238</v>
+        <v>1.7594</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6523</v>
+        <v>2.1011</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8238</v>
+        <v>1.7594</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8238</v>
+        <v>1.7594</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6523</v>
+        <v>2.1011</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>214</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4761</v>
+        <v>3.8605</v>
       </c>
       <c r="N5" t="n">
         <v>261</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.431</v>
+        <v>3.706</v>
       </c>
       <c r="C6" t="n">
-        <v>3.2181</v>
+        <v>3.476</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9109</v>
+        <v>1.0628</v>
       </c>
       <c r="E6" t="n">
-        <v>3.431</v>
+        <v>3.706</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7284</v>
+        <v>1.6488</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7026</v>
+        <v>2.0572</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7284</v>
+        <v>1.6488</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7284</v>
+        <v>1.6488</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7026</v>
+        <v>2.0572</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>214</v>
       </c>
       <c r="M6" t="n">
-        <v>3.431</v>
+        <v>3.706</v>
       </c>
       <c r="N6" t="n">
         <v>261</v>
@@ -722,311 +722,311 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>Happy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8202</v>
+        <v>2.8823</v>
       </c>
       <c r="C7" t="n">
-        <v>2.6452</v>
+        <v>2.7034</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6352</v>
+        <v>0.6879</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8202</v>
+        <v>2.8823</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1666</v>
+        <v>0.8761</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6536</v>
+        <v>2.0062</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1666</v>
+        <v>0.8761</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1666</v>
+        <v>0.8761</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6536</v>
+        <v>2.0062</v>
       </c>
       <c r="K7" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L7" t="n">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8202</v>
+        <v>2.8823</v>
       </c>
       <c r="N7" t="n">
-        <v>119</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5819</v>
+        <v>2.8012</v>
       </c>
       <c r="C8" t="n">
-        <v>2.4217</v>
+        <v>2.6274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5276</v>
+        <v>0.651</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5819</v>
+        <v>2.8012</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8929</v>
+        <v>2.0684</v>
       </c>
       <c r="G8" t="n">
-        <v>1.689</v>
+        <v>0.7328</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8929</v>
+        <v>2.0684</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8929</v>
+        <v>2.0684</v>
       </c>
       <c r="J8" t="n">
-        <v>1.689</v>
+        <v>0.7328</v>
       </c>
       <c r="K8" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L8" t="n">
-        <v>214</v>
+        <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5819</v>
+        <v>2.8012</v>
       </c>
       <c r="N8" t="n">
-        <v>261</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>kioShiMa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5097</v>
+        <v>2.5243</v>
       </c>
       <c r="C9" t="n">
-        <v>2.354</v>
+        <v>2.3677</v>
       </c>
       <c r="D9" t="n">
-        <v>0.495</v>
+        <v>0.5249</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5097</v>
+        <v>2.5243</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3607</v>
+        <v>1.3251</v>
       </c>
       <c r="G9" t="n">
-        <v>0.149</v>
+        <v>1.1992</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3607</v>
+        <v>1.3251</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4578</v>
+        <v>1.3251</v>
       </c>
       <c r="J9" t="n">
-        <v>0.149</v>
+        <v>1.1992</v>
       </c>
       <c r="K9" t="n">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="L9" t="n">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="M9" t="n">
-        <v>2.6068</v>
+        <v>2.5243</v>
       </c>
       <c r="N9" t="n">
-        <v>173</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>kioShiMa</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3137</v>
+        <v>2.4475</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1701</v>
+        <v>2.2956</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4065</v>
+        <v>0.4899</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3137</v>
+        <v>2.4475</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3428</v>
+        <v>2.3182</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9709</v>
+        <v>0.1293</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3428</v>
+        <v>2.349</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3428</v>
+        <v>2.4095</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9709</v>
+        <v>0.1293</v>
       </c>
       <c r="K10" t="n">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="L10" t="n">
-        <v>214</v>
+        <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>2.3137</v>
+        <v>2.5388</v>
       </c>
       <c r="N10" t="n">
-        <v>261</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.1377</v>
+        <v>2.0572</v>
       </c>
       <c r="C11" t="n">
-        <v>2.005</v>
+        <v>1.9295</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3271</v>
+        <v>0.3123</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1377</v>
+        <v>2.0572</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1377</v>
+        <v>2.3247</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0.2675</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1377</v>
+        <v>2.3632</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1377</v>
+        <v>2.4241</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.2675</v>
       </c>
       <c r="K11" t="n">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1377</v>
+        <v>2.1566</v>
       </c>
       <c r="N11" t="n">
-        <v>52</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0979</v>
+        <v>2.0127</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9677</v>
+        <v>1.8878</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3091</v>
+        <v>0.292</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0979</v>
+        <v>2.0127</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4226</v>
+        <v>2.0127</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3247</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4226</v>
+        <v>2.0127</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5222</v>
+        <v>2.0127</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3247</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="L12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1975</v>
+        <v>2.0127</v>
       </c>
       <c r="N12" t="n">
-        <v>173</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0233</v>
+        <v>1.9596</v>
       </c>
       <c r="C13" t="n">
-        <v>1.8977</v>
+        <v>1.838</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2754</v>
+        <v>0.2678</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0233</v>
+        <v>1.9596</v>
       </c>
       <c r="F13" t="n">
-        <v>2.925</v>
+        <v>-0.2347</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9016999999999999</v>
+        <v>2.1943</v>
       </c>
       <c r="H13" t="n">
-        <v>3.063</v>
+        <v>-0.2347</v>
       </c>
       <c r="I13" t="n">
-        <v>3.189</v>
+        <v>-0.2407</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9016999999999999</v>
+        <v>2.1943</v>
       </c>
       <c r="K13" t="n">
         <v>128</v>
@@ -1035,7 +1035,7 @@
         <v>151</v>
       </c>
       <c r="M13" t="n">
-        <v>2.2873</v>
+        <v>1.9536</v>
       </c>
       <c r="N13" t="n">
         <v>279</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0221</v>
+        <v>1.9121</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8966</v>
+        <v>1.7934</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2749</v>
+        <v>0.2462</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0221</v>
+        <v>1.9121</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3093</v>
+        <v>2.2314</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2872</v>
+        <v>-0.3193</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3093</v>
+        <v>2.2314</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3093</v>
+        <v>2.2314</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2872</v>
+        <v>-0.3193</v>
       </c>
       <c r="K14" t="n">
         <v>44</v>
@@ -1081,7 +1081,7 @@
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0221</v>
+        <v>1.9121</v>
       </c>
       <c r="N14" t="n">
         <v>94</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9217</v>
+        <v>1.8655</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8024</v>
+        <v>1.7497</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2295</v>
+        <v>0.225</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9217</v>
+        <v>1.8655</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2852</v>
+        <v>2.2586</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3635</v>
+        <v>-0.3931</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2852</v>
+        <v>2.2586</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2852</v>
+        <v>2.2586</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3635</v>
+        <v>-0.3931</v>
       </c>
       <c r="K15" t="n">
         <v>56</v>
@@ -1127,7 +1127,7 @@
         <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9217</v>
+        <v>1.8655</v>
       </c>
       <c r="N15" t="n">
         <v>115</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.845</v>
+        <v>1.7571</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7305</v>
+        <v>1.6481</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1949</v>
+        <v>0.1757</v>
       </c>
       <c r="E16" t="n">
-        <v>1.845</v>
+        <v>1.7571</v>
       </c>
       <c r="F16" t="n">
-        <v>1.845</v>
+        <v>2.6381</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.881</v>
       </c>
       <c r="H16" t="n">
-        <v>1.845</v>
+        <v>3.049</v>
       </c>
       <c r="I16" t="n">
-        <v>1.845</v>
+        <v>3.1276</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.881</v>
       </c>
       <c r="K16" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M16" t="n">
-        <v>1.845</v>
+        <v>2.2466</v>
       </c>
       <c r="N16" t="n">
-        <v>132</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7574</v>
+        <v>1.7444</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6483</v>
+        <v>1.6361</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1554</v>
+        <v>0.1699</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7574</v>
+        <v>1.7444</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2187</v>
+        <v>1.7444</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9761</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2187</v>
+        <v>1.7444</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2277</v>
+        <v>1.7444</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9761</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="L17" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7484</v>
+        <v>1.7444</v>
       </c>
       <c r="N17" t="n">
-        <v>279</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5894</v>
+        <v>1.6324</v>
       </c>
       <c r="C18" t="n">
-        <v>1.4908</v>
+        <v>1.5311</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0795</v>
+        <v>0.1189</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5894</v>
+        <v>1.6324</v>
       </c>
       <c r="F18" t="n">
-        <v>1.052</v>
+        <v>1.0133</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5374</v>
+        <v>0.6191</v>
       </c>
       <c r="H18" t="n">
-        <v>1.052</v>
+        <v>1.0133</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0953</v>
+        <v>1.0394</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5374</v>
+        <v>0.6191</v>
       </c>
       <c r="K18" t="n">
         <v>130</v>
@@ -1265,7 +1265,7 @@
         <v>157</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6327</v>
+        <v>1.6585</v>
       </c>
       <c r="N18" t="n">
         <v>287</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>fox</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5869</v>
+        <v>1.579</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4884</v>
+        <v>1.481</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0784</v>
+        <v>0.0946</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5869</v>
+        <v>1.579</v>
       </c>
       <c r="F19" t="n">
-        <v>3.165</v>
+        <v>1.6472</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5781</v>
+        <v>-0.0682</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5901</v>
+        <v>1.6472</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7377</v>
+        <v>1.6896</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5781</v>
+        <v>-0.0682</v>
       </c>
       <c r="K19" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="L19" t="n">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1596</v>
+        <v>1.6214</v>
       </c>
       <c r="N19" t="n">
-        <v>194</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fox</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4303</v>
+        <v>1.2619</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3415</v>
+        <v>1.1836</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0077</v>
+        <v>-0.0498</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4303</v>
+        <v>1.2619</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6564</v>
+        <v>2.8874</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2261</v>
+        <v>-1.6255</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6564</v>
+        <v>3.5948</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7245</v>
+        <v>3.6874</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2261</v>
+        <v>-1.6255</v>
       </c>
       <c r="K20" t="n">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="L20" t="n">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4984</v>
+        <v>2.0619</v>
       </c>
       <c r="N20" t="n">
-        <v>287</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1848</v>
+        <v>1.0709</v>
       </c>
       <c r="C21" t="n">
-        <v>1.1113</v>
+        <v>1.0044</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1031</v>
+        <v>-0.1367</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1848</v>
+        <v>1.0709</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1848</v>
+        <v>1.7366</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.6657</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1848</v>
+        <v>1.7366</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1848</v>
+        <v>1.7813</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.6657</v>
       </c>
       <c r="K21" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1848</v>
+        <v>1.1156</v>
       </c>
       <c r="N21" t="n">
-        <v>99</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1021</v>
+        <v>1.0428</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0337</v>
+        <v>0.9781</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1405</v>
+        <v>-0.1495</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1021</v>
+        <v>1.0428</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1021</v>
+        <v>1.0428</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1021</v>
+        <v>1.0428</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1021</v>
+        <v>1.0428</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1021</v>
+        <v>1.0428</v>
       </c>
       <c r="N22" t="n">
         <v>46</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.069</v>
+        <v>1.0427</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0027</v>
+        <v>0.978</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1554</v>
+        <v>-0.1495</v>
       </c>
       <c r="E23" t="n">
-        <v>1.069</v>
+        <v>1.0427</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7539</v>
+        <v>1.0427</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6849</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7539</v>
+        <v>1.0427</v>
       </c>
       <c r="I23" t="n">
-        <v>1.826</v>
+        <v>1.0427</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6849</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L23" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1411</v>
+        <v>1.0427</v>
       </c>
       <c r="N23" t="n">
-        <v>194</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9283</v>
+        <v>0.8781</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8707</v>
+        <v>0.8236</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2189</v>
+        <v>-0.2245</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9283</v>
+        <v>0.8781</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9283</v>
+        <v>0.8781</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9283</v>
+        <v>0.8781</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9283</v>
+        <v>0.8781</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9283</v>
+        <v>0.8781</v>
       </c>
       <c r="N24" t="n">
         <v>132</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8663</v>
+        <v>0.8694</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8125</v>
+        <v>0.8154</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2469</v>
+        <v>-0.2284</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8663</v>
+        <v>0.8694</v>
       </c>
       <c r="F25" t="n">
-        <v>1.1143</v>
+        <v>0.2181</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.248</v>
+        <v>0.6513</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1143</v>
+        <v>0.2181</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1143</v>
+        <v>0.2237</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.248</v>
+        <v>0.6513</v>
       </c>
       <c r="K25" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="L25" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8663000000000001</v>
+        <v>0.875</v>
       </c>
       <c r="N25" t="n">
-        <v>119</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7922</v>
+        <v>0.8198</v>
       </c>
       <c r="C26" t="n">
-        <v>0.743</v>
+        <v>0.7689</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2804</v>
+        <v>-0.251</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7922</v>
+        <v>0.8198</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2679</v>
+        <v>1.0858</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5243</v>
+        <v>-0.266</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2679</v>
+        <v>1.0858</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2789</v>
+        <v>1.0858</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5243</v>
+        <v>-0.266</v>
       </c>
       <c r="K26" t="n">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="L26" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8031999999999999</v>
+        <v>0.8198000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>194</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7843</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7356</v>
+        <v>0.72</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2839</v>
+        <v>-0.2748</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7843</v>
+        <v>0.7675999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1082</v>
+        <v>1.1198</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3239</v>
+        <v>-0.3522</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1082</v>
+        <v>1.1198</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1082</v>
+        <v>1.1198</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3239</v>
+        <v>-0.3522</v>
       </c>
       <c r="K27" t="n">
         <v>44</v>
@@ -1679,7 +1679,7 @@
         <v>50</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7843</v>
+        <v>0.7675999999999998</v>
       </c>
       <c r="N27" t="n">
         <v>94</v>
@@ -1688,78 +1688,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6408</v>
+        <v>0.5831</v>
       </c>
       <c r="C28" t="n">
-        <v>0.601</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3487</v>
+        <v>-0.3588</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6408</v>
+        <v>0.5831</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6408</v>
+        <v>-0.7187</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.3018</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6408</v>
+        <v>-0.7187</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6408</v>
+        <v>-0.7372</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1.3018</v>
       </c>
       <c r="K28" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6408</v>
+        <v>0.5646000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>133</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6276</v>
+        <v>0.5652</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5887</v>
+        <v>0.5301</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3547</v>
+        <v>-0.3669</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6276</v>
+        <v>0.5652</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6276</v>
+        <v>0.5652</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6276</v>
+        <v>0.5652</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6276</v>
+        <v>0.5652</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.6276</v>
+        <v>0.5652</v>
       </c>
       <c r="N29" t="n">
         <v>133</v>
@@ -1780,369 +1780,369 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5158</v>
+        <v>0.553</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4838</v>
+        <v>0.5187</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4052</v>
+        <v>-0.3725</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5158</v>
+        <v>0.553</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5158</v>
+        <v>0.553</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5158</v>
+        <v>0.553</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5158</v>
+        <v>0.553</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.5158</v>
+        <v>0.553</v>
       </c>
       <c r="N30" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4514</v>
+        <v>0.5113</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4234</v>
+        <v>0.4796</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4342</v>
+        <v>-0.3914</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4514</v>
+        <v>0.5113</v>
       </c>
       <c r="F31" t="n">
-        <v>0.31</v>
+        <v>0.5113</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1414</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.31</v>
+        <v>0.5113</v>
       </c>
       <c r="I31" t="n">
-        <v>0.31</v>
+        <v>0.5113</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1414</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="L31" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.4514</v>
+        <v>0.5113</v>
       </c>
       <c r="N31" t="n">
-        <v>94</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4353</v>
+        <v>0.4649</v>
       </c>
       <c r="C32" t="n">
-        <v>0.4083</v>
+        <v>0.436</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4415</v>
+        <v>-0.4126</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4353</v>
+        <v>0.4649</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4353</v>
+        <v>0.1417</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.3232</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4353</v>
+        <v>0.1417</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4353</v>
+        <v>0.1454</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.3232</v>
       </c>
       <c r="K32" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4353</v>
+        <v>0.4686</v>
       </c>
       <c r="N32" t="n">
-        <v>99</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4222</v>
+        <v>0.4643</v>
       </c>
       <c r="C33" t="n">
-        <v>0.396</v>
+        <v>0.4355</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4474</v>
+        <v>-0.4128</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4222</v>
+        <v>0.4643</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4222</v>
+        <v>0.3435</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.1208</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4222</v>
+        <v>0.3435</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4222</v>
+        <v>0.3435</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.1208</v>
       </c>
       <c r="K33" t="n">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4222</v>
+        <v>0.4643</v>
       </c>
       <c r="N33" t="n">
-        <v>132</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3907</v>
+        <v>0.3787</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3665</v>
+        <v>0.3552</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4616</v>
+        <v>-0.4518</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3907</v>
+        <v>0.3787</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5012</v>
+        <v>0.3787</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.1105</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5012</v>
+        <v>0.3787</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5012</v>
+        <v>0.3787</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.1105</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="L34" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3907</v>
+        <v>0.3787</v>
       </c>
       <c r="N34" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.379</v>
+        <v>0.3458</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3555</v>
+        <v>0.3243</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4669</v>
+        <v>-0.4668</v>
       </c>
       <c r="E35" t="n">
-        <v>0.379</v>
+        <v>0.3458</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1257</v>
+        <v>0.468</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2533</v>
+        <v>-0.1222</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1257</v>
+        <v>0.468</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1309</v>
+        <v>0.468</v>
       </c>
       <c r="J35" t="n">
-        <v>0.2533</v>
+        <v>-0.1222</v>
       </c>
       <c r="K35" t="n">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="L35" t="n">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3842</v>
+        <v>0.3458</v>
       </c>
       <c r="N35" t="n">
-        <v>194</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3722</v>
+        <v>0.3359</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3491</v>
+        <v>0.3151</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.47</v>
+        <v>-0.4713</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3722</v>
+        <v>0.3359</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3722</v>
+        <v>0.3359</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3722</v>
+        <v>0.3359</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3722</v>
+        <v>0.3359</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3722</v>
+        <v>0.3359</v>
       </c>
       <c r="N36" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3637</v>
+        <v>0.3232</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3411</v>
+        <v>0.3031</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4738</v>
+        <v>-0.4771</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3637</v>
+        <v>0.3232</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7542</v>
+        <v>0.297</v>
       </c>
       <c r="G37" t="n">
-        <v>1.1179</v>
+        <v>0.0262</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7542</v>
+        <v>0.297</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7852</v>
+        <v>0.3047</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1179</v>
+        <v>0.0262</v>
       </c>
       <c r="K37" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="L37" t="n">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3326999999999999</v>
+        <v>0.3309</v>
       </c>
       <c r="N37" t="n">
-        <v>279</v>
+        <v>194</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.2986</v>
+        <v>0.323</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2801</v>
+        <v>0.303</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.5032</v>
+        <v>-0.4772</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2986</v>
+        <v>0.323</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4727</v>
+        <v>0.493</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.1741</v>
+        <v>-0.17</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4727</v>
+        <v>0.493</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4727</v>
+        <v>0.493</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.1741</v>
+        <v>-0.17</v>
       </c>
       <c r="K38" t="n">
         <v>44</v>
@@ -2185,7 +2185,7 @@
         <v>50</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2986</v>
+        <v>0.323</v>
       </c>
       <c r="N38" t="n">
         <v>94</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.2906</v>
+        <v>0.268</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2726</v>
+        <v>0.2514</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5068</v>
+        <v>-0.5022</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2906</v>
+        <v>0.268</v>
       </c>
       <c r="F39" t="n">
-        <v>0.595</v>
+        <v>0.604</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.3044</v>
+        <v>-0.336</v>
       </c>
       <c r="H39" t="n">
-        <v>0.595</v>
+        <v>0.604</v>
       </c>
       <c r="I39" t="n">
-        <v>0.595</v>
+        <v>0.604</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.3044</v>
+        <v>-0.336</v>
       </c>
       <c r="K39" t="n">
         <v>44</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="M39" t="n">
-        <v>0.2906</v>
+        <v>0.268</v>
       </c>
       <c r="N39" t="n">
         <v>94</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2634</v>
+        <v>0.2565</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2471</v>
+        <v>0.2406</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5191</v>
+        <v>-0.5074</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2634</v>
+        <v>0.2565</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2458</v>
+        <v>0.3944</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0176</v>
+        <v>-0.1379</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2458</v>
+        <v>0.3944</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2559</v>
+        <v>0.4046</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0176</v>
+        <v>-0.1379</v>
       </c>
       <c r="K40" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L40" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2735</v>
+        <v>0.2667</v>
       </c>
       <c r="N40" t="n">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.219</v>
+        <v>0.2554</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2054</v>
+        <v>0.2396</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.5391</v>
+        <v>-0.5079</v>
       </c>
       <c r="E41" t="n">
-        <v>0.219</v>
+        <v>0.2554</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3575</v>
+        <v>0.2554</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1385</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3575</v>
+        <v>0.2554</v>
       </c>
       <c r="I41" t="n">
-        <v>0.3722</v>
+        <v>0.2554</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1385</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L41" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2337</v>
+        <v>0.2554</v>
       </c>
       <c r="N41" t="n">
-        <v>173</v>
+        <v>106</v>
       </c>
     </row>
     <row r="42">
@@ -2336,31 +2336,31 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.1717</v>
+        <v>0.0882</v>
       </c>
       <c r="C42" t="n">
-        <v>0.161</v>
+        <v>0.0827</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5605</v>
+        <v>-0.5841</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1717</v>
+        <v>0.0882</v>
       </c>
       <c r="F42" t="n">
-        <v>1.5214</v>
+        <v>1.4563</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.3497</v>
+        <v>-1.3681</v>
       </c>
       <c r="H42" t="n">
-        <v>1.5214</v>
+        <v>1.4563</v>
       </c>
       <c r="I42" t="n">
-        <v>1.584</v>
+        <v>1.4938</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.3497</v>
+        <v>-1.3681</v>
       </c>
       <c r="K42" t="n">
         <v>130</v>
@@ -2369,7 +2369,7 @@
         <v>157</v>
       </c>
       <c r="M42" t="n">
-        <v>0.2343000000000002</v>
+        <v>0.1256999999999999</v>
       </c>
       <c r="N42" t="n">
         <v>287</v>
@@ -2378,78 +2378,78 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1079</v>
+        <v>0.0223</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1012</v>
+        <v>0.0209</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.5893</v>
+        <v>-0.6141</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1079</v>
+        <v>0.0223</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1079</v>
+        <v>0.0223</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1079</v>
+        <v>0.0223</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1079</v>
+        <v>0.0223</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.1079</v>
+        <v>0.0223</v>
       </c>
       <c r="N43" t="n">
-        <v>133</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0521</v>
+        <v>0.0066</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0489</v>
+        <v>0.0062</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6145</v>
+        <v>-0.6212</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0521</v>
+        <v>0.0066</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0521</v>
+        <v>0.0066</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0521</v>
+        <v>0.0066</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0521</v>
+        <v>0.0066</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0521</v>
+        <v>0.0066</v>
       </c>
       <c r="N44" t="n">
         <v>61</v>
@@ -2470,93 +2470,93 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.0334</v>
+        <v>-0.0032</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0313</v>
+        <v>-0.003</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6229</v>
+        <v>-0.6257</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0334</v>
+        <v>-0.0032</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0334</v>
+        <v>-0.1866</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.1834</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0334</v>
+        <v>-0.1866</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0334</v>
+        <v>-0.1866</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.1834</v>
       </c>
       <c r="K45" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M45" t="n">
-        <v>0.0334</v>
+        <v>-0.003199999999999981</v>
       </c>
       <c r="N45" t="n">
-        <v>61</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.001</v>
+        <v>-0.0262</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0009</v>
+        <v>-0.0246</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6385</v>
+        <v>-0.6361</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.001</v>
+        <v>-0.0262</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.2001</v>
+        <v>-0.0262</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1991</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.2001</v>
+        <v>-0.0262</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2001</v>
+        <v>-0.0262</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1991</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="L46" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.001000000000000001</v>
+        <v>-0.0262</v>
       </c>
       <c r="N46" t="n">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0227</v>
+        <v>-0.0362</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.0213</v>
+        <v>-0.034</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6483</v>
+        <v>-0.6407</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0227</v>
+        <v>-0.0362</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0227</v>
+        <v>-0.0362</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0227</v>
+        <v>-0.0362</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0227</v>
+        <v>-0.0362</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0227</v>
+        <v>-0.0362</v>
       </c>
       <c r="N47" t="n">
         <v>55</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0437</v>
+        <v>-0.0618</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.041</v>
+        <v>-0.058</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6577</v>
+        <v>-0.6523</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0437</v>
+        <v>-0.0618</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0437</v>
+        <v>-0.0618</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0437</v>
+        <v>-0.0618</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0437</v>
+        <v>-0.0618</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0437</v>
+        <v>-0.0618</v>
       </c>
       <c r="N48" t="n">
         <v>55</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.05</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0469</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6606</v>
+        <v>-0.6636</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.05</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.05</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.05</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.05</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.05</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="N49" t="n">
         <v>106</v>
@@ -2700,231 +2700,231 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1035</v>
+        <v>-0.1323</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.1241</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6847</v>
+        <v>-0.6844</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1035</v>
+        <v>-0.1323</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.1035</v>
+        <v>0.8677</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.1035</v>
+        <v>0.8677</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1035</v>
+        <v>0.8901</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K50" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1035</v>
+        <v>-0.1099</v>
       </c>
       <c r="N50" t="n">
-        <v>106</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1145</v>
+        <v>-0.1609</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1074</v>
+        <v>-0.1509</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6897</v>
+        <v>-0.6974</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1145</v>
+        <v>-0.1609</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8855</v>
+        <v>-0.1609</v>
       </c>
       <c r="G51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8855</v>
+        <v>-0.1609</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9219000000000001</v>
+        <v>-0.1609</v>
       </c>
       <c r="J51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="L51" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.07809999999999995</v>
+        <v>-0.1609</v>
       </c>
       <c r="N51" t="n">
-        <v>173</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1422</v>
+        <v>-0.1715</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1334</v>
+        <v>-0.1609</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7022</v>
+        <v>-0.7023</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1422</v>
+        <v>-0.1715</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1422</v>
+        <v>-0.1715</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1422</v>
+        <v>-0.1715</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1422</v>
+        <v>-0.1715</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1422</v>
+        <v>-0.1715</v>
       </c>
       <c r="N52" t="n">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2411</v>
+        <v>-0.2722</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2261</v>
+        <v>-0.2553</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7469</v>
+        <v>-0.7481</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2411</v>
+        <v>-0.2722</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2411</v>
+        <v>-0.2722</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2411</v>
+        <v>-0.2722</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2411</v>
+        <v>-0.2722</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2411</v>
+        <v>-0.2722</v>
       </c>
       <c r="N53" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2541</v>
+        <v>-0.2728</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2383</v>
+        <v>-0.2559</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7527</v>
+        <v>-0.7484</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2541</v>
+        <v>-0.2728</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2541</v>
+        <v>-0.2728</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2541</v>
+        <v>-0.2728</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2541</v>
+        <v>-0.2728</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2541</v>
+        <v>-0.2728</v>
       </c>
       <c r="N54" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55">
@@ -2934,31 +2934,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2802</v>
+        <v>-0.2908</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2628</v>
+        <v>-0.2728</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7645</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2802</v>
+        <v>-0.2908</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3571</v>
+        <v>0.3663</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.6373</v>
+        <v>-0.6571</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3571</v>
+        <v>0.3663</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3571</v>
+        <v>0.3663</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.6373</v>
+        <v>-0.6571</v>
       </c>
       <c r="K55" t="n">
         <v>57</v>
@@ -2967,7 +2967,7 @@
         <v>62</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2802</v>
+        <v>-0.2908</v>
       </c>
       <c r="N55" t="n">
         <v>119</v>
@@ -2976,93 +2976,93 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.3265</v>
+        <v>-0.2936</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.3062</v>
+        <v>-0.2754</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7854</v>
+        <v>-0.7579</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.3265</v>
+        <v>-0.2936</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.3265</v>
+        <v>-0.9149</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>0.6213</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.3265</v>
+        <v>-0.9149</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3265</v>
+        <v>-0.9149</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.6213</v>
       </c>
       <c r="K56" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.3265</v>
+        <v>-0.2936000000000001</v>
       </c>
       <c r="N56" t="n">
-        <v>46</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4105</v>
+        <v>-0.3576</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.385</v>
+        <v>-0.3354</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.8233</v>
+        <v>-0.787</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4105</v>
+        <v>-0.3576</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.9663</v>
+        <v>-0.3576</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5558</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.9663</v>
+        <v>-0.3576</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.9663</v>
+        <v>-0.3576</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5558</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L57" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4105000000000001</v>
+        <v>-0.3576</v>
       </c>
       <c r="N57" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58">
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4686</v>
+        <v>-0.5048</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.4395</v>
+        <v>-0.4735</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.8496</v>
+        <v>-0.854</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4686</v>
+        <v>-0.5048</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4686</v>
+        <v>-0.5048</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4686</v>
+        <v>-0.5048</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4686</v>
+        <v>-0.5048</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4686</v>
+        <v>-0.5048</v>
       </c>
       <c r="N58" t="n">
         <v>52</v>
@@ -3118,28 +3118,28 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4995</v>
+        <v>-0.5151</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.4685</v>
+        <v>-0.4831</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.8635</v>
+        <v>-0.8587</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4995</v>
+        <v>-0.5151</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4995</v>
+        <v>-0.5151</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.4995</v>
+        <v>-0.5151</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4995</v>
+        <v>-0.5151</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4995</v>
+        <v>-0.5151</v>
       </c>
       <c r="N59" t="n">
         <v>99</v>
@@ -3164,28 +3164,28 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5414</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.4817</v>
+        <v>-0.5078</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.8699</v>
+        <v>-0.8707</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5414</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5414</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5414</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5414</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5414</v>
       </c>
       <c r="N60" t="n">
         <v>55</v>
@@ -3210,28 +3210,28 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5183</v>
+        <v>-0.548</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4861</v>
+        <v>-0.514</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.872</v>
+        <v>-0.8737</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5183</v>
+        <v>-0.548</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5183</v>
+        <v>-0.548</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5183</v>
+        <v>-0.548</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5183</v>
+        <v>-0.548</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5183</v>
+        <v>-0.548</v>
       </c>
       <c r="N61" t="n">
         <v>55</v>
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.547</v>
+        <v>-0.5766</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.5131</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.885</v>
+        <v>-0.8867</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.547</v>
+        <v>-0.5766</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.547</v>
+        <v>-0.5766</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.547</v>
+        <v>-0.5766</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.547</v>
+        <v>-0.5766</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.547</v>
+        <v>-0.5766</v>
       </c>
       <c r="N62" t="n">
         <v>61</v>
@@ -3298,93 +3298,93 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.6302</v>
+        <v>-0.6481</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.9413</v>
+        <v>-0.9388</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6771</v>
+        <v>-0.7295</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.6351</v>
+        <v>-0.6842</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9437</v>
+        <v>-0.9563</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6771</v>
+        <v>-0.7295</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6771</v>
+        <v>-0.7295</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6771</v>
+        <v>-0.7295</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6771</v>
+        <v>-0.7295</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6771</v>
+        <v>-0.7295</v>
       </c>
       <c r="N64" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
     <row r="65">
@@ -3394,31 +3394,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7565</v>
+        <v>-0.7511</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.7096</v>
+        <v>-0.7045</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9795</v>
+        <v>-0.9661</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7565</v>
+        <v>-0.7511</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8111</v>
+        <v>-0.8218</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0546</v>
+        <v>0.0707</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8111</v>
+        <v>-0.8218</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8445</v>
+        <v>-0.843</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0546</v>
+        <v>0.0707</v>
       </c>
       <c r="K65" t="n">
         <v>130</v>
@@ -3427,7 +3427,7 @@
         <v>157</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7899</v>
+        <v>-0.7723</v>
       </c>
       <c r="N65" t="n">
         <v>287</v>
@@ -3436,78 +3436,78 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DavCost</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8098</v>
+        <v>-0.8025</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.7595</v>
+        <v>-0.7527</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.0036</v>
+        <v>-0.9895</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8098</v>
+        <v>-0.8025</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8098</v>
+        <v>-0.8017</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-0.0008</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8098</v>
+        <v>-0.8017</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8098</v>
+        <v>-0.8017</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-0.0008</v>
       </c>
       <c r="K66" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8098</v>
+        <v>-0.8025</v>
       </c>
       <c r="N66" t="n">
-        <v>46</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>DavCost</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8165</v>
+        <v>-0.833</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.7658</v>
+        <v>-0.7813</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.0066</v>
+        <v>-1.0034</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8165</v>
+        <v>-0.833</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8165</v>
+        <v>-0.833</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8165</v>
+        <v>-0.833</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.8165</v>
+        <v>-0.833</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8165</v>
+        <v>-0.833</v>
       </c>
       <c r="N67" t="n">
         <v>46</v>
@@ -3528,93 +3528,93 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8435</v>
+        <v>-0.8369</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.7912</v>
+        <v>-0.785</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0188</v>
+        <v>-1.0052</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8435</v>
+        <v>-0.8369</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8435</v>
+        <v>-0.8369</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8435</v>
+        <v>-0.8369</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8435</v>
+        <v>-0.8369</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8435</v>
+        <v>-0.8369</v>
       </c>
       <c r="N68" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.8671</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.8571</v>
+        <v>-0.8133</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0505</v>
+        <v>-1.0189</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.8671</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9204</v>
+        <v>-0.8671</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0066</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9204</v>
+        <v>-0.8671</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.9204</v>
+        <v>-0.8671</v>
       </c>
       <c r="J69" t="n">
-        <v>0.0066</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="L69" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.9137999999999999</v>
+        <v>-0.8671</v>
       </c>
       <c r="N69" t="n">
-        <v>115</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70">
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.968</v>
+        <v>-1.0033</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.9079</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.075</v>
+        <v>-1.0809</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.968</v>
+        <v>-1.0033</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.968</v>
+        <v>-1.0033</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.968</v>
+        <v>-1.0033</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.968</v>
+        <v>-1.0033</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.968</v>
+        <v>-1.0033</v>
       </c>
       <c r="N70" t="n">
         <v>133</v>
@@ -3670,31 +3670,31 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0033</v>
+        <v>-1.0034</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.9411</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.091</v>
+        <v>-1.081</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0033</v>
+        <v>-1.0034</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.1145</v>
+        <v>-0.0997</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.8888</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.1145</v>
+        <v>-0.0997</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1145</v>
+        <v>-0.0997</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.8888</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="K71" t="n">
         <v>56</v>
@@ -3703,7 +3703,7 @@
         <v>59</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.0033</v>
+        <v>-1.0034</v>
       </c>
       <c r="N71" t="n">
         <v>115</v>
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0151</v>
+        <v>-1.0446</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-0.9798</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0963</v>
+        <v>-1.0997</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0151</v>
+        <v>-1.0446</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.0151</v>
+        <v>-1.0446</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0151</v>
+        <v>-1.0446</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.0151</v>
+        <v>-1.0446</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.0151</v>
+        <v>-1.0446</v>
       </c>
       <c r="N72" t="n">
         <v>106</v>
@@ -3762,31 +3762,31 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.1369</v>
+        <v>-1.0454</v>
       </c>
       <c r="C73" t="n">
-        <v>-1.0663</v>
+        <v>-0.9805</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1513</v>
+        <v>-1.1001</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.1369</v>
+        <v>-1.0454</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4312</v>
+        <v>-0.4415</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.7057</v>
+        <v>-0.6039</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.4312</v>
+        <v>-0.4415</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.4489</v>
+        <v>-0.4529</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.7057</v>
+        <v>-0.6039</v>
       </c>
       <c r="K73" t="n">
         <v>128</v>
@@ -3795,7 +3795,7 @@
         <v>151</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.1546</v>
+        <v>-1.0568</v>
       </c>
       <c r="N73" t="n">
         <v>279</v>
@@ -3804,93 +3804,93 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1922</v>
+        <v>-1.1836</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.1182</v>
+        <v>-1.1101</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1762</v>
+        <v>-1.163</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1922</v>
+        <v>-1.1836</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1922</v>
+        <v>-1.1836</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.1922</v>
+        <v>-1.1836</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1922</v>
+        <v>-1.1836</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.1922</v>
+        <v>-1.1836</v>
       </c>
       <c r="N74" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1967</v>
+        <v>-1.1946</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.1224</v>
+        <v>-1.1205</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1783</v>
+        <v>-1.168</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1967</v>
+        <v>-1.1946</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.1967</v>
+        <v>-1.1946</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.1967</v>
+        <v>-1.1946</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1967</v>
+        <v>-1.1946</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1967</v>
+        <v>-1.1946</v>
       </c>
       <c r="N75" t="n">
-        <v>106</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76">
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3538</v>
+        <v>-1.2826</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.2698</v>
+        <v>-1.203</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2492</v>
+        <v>-1.2081</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3538</v>
+        <v>-1.2826</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.212</v>
+        <v>-1.1322</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.1418</v>
+        <v>-0.1504</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.212</v>
+        <v>-1.1322</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.212</v>
+        <v>-1.1322</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.1418</v>
+        <v>-0.1504</v>
       </c>
       <c r="K76" t="n">
         <v>57</v>
@@ -3933,7 +3933,7 @@
         <v>62</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.3538</v>
+        <v>-1.2826</v>
       </c>
       <c r="N76" t="n">
         <v>119</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5514</v>
+        <v>-1.5552</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.4551</v>
+        <v>-1.4587</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3384</v>
+        <v>-1.3322</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5514</v>
+        <v>-1.5552</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.5514</v>
+        <v>-1.5552</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.5514</v>
+        <v>-1.5552</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.5514</v>
+        <v>-1.5552</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.5514</v>
+        <v>-1.5552</v>
       </c>
       <c r="N77" t="n">
         <v>99</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.597</v>
+        <v>-1.5621</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.4979</v>
+        <v>-1.4652</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.359</v>
+        <v>-1.3353</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.597</v>
+        <v>-1.5621</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.597</v>
+        <v>-1.5621</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.597</v>
+        <v>-1.5621</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.597</v>
+        <v>-1.5621</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.597</v>
+        <v>-1.5621</v>
       </c>
       <c r="N78" t="n">
         <v>132</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.8411</v>
+        <v>-1.81</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.7268</v>
+        <v>-1.6977</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4692</v>
+        <v>-1.4482</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.8411</v>
+        <v>-1.81</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.8411</v>
+        <v>-1.81</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.8411</v>
+        <v>-1.81</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.8411</v>
+        <v>-1.81</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.8411</v>
+        <v>-1.81</v>
       </c>
       <c r="N79" t="n">
         <v>132</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.1265</v>
+        <v>-2.0546</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.9945</v>
+        <v>-1.9271</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.598</v>
+        <v>-1.5595</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.1265</v>
+        <v>-2.0546</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.1265</v>
+        <v>-2.0546</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.1265</v>
+        <v>-2.0546</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.1265</v>
+        <v>-2.0546</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.1265</v>
+        <v>-2.0546</v>
       </c>
       <c r="N80" t="n">
         <v>133</v>
@@ -4130,31 +4130,31 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.8168</v>
+        <v>-2.7567</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.642</v>
+        <v>-2.5856</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.9097</v>
+        <v>-1.8791</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.8168</v>
+        <v>-2.7567</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.8301</v>
+        <v>-1.7567</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.9867</v>
+        <v>-1</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.8301</v>
+        <v>-1.7567</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.9054</v>
+        <v>-1.802</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.9867</v>
+        <v>-1</v>
       </c>
       <c r="K81" t="n">
         <v>105</v>
@@ -4163,7 +4163,7 @@
         <v>68</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.8921</v>
+        <v>-2.802</v>
       </c>
       <c r="N81" t="n">
         <v>173</v>
@@ -4269,10 +4269,10 @@
         <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2184</v>
+        <v>1.2191</v>
       </c>
       <c r="J2" t="n">
-        <v>36.552</v>
+        <v>36.573</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.83</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4999</v>
+        <v>-0.4878</v>
       </c>
       <c r="J3" t="n">
-        <v>-14.997</v>
+        <v>-14.634</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.75</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7045</v>
+        <v>-0.6691</v>
       </c>
       <c r="J4" t="n">
-        <v>-21.135</v>
+        <v>-20.073</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.66</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-0.8631</v>
       </c>
       <c r="J5" t="n">
-        <v>-27.837</v>
+        <v>-25.893</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0496</v>
+        <v>-0.9675</v>
       </c>
       <c r="J6" t="n">
-        <v>-31.488</v>
+        <v>-29.025</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>26.265</v>
+        <v>25.086</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7796</v>
+        <v>0.7504</v>
       </c>
       <c r="J8" t="n">
-        <v>23.388</v>
+        <v>22.512</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0463</v>
+        <v>-0.0506</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.389</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0463</v>
+        <v>-0.0506</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.389</v>
+        <v>-1.518</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3753</v>
+        <v>-0.3835</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.259</v>
+        <v>-11.505</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>2.01</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7053</v>
+        <v>1.8453</v>
       </c>
       <c r="J12" t="n">
-        <v>35.8113</v>
+        <v>38.7513</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.51</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1192</v>
+        <v>1.1166</v>
       </c>
       <c r="J13" t="n">
-        <v>23.5032</v>
+        <v>23.4486</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0451</v>
+        <v>1.0092</v>
       </c>
       <c r="J14" t="n">
-        <v>21.9471</v>
+        <v>21.1932</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0057</v>
+        <v>0.0384</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1197</v>
+        <v>0.8064</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4438</v>
+        <v>-0.4085</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.319800000000001</v>
+        <v>-8.5785</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1907</v>
+        <v>0.1557</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0047</v>
+        <v>3.2697</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2703</v>
+        <v>-0.2928</v>
       </c>
       <c r="J18" t="n">
-        <v>-5.6763</v>
+        <v>-6.1488</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.55</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.427</v>
+        <v>-0.4431</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.967000000000001</v>
+        <v>-9.305099999999999</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4739</v>
+        <v>-0.4871</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.9519</v>
+        <v>-10.2291</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5222</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.7436</v>
+        <v>-10.9662</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3858</v>
+        <v>0.382</v>
       </c>
       <c r="J22" t="n">
-        <v>7.3302</v>
+        <v>7.258</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3012</v>
+        <v>-0.3223</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.7228</v>
+        <v>-6.1237</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3284</v>
+        <v>-0.3486</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.2396</v>
+        <v>-6.6234</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4757</v>
+        <v>-0.4885</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.0383</v>
+        <v>-9.281499999999999</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.34</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6264</v>
+        <v>-0.6283</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.9016</v>
+        <v>-11.9377</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>2.03</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4491</v>
+        <v>1.5793</v>
       </c>
       <c r="J27" t="n">
-        <v>27.5329</v>
+        <v>30.0067</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.98</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3925</v>
+        <v>1.5203</v>
       </c>
       <c r="J28" t="n">
-        <v>26.4575</v>
+        <v>28.8857</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.473</v>
+        <v>0.5298</v>
       </c>
       <c r="J29" t="n">
-        <v>8.987</v>
+        <v>10.0662</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3888</v>
+        <v>-0.3568</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.3872</v>
+        <v>-6.7792</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6389</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.1391</v>
+        <v>-11.1188</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>0.84</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1024</v>
+        <v>-0.137</v>
       </c>
       <c r="J32" t="n">
-        <v>-2.2528</v>
+        <v>-3.014</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>0.61</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3553</v>
+        <v>-0.378</v>
       </c>
       <c r="J33" t="n">
-        <v>-7.8166</v>
+        <v>-8.316000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>0.57</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.393</v>
+        <v>-0.4137</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.646000000000001</v>
+        <v>-9.1014</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.54</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4188</v>
+        <v>-0.4383</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.2136</v>
+        <v>-9.6426</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.19</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7567</v>
+        <v>-0.7489</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.6474</v>
+        <v>-16.4758</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.68</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0459</v>
+        <v>1.1553</v>
       </c>
       <c r="J37" t="n">
-        <v>23.0098</v>
+        <v>25.4166</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.62</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9749</v>
+        <v>1.0795</v>
       </c>
       <c r="J38" t="n">
-        <v>21.4478</v>
+        <v>23.749</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.46</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7824</v>
+        <v>0.872</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2128</v>
+        <v>19.184</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>1.13</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3356</v>
+        <v>0.3551</v>
       </c>
       <c r="J40" t="n">
-        <v>7.3832</v>
+        <v>7.8122</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2288</v>
+        <v>0.2523</v>
       </c>
       <c r="J41" t="n">
-        <v>5.0336</v>
+        <v>5.5506</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4221</v>
+        <v>0.4628</v>
       </c>
       <c r="J42" t="n">
-        <v>10.9746</v>
+        <v>12.0328</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1115</v>
+        <v>0.1144</v>
       </c>
       <c r="J43" t="n">
-        <v>2.899</v>
+        <v>2.9744</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.8</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2254</v>
+        <v>-0.2418</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.8604</v>
+        <v>-6.2868</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.73</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2939</v>
+        <v>-0.3091</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.6414</v>
+        <v>-8.0366</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4258</v>
+        <v>-0.436</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.0708</v>
+        <v>-11.336</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.54</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5397</v>
+        <v>0.6155</v>
       </c>
       <c r="J47" t="n">
-        <v>14.0322</v>
+        <v>16.003</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.42</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4605</v>
+        <v>0.5229</v>
       </c>
       <c r="J48" t="n">
-        <v>11.973</v>
+        <v>13.5954</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0491</v>
+        <v>-0.0529</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.2766</v>
+        <v>-1.3754</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.126</v>
+        <v>-0.1347</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.276</v>
+        <v>-3.5022</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2435</v>
+        <v>-0.2538</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.331</v>
+        <v>-6.5988</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4004</v>
+        <v>0.4319</v>
       </c>
       <c r="J52" t="n">
-        <v>18.4184</v>
+        <v>19.8674</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3844</v>
+        <v>0.4091</v>
       </c>
       <c r="J53" t="n">
-        <v>17.6824</v>
+        <v>18.8186</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3682</v>
+        <v>0.3845</v>
       </c>
       <c r="J54" t="n">
-        <v>16.9372</v>
+        <v>17.687</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3323</v>
+        <v>0.3331</v>
       </c>
       <c r="J55" t="n">
-        <v>15.2858</v>
+        <v>15.3226</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8605</v>
+        <v>-0.7957</v>
       </c>
       <c r="J56" t="n">
-        <v>-39.583</v>
+        <v>-36.6022</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.447</v>
+        <v>0.4947</v>
       </c>
       <c r="J57" t="n">
-        <v>20.562</v>
+        <v>22.7562</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1143</v>
+        <v>0.1233</v>
       </c>
       <c r="J58" t="n">
-        <v>5.2578</v>
+        <v>5.6718</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0902</v>
+        <v>0.0988</v>
       </c>
       <c r="J59" t="n">
-        <v>4.1492</v>
+        <v>4.5448</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0509</v>
+        <v>-0.0589</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.3414</v>
+        <v>-2.7094</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2797</v>
+        <v>-0.2923</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.8662</v>
+        <v>-13.4458</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.75</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1319</v>
+        <v>1.2458</v>
       </c>
       <c r="J62" t="n">
-        <v>26.0337</v>
+        <v>28.6534</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9542</v>
+        <v>1.0568</v>
       </c>
       <c r="J63" t="n">
-        <v>21.9466</v>
+        <v>24.3064</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.53</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8698</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>20.0054</v>
+        <v>22.2226</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1.25</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5174</v>
+        <v>0.5789</v>
       </c>
       <c r="J65" t="n">
-        <v>11.9002</v>
+        <v>13.3147</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.76</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8135</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.7105</v>
+        <v>-17.0522</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.03</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1917</v>
+        <v>0.1731</v>
       </c>
       <c r="J67" t="n">
-        <v>4.4091</v>
+        <v>3.9813</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1917</v>
+        <v>0.1731</v>
       </c>
       <c r="J68" t="n">
-        <v>4.4091</v>
+        <v>3.9813</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2918</v>
+        <v>-0.3112</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.7114</v>
+        <v>-7.1576</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.58</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4131</v>
+        <v>-0.4276</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.501300000000001</v>
+        <v>-9.8348</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.31</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6636</v>
+        <v>-0.6613</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.2628</v>
+        <v>-15.2099</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7405</v>
+        <v>0.8227</v>
       </c>
       <c r="J72" t="n">
-        <v>22.215</v>
+        <v>24.681</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0448</v>
+        <v>0.0484</v>
       </c>
       <c r="J73" t="n">
-        <v>1.344</v>
+        <v>1.452</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0843</v>
+        <v>-0.0961</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.529</v>
+        <v>-2.883</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.91</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1188</v>
+        <v>-0.1321</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.564</v>
+        <v>-3.963</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.41</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5955</v>
+        <v>-0.5951</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.865</v>
+        <v>-17.853</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.62</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0588</v>
+        <v>1.1538</v>
       </c>
       <c r="J77" t="n">
-        <v>31.764</v>
+        <v>34.614</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4084</v>
+        <v>0.4449</v>
       </c>
       <c r="J78" t="n">
-        <v>12.252</v>
+        <v>13.347</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2827</v>
+        <v>-0.2753</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.481</v>
+        <v>-8.259</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.401</v>
+        <v>-0.3846</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.03</v>
+        <v>-11.538</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.82</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5925</v>
+        <v>-0.5575</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.775</v>
+        <v>-16.725</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2834</v>
+        <v>0.2795</v>
       </c>
       <c r="J82" t="n">
-        <v>8.2186</v>
+        <v>8.105499999999999</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>0.97</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0382</v>
+        <v>-0.0492</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.1078</v>
+        <v>-1.4268</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.84</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1847</v>
+        <v>-0.2014</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.3563</v>
+        <v>-5.8406</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2447</v>
+        <v>-0.261</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.0963</v>
+        <v>-7.569</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.2933</v>
+        <v>-0.3086</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.505699999999999</v>
+        <v>-8.949400000000001</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5043</v>
+        <v>0.5496</v>
       </c>
       <c r="J87" t="n">
-        <v>14.6247</v>
+        <v>15.9384</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I88" t="n">
-        <v>0.426</v>
+        <v>0.4615</v>
       </c>
       <c r="J88" t="n">
-        <v>12.354</v>
+        <v>13.3835</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0527</v>
+        <v>-0.0582</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.5283</v>
+        <v>-1.6878</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4324</v>
+        <v>-0.4185</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.5396</v>
+        <v>-12.1365</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6972</v>
+        <v>-0.6549</v>
       </c>
       <c r="J91" t="n">
-        <v>-20.2188</v>
+        <v>-18.9921</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3562</v>
+        <v>0.3657</v>
       </c>
       <c r="J92" t="n">
-        <v>9.261200000000001</v>
+        <v>9.5082</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1041</v>
+        <v>-0.1179</v>
       </c>
       <c r="J93" t="n">
-        <v>-2.7066</v>
+        <v>-3.0654</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.91</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.115</v>
+        <v>-0.1292</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.99</v>
+        <v>-3.3592</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.87</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1578</v>
+        <v>-0.1732</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.1028</v>
+        <v>-4.5032</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2786</v>
+        <v>-0.2934</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.2436</v>
+        <v>-7.6284</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0098</v>
+        <v>1.1015</v>
       </c>
       <c r="J97" t="n">
-        <v>26.2548</v>
+        <v>28.639</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0383</v>
+        <v>0.0485</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9958</v>
+        <v>1.261</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1838</v>
+        <v>-0.1822</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.7788</v>
+        <v>-4.7372</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3407</v>
+        <v>-0.3297</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.8582</v>
+        <v>-8.5722</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3407</v>
+        <v>-0.3297</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.8582</v>
+        <v>-8.5722</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.2564</v>
+        <v>0.25</v>
       </c>
       <c r="J102" t="n">
-        <v>6.1536</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>0.96</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0453</v>
+        <v>-0.0588</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.0872</v>
+        <v>-1.4112</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1294</v>
+        <v>-0.1461</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.1056</v>
+        <v>-3.5064</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2003</v>
+        <v>-0.2181</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.8072</v>
+        <v>-5.2344</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.47</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5303</v>
+        <v>-0.5357</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.7272</v>
+        <v>-12.8568</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.75</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1843</v>
+        <v>1.2923</v>
       </c>
       <c r="J107" t="n">
-        <v>28.4232</v>
+        <v>31.0152</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.22</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4962</v>
+        <v>0.5498</v>
       </c>
       <c r="J108" t="n">
-        <v>11.9088</v>
+        <v>13.1952</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3655</v>
+        <v>0.3876</v>
       </c>
       <c r="J109" t="n">
-        <v>8.772</v>
+        <v>9.3024</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>1.09</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2768</v>
+        <v>0.2858</v>
       </c>
       <c r="J110" t="n">
-        <v>6.6432</v>
+        <v>6.8592</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.799</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-19.176</v>
+        <v>-17.6496</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.67</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9075</v>
+        <v>1.001</v>
       </c>
       <c r="J112" t="n">
-        <v>23.595</v>
+        <v>26.026</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1847</v>
+        <v>-0.2014</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.8022</v>
+        <v>-5.2364</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.77</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2545</v>
+        <v>-0.2706</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.617</v>
+        <v>-7.0356</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.64</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3788</v>
+        <v>-0.3912</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.848800000000001</v>
+        <v>-10.1712</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5077</v>
+        <v>-0.5137</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.2002</v>
+        <v>-13.3562</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.96</v>
       </c>
       <c r="I117" t="n">
-        <v>1.449</v>
+        <v>1.5672</v>
       </c>
       <c r="J117" t="n">
-        <v>37.674</v>
+        <v>40.7472</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.19</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4565</v>
+        <v>0.5042</v>
       </c>
       <c r="J118" t="n">
-        <v>11.869</v>
+        <v>13.1092</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0395</v>
+        <v>-0.0272</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.027</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1728</v>
+        <v>-0.1651</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.4928</v>
+        <v>-4.2926</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9165</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>-23.829</v>
+        <v>-21.8192</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I122" t="n">
-        <v>0.237</v>
+        <v>0.2408</v>
       </c>
       <c r="J122" t="n">
-        <v>8.532</v>
+        <v>8.668799999999999</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0742</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>2.6712</v>
+        <v>2.8512</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0065</v>
+        <v>0.0046</v>
       </c>
       <c r="J124" t="n">
-        <v>0.234</v>
+        <v>0.1656</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1296</v>
+        <v>-0.1434</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.6656</v>
+        <v>-5.1624</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2539</v>
+        <v>-0.2682</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.1404</v>
+        <v>-9.655200000000001</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.26</v>
       </c>
       <c r="I127" t="n">
-        <v>0.5843</v>
+        <v>0.6404</v>
       </c>
       <c r="J127" t="n">
-        <v>21.0348</v>
+        <v>23.0544</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.15</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4178</v>
+        <v>0.4539</v>
       </c>
       <c r="J128" t="n">
-        <v>15.0408</v>
+        <v>16.3404</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2688</v>
+        <v>-0.2656</v>
       </c>
       <c r="J129" t="n">
-        <v>-9.6768</v>
+        <v>-9.5616</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2992</v>
+        <v>-0.2939</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.7712</v>
+        <v>-10.5804</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3581</v>
+        <v>-0.3484</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.8916</v>
+        <v>-12.5424</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.13</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2861</v>
+        <v>0.2814</v>
       </c>
       <c r="J132" t="n">
-        <v>7.1525</v>
+        <v>7.035</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1304</v>
+        <v>0.1286</v>
       </c>
       <c r="J133" t="n">
-        <v>3.26</v>
+        <v>3.215</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1891</v>
+        <v>-0.2071</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.7275</v>
+        <v>-5.1775</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.67</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3424</v>
+        <v>-0.3577</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.56</v>
+        <v>-8.942500000000001</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5462</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.655</v>
+        <v>-13.7725</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.66</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6161</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="J137" t="n">
-        <v>15.4025</v>
+        <v>17.6025</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.27</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3571</v>
+        <v>0.3863</v>
       </c>
       <c r="J138" t="n">
-        <v>8.9275</v>
+        <v>9.657500000000001</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3001</v>
+        <v>0.3157</v>
       </c>
       <c r="J139" t="n">
-        <v>7.5025</v>
+        <v>7.8925</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.203</v>
+        <v>-0.2132</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.075</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3503</v>
+        <v>-0.3588</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.7575</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.8227</v>
       </c>
       <c r="J142" t="n">
-        <v>18.535</v>
+        <v>20.5675</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.4</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7285</v>
+        <v>0.8086</v>
       </c>
       <c r="J143" t="n">
-        <v>18.2125</v>
+        <v>20.215</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.3</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5975</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J144" t="n">
-        <v>14.9375</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>1.23</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5044</v>
+        <v>0.5607</v>
       </c>
       <c r="J145" t="n">
-        <v>12.61</v>
+        <v>14.0175</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3864</v>
+        <v>-0.3617</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.66</v>
+        <v>-9.0425</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.08</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3127</v>
+        <v>0.292</v>
       </c>
       <c r="J147" t="n">
-        <v>7.8175</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1286</v>
+        <v>0.1097</v>
       </c>
       <c r="J148" t="n">
-        <v>3.215</v>
+        <v>2.7425</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.58</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4141</v>
+        <v>-0.4283</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.3525</v>
+        <v>-10.7075</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.53</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4607</v>
+        <v>-0.4724</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.5175</v>
+        <v>-11.81</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.49</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.498</v>
+        <v>-0.5074</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.45</v>
+        <v>-12.685</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.75</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1108</v>
+        <v>1.2272</v>
       </c>
       <c r="J152" t="n">
-        <v>19.9944</v>
+        <v>22.0896</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.74</v>
       </c>
       <c r="I153" t="n">
-        <v>1.0993</v>
+        <v>1.2151</v>
       </c>
       <c r="J153" t="n">
-        <v>19.7874</v>
+        <v>21.8718</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>1.61</v>
       </c>
       <c r="I154" t="n">
-        <v>0.9493</v>
+        <v>1.0549</v>
       </c>
       <c r="J154" t="n">
-        <v>17.0874</v>
+        <v>18.9882</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>1.38</v>
       </c>
       <c r="I155" t="n">
-        <v>0.6766</v>
+        <v>0.7581</v>
       </c>
       <c r="J155" t="n">
-        <v>12.1788</v>
+        <v>13.6458</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3131</v>
+        <v>-0.2813</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.6358</v>
+        <v>-5.0634</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>0.59</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.3367</v>
+        <v>-0.3667</v>
       </c>
       <c r="J157" t="n">
-        <v>-6.0606</v>
+        <v>-6.6006</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.3696</v>
+        <v>-0.397</v>
       </c>
       <c r="J158" t="n">
-        <v>-6.6528</v>
+        <v>-7.146</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>0.45</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4801</v>
+        <v>-0.4992</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.6418</v>
+        <v>-8.9856</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>0.43</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4971</v>
+        <v>-0.5152</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.947800000000001</v>
+        <v>-9.2736</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.18</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7513</v>
+        <v>-0.7456</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.5234</v>
+        <v>-13.4208</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5132</v>
+        <v>0.4886</v>
       </c>
       <c r="J162" t="n">
-        <v>12.83</v>
+        <v>12.215</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.08</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2636</v>
+        <v>0.2553</v>
       </c>
       <c r="J163" t="n">
-        <v>6.59</v>
+        <v>6.3825</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2279</v>
+        <v>-0.2459</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.6975</v>
+        <v>-6.1475</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.66</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3524</v>
+        <v>-0.3672</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.81</v>
+        <v>-9.18</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.41</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5829</v>
+        <v>-0.5851</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.5725</v>
+        <v>-14.6275</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>1.58</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2639</v>
+        <v>1.2313</v>
       </c>
       <c r="J167" t="n">
-        <v>31.5975</v>
+        <v>30.7825</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5496</v>
+        <v>0.5327</v>
       </c>
       <c r="J168" t="n">
-        <v>13.74</v>
+        <v>13.3175</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2612</v>
+        <v>0.268</v>
       </c>
       <c r="J169" t="n">
-        <v>6.53</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1267</v>
+        <v>-0.1223</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.1675</v>
+        <v>-3.0575</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.82</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6055</v>
+        <v>-0.5666</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.1375</v>
+        <v>-14.165</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.47</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6417</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J172" t="n">
-        <v>16.6842</v>
+        <v>16.4736</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.31</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4501</v>
+        <v>0.4543</v>
       </c>
       <c r="J173" t="n">
-        <v>11.7026</v>
+        <v>11.8118</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.85</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1886</v>
+        <v>-0.202</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.9036</v>
+        <v>-5.252</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3179</v>
+        <v>-0.3297</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.2654</v>
+        <v>-8.5722</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3558</v>
+        <v>-0.3665</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.2508</v>
+        <v>-9.529</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.574</v>
+        <v>0.5561</v>
       </c>
       <c r="J177" t="n">
-        <v>14.924</v>
+        <v>14.4586</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I178" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0704</v>
       </c>
       <c r="J178" t="n">
-        <v>1.7706</v>
+        <v>1.8304</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2371</v>
+        <v>-0.253</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.1646</v>
+        <v>-6.578</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.286</v>
+        <v>-0.3011</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.436</v>
+        <v>-7.8286</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.409</v>
+        <v>-0.4197</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.634</v>
+        <v>-10.9122</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5911</v>
+        <v>0.5532</v>
       </c>
       <c r="J182" t="n">
-        <v>14.1864</v>
+        <v>13.2768</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>0.93</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0873</v>
       </c>
       <c r="J183" t="n">
-        <v>-1.6464</v>
+        <v>-2.0952</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>0.79</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.222</v>
+        <v>-0.2414</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.328</v>
+        <v>-5.7936</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4745</v>
+        <v>-0.4847</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.388</v>
+        <v>-11.6328</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.38</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6034</v>
+        <v>-0.6052</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.4816</v>
+        <v>-14.5248</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.91</v>
       </c>
       <c r="I187" t="n">
-        <v>1.6382</v>
+        <v>1.6302</v>
       </c>
       <c r="J187" t="n">
-        <v>39.3168</v>
+        <v>39.1248</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.4054</v>
+        <v>0.406</v>
       </c>
       <c r="J188" t="n">
-        <v>9.7296</v>
+        <v>9.744</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>1.11</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3244</v>
+        <v>0.3318</v>
       </c>
       <c r="J189" t="n">
-        <v>7.7856</v>
+        <v>7.9632</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2678</v>
+        <v>0.2795</v>
       </c>
       <c r="J190" t="n">
-        <v>6.4272</v>
+        <v>6.708</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.88</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4669</v>
+        <v>-0.4368</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.2056</v>
+        <v>-10.4832</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.17</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5538</v>
+        <v>0.5252</v>
       </c>
       <c r="J192" t="n">
-        <v>16.614</v>
+        <v>15.756</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.03</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1372</v>
+        <v>0.1403</v>
       </c>
       <c r="J193" t="n">
-        <v>4.116</v>
+        <v>4.209</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1247</v>
+        <v>-0.1318</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.741</v>
+        <v>-3.954</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2223</v>
+        <v>-0.2258</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.669</v>
+        <v>-6.774</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7159</v>
+        <v>-0.6726</v>
       </c>
       <c r="J196" t="n">
-        <v>-21.477</v>
+        <v>-20.178</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.59</v>
       </c>
       <c r="I197" t="n">
-        <v>1.0276</v>
+        <v>0.9867</v>
       </c>
       <c r="J197" t="n">
-        <v>30.828</v>
+        <v>29.601</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.48</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8784999999999999</v>
+        <v>0.8384</v>
       </c>
       <c r="J198" t="n">
-        <v>26.355</v>
+        <v>25.152</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.156</v>
+        <v>-0.1666</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.68</v>
+        <v>-4.998</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2092</v>
+        <v>-0.2204</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.276</v>
+        <v>-6.612</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3559</v>
+        <v>-0.3649</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.677</v>
+        <v>-10.947</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>2.17</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8283</v>
+        <v>1.8437</v>
       </c>
       <c r="J202" t="n">
-        <v>31.0811</v>
+        <v>31.3429</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.65</v>
       </c>
       <c r="I203" t="n">
-        <v>1.2568</v>
+        <v>1.241</v>
       </c>
       <c r="J203" t="n">
-        <v>21.3656</v>
+        <v>21.097</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.59</v>
       </c>
       <c r="I204" t="n">
-        <v>1.19</v>
+        <v>1.1688</v>
       </c>
       <c r="J204" t="n">
-        <v>20.23</v>
+        <v>19.8696</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.41</v>
       </c>
       <c r="I205" t="n">
-        <v>0.9566</v>
+        <v>0.913</v>
       </c>
       <c r="J205" t="n">
-        <v>16.2622</v>
+        <v>15.521</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3015</v>
+        <v>0.3277</v>
       </c>
       <c r="J206" t="n">
-        <v>5.1255</v>
+        <v>5.5709</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>0.64</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.2375</v>
+        <v>-0.2805</v>
       </c>
       <c r="J207" t="n">
-        <v>-4.0375</v>
+        <v>-4.7685</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.59</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2999</v>
+        <v>-0.3375</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.0983</v>
+        <v>-5.7375</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.43</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.482</v>
+        <v>-0.5036</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.194000000000001</v>
+        <v>-8.561199999999999</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.2</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.717</v>
+        <v>-0.7161999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>-12.189</v>
+        <v>-12.1754</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.05</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8882</v>
+        <v>-0.8681</v>
       </c>
       <c r="J211" t="n">
-        <v>-15.0994</v>
+        <v>-14.7577</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7855</v>
+        <v>0.7442</v>
       </c>
       <c r="J212" t="n">
-        <v>27.4925</v>
+        <v>26.047</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3467</v>
+        <v>0.3433</v>
       </c>
       <c r="J213" t="n">
-        <v>12.1345</v>
+        <v>12.0155</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.79</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2411</v>
+        <v>-0.2561</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.438499999999999</v>
+        <v>-8.9635</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2901</v>
+        <v>-0.3042</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.1535</v>
+        <v>-10.647</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4035</v>
+        <v>-0.4139</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.1225</v>
+        <v>-14.4865</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0713</v>
+        <v>1.0184</v>
       </c>
       <c r="J217" t="n">
-        <v>37.4955</v>
+        <v>35.644</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.37</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9936</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="J218" t="n">
-        <v>34.776</v>
+        <v>32.4765</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.03</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1161</v>
+        <v>0.1261</v>
       </c>
       <c r="J219" t="n">
-        <v>4.0635</v>
+        <v>4.4135</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6421</v>
+        <v>-0.6021</v>
       </c>
       <c r="J220" t="n">
-        <v>-22.4735</v>
+        <v>-21.0735</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7948</v>
+        <v>-0.7368</v>
       </c>
       <c r="J221" t="n">
-        <v>-27.818</v>
+        <v>-25.788</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5288</v>
+        <v>0.5314</v>
       </c>
       <c r="J222" t="n">
-        <v>14.8064</v>
+        <v>14.8792</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.33</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4579</v>
+        <v>0.4646</v>
       </c>
       <c r="J223" t="n">
-        <v>12.8212</v>
+        <v>13.0088</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.04</v>
+        <v>0.0493</v>
       </c>
       <c r="J224" t="n">
-        <v>1.12</v>
+        <v>1.3804</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0195</v>
+        <v>0.0268</v>
       </c>
       <c r="J225" t="n">
-        <v>0.546</v>
+        <v>0.7504</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.61</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4272</v>
+        <v>-0.4341</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.9616</v>
+        <v>-12.1548</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.1</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2225</v>
+        <v>0.2231</v>
       </c>
       <c r="J227" t="n">
-        <v>6.23</v>
+        <v>6.2468</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.0868</v>
+        <v>-0.1015</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.4304</v>
+        <v>-2.842</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.88</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1427</v>
+        <v>-0.159</v>
       </c>
       <c r="J229" t="n">
-        <v>-3.9956</v>
+        <v>-4.452</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.78</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2423</v>
+        <v>-0.2592</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.7844</v>
+        <v>-7.2576</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.64</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3764</v>
+        <v>-0.3893</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.5392</v>
+        <v>-10.9004</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>0.89</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.0725</v>
+        <v>-0.1015</v>
       </c>
       <c r="J232" t="n">
-        <v>-1.5225</v>
+        <v>-2.1315</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.85</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.121</v>
+        <v>-0.1495</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.541</v>
+        <v>-3.1395</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.53</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.4406</v>
+        <v>-0.4567</v>
       </c>
       <c r="J234" t="n">
-        <v>-9.252599999999999</v>
+        <v>-9.5907</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.45</v>
+        <v>-0.4655</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.775499999999999</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.31</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6494</v>
+        <v>-0.6501</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.6374</v>
+        <v>-13.6521</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.65</v>
       </c>
       <c r="I237" t="n">
-        <v>1.2912</v>
+        <v>1.271</v>
       </c>
       <c r="J237" t="n">
-        <v>27.1152</v>
+        <v>26.691</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.57</v>
       </c>
       <c r="I238" t="n">
-        <v>1.195</v>
+        <v>1.1682</v>
       </c>
       <c r="J238" t="n">
-        <v>25.095</v>
+        <v>24.5322</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.38</v>
       </c>
       <c r="I239" t="n">
-        <v>0.9334</v>
+        <v>0.8837</v>
       </c>
       <c r="J239" t="n">
-        <v>19.6014</v>
+        <v>18.5577</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.21</v>
       </c>
       <c r="I240" t="n">
-        <v>0.5532</v>
+        <v>0.5456</v>
       </c>
       <c r="J240" t="n">
-        <v>11.6172</v>
+        <v>11.4576</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.99</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1412</v>
+        <v>-0.1198</v>
       </c>
       <c r="J241" t="n">
-        <v>-2.9652</v>
+        <v>-2.5158</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1011</v>
+        <v>-0.1186</v>
       </c>
       <c r="J242" t="n">
-        <v>-2.2242</v>
+        <v>-2.6092</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>0.91</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1011</v>
+        <v>-0.1186</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.2242</v>
+        <v>-2.6092</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1567</v>
+        <v>-0.175</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.4474</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2161</v>
+        <v>-0.2347</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.7542</v>
+        <v>-5.1634</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4431</v>
+        <v>-0.4541</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.748200000000001</v>
+        <v>-9.9902</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3141</v>
+        <v>1.2869</v>
       </c>
       <c r="J247" t="n">
-        <v>28.9102</v>
+        <v>28.3118</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.38</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9778</v>
+        <v>0.9182</v>
       </c>
       <c r="J248" t="n">
-        <v>21.5116</v>
+        <v>20.2004</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.6606</v>
+        <v>0.634</v>
       </c>
       <c r="J249" t="n">
-        <v>14.5332</v>
+        <v>13.948</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.95</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2433</v>
+        <v>-0.2323</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.3526</v>
+        <v>-5.1106</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-1.0145</v>
+        <v>-0.9241</v>
       </c>
       <c r="J251" t="n">
-        <v>-22.319</v>
+        <v>-20.3302</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>0.98</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0293</v>
+        <v>-0.0377</v>
       </c>
       <c r="J252" t="n">
-        <v>-0.8204</v>
+        <v>-1.0556</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>0.96</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.057</v>
+        <v>-0.0678</v>
       </c>
       <c r="J253" t="n">
-        <v>-1.596</v>
+        <v>-1.8984</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.95</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0696</v>
+        <v>-0.0813</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.9488</v>
+        <v>-2.2764</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.9</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1262</v>
+        <v>-0.1407</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.5336</v>
+        <v>-3.9396</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.83</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1996</v>
+        <v>-0.2152</v>
       </c>
       <c r="J256" t="n">
-        <v>-5.5888</v>
+        <v>-6.0256</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.36</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9651</v>
+        <v>0.9003</v>
       </c>
       <c r="J257" t="n">
-        <v>27.0228</v>
+        <v>25.2084</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3235</v>
+        <v>0.3246</v>
       </c>
       <c r="J258" t="n">
-        <v>9.058</v>
+        <v>9.088800000000001</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.06</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2089</v>
+        <v>0.2168</v>
       </c>
       <c r="J259" t="n">
-        <v>5.8492</v>
+        <v>6.0704</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.03</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1105</v>
+        <v>0.1222</v>
       </c>
       <c r="J260" t="n">
-        <v>3.094</v>
+        <v>3.4216</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2866</v>
+        <v>-0.278</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.024800000000001</v>
+        <v>-7.784</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.48</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1035</v>
+        <v>1.0655</v>
       </c>
       <c r="J262" t="n">
-        <v>27.5875</v>
+        <v>26.6375</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.41</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0081</v>
+        <v>0.9549</v>
       </c>
       <c r="J263" t="n">
-        <v>25.2025</v>
+        <v>23.8725</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8915</v>
+        <v>0.8417</v>
       </c>
       <c r="J264" t="n">
-        <v>22.2875</v>
+        <v>21.0425</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.08</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2314</v>
+        <v>0.2473</v>
       </c>
       <c r="J265" t="n">
-        <v>5.785</v>
+        <v>6.1825</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.96</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.2308</v>
+        <v>-0.215</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.77</v>
+        <v>-5.375</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3879</v>
+        <v>0.3696</v>
       </c>
       <c r="J267" t="n">
-        <v>9.6975</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.1863</v>
+        <v>-0.205</v>
       </c>
       <c r="J268" t="n">
-        <v>-4.6575</v>
+        <v>-5.125</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.7</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3102</v>
+        <v>-0.3273</v>
       </c>
       <c r="J269" t="n">
-        <v>-7.755</v>
+        <v>-8.182499999999999</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3292</v>
+        <v>-0.3457</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.23</v>
+        <v>-8.6425</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.65</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3575</v>
+        <v>-0.3729</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.9375</v>
+        <v>-9.3225</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.6</v>
       </c>
       <c r="I272" t="n">
-        <v>1.258</v>
+        <v>1.2306</v>
       </c>
       <c r="J272" t="n">
-        <v>28.934</v>
+        <v>28.3038</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.5</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1326</v>
+        <v>1.0964</v>
       </c>
       <c r="J273" t="n">
-        <v>26.0498</v>
+        <v>25.2172</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.31</v>
       </c>
       <c r="I274" t="n">
-        <v>0.8065</v>
+        <v>0.7662</v>
       </c>
       <c r="J274" t="n">
-        <v>18.5495</v>
+        <v>17.6226</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.058</v>
+        <v>-0.0402</v>
       </c>
       <c r="J275" t="n">
-        <v>-1.334</v>
+        <v>-0.9246</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.735</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.905</v>
+        <v>-15.5687</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0851</v>
       </c>
       <c r="J277" t="n">
-        <v>2.1896</v>
+        <v>1.9573</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.85</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1666</v>
+        <v>-0.1851</v>
       </c>
       <c r="J278" t="n">
-        <v>-3.8318</v>
+        <v>-4.2573</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.84</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1769</v>
+        <v>-0.1954</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.0687</v>
+        <v>-4.4942</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1769</v>
+        <v>-0.1954</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.0687</v>
+        <v>-4.4942</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.48</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5163</v>
+        <v>-0.5232</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.8749</v>
+        <v>-12.0336</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.79</v>
       </c>
       <c r="I282" t="n">
-        <v>1.4848</v>
+        <v>1.4712</v>
       </c>
       <c r="J282" t="n">
-        <v>32.6656</v>
+        <v>32.3664</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.43</v>
       </c>
       <c r="I283" t="n">
-        <v>1.0383</v>
+        <v>0.9893</v>
       </c>
       <c r="J283" t="n">
-        <v>22.8426</v>
+        <v>21.7646</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.02</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0336</v>
+        <v>0.058</v>
       </c>
       <c r="J284" t="n">
-        <v>0.7392</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.02</v>
       </c>
       <c r="I285" t="n">
-        <v>0.0336</v>
+        <v>0.058</v>
       </c>
       <c r="J285" t="n">
-        <v>0.7392</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>1.02</v>
       </c>
       <c r="I286" t="n">
-        <v>0.0336</v>
+        <v>0.058</v>
       </c>
       <c r="J286" t="n">
-        <v>0.7392</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.19</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5213</v>
       </c>
       <c r="J287" t="n">
-        <v>12.364</v>
+        <v>11.4686</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>0.8</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2054</v>
+        <v>-0.2265</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.5188</v>
+        <v>-4.983</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>0.68</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3187</v>
+        <v>-0.3375</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.0114</v>
+        <v>-7.425</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.55</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4402</v>
+        <v>-0.4534</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.6844</v>
+        <v>-9.9748</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.41</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5705</v>
+        <v>-0.5753</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.551</v>
+        <v>-12.6566</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.24</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5148</v>
+        <v>0.5033</v>
       </c>
       <c r="J292" t="n">
-        <v>14.9292</v>
+        <v>14.5957</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1859</v>
+        <v>0.1932</v>
       </c>
       <c r="J293" t="n">
-        <v>5.3911</v>
+        <v>5.6028</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.06</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1639</v>
+        <v>0.1717</v>
       </c>
       <c r="J294" t="n">
-        <v>4.7531</v>
+        <v>4.9793</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.84</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1972</v>
+        <v>-0.211</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.7188</v>
+        <v>-6.119</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.74</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2968</v>
+        <v>-0.3095</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.607200000000001</v>
+        <v>-8.9755</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.22</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.6481</v>
       </c>
       <c r="J297" t="n">
-        <v>20.1289</v>
+        <v>18.7949</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.18</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5884</v>
+        <v>0.5546</v>
       </c>
       <c r="J298" t="n">
-        <v>17.0636</v>
+        <v>16.0834</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.95</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1875</v>
+        <v>-0.1937</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.4375</v>
+        <v>-5.6173</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.91</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3081</v>
+        <v>-0.3071</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.934900000000001</v>
+        <v>-8.905900000000001</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.53</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.2693</v>
+        <v>-1.1503</v>
       </c>
       <c r="J301" t="n">
-        <v>-36.8097</v>
+        <v>-33.3587</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.73</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2031</v>
+        <v>1.1775</v>
       </c>
       <c r="J302" t="n">
-        <v>36.093</v>
+        <v>35.325</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.96</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0602</v>
+        <v>-0.0703</v>
       </c>
       <c r="J303" t="n">
-        <v>-1.806</v>
+        <v>-2.109</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1412</v>
+        <v>-0.1551</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.236</v>
+        <v>-4.653</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.313</v>
+        <v>-0.3259</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.390000000000001</v>
+        <v>-9.776999999999999</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4981</v>
+        <v>-0.5033</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.943</v>
+        <v>-15.099</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.36</v>
       </c>
       <c r="I307" t="n">
-        <v>1.0187</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="J307" t="n">
-        <v>30.561</v>
+        <v>28.413</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1013</v>
+        <v>0.1047</v>
       </c>
       <c r="J308" t="n">
-        <v>3.039</v>
+        <v>3.141</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>0.98</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.0885</v>
+        <v>-0.096</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.655</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1242</v>
+        <v>-0.1315</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.726</v>
+        <v>-3.945</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.52</v>
       </c>
       <c r="I311" t="n">
-        <v>-1.2959</v>
+        <v>-1.1723</v>
       </c>
       <c r="J311" t="n">
-        <v>-38.877</v>
+        <v>-35.169</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.15</v>
       </c>
       <c r="I312" t="n">
-        <v>0.401</v>
+        <v>0.3873</v>
       </c>
       <c r="J312" t="n">
-        <v>10.827</v>
+        <v>10.4571</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.04</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1589</v>
+        <v>0.1557</v>
       </c>
       <c r="J313" t="n">
-        <v>4.2903</v>
+        <v>4.2039</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>0.89</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1305</v>
+        <v>-0.1469</v>
       </c>
       <c r="J314" t="n">
-        <v>-3.5235</v>
+        <v>-3.9663</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3839</v>
+        <v>-0.3968</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.3653</v>
+        <v>-10.7136</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.55</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4581</v>
+        <v>-0.4675</v>
       </c>
       <c r="J316" t="n">
-        <v>-12.3687</v>
+        <v>-12.6225</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.52</v>
       </c>
       <c r="I317" t="n">
-        <v>1.187</v>
+        <v>1.1493</v>
       </c>
       <c r="J317" t="n">
-        <v>32.049</v>
+        <v>31.0311</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.39</v>
       </c>
       <c r="I318" t="n">
-        <v>1.0093</v>
+        <v>0.9489</v>
       </c>
       <c r="J318" t="n">
-        <v>27.2511</v>
+        <v>25.6203</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.05</v>
       </c>
       <c r="I319" t="n">
-        <v>0.17</v>
+        <v>0.1818</v>
       </c>
       <c r="J319" t="n">
-        <v>4.59</v>
+        <v>4.9086</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.99</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0805</v>
       </c>
       <c r="J320" t="n">
-        <v>-2.295</v>
+        <v>-2.1735</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.9322</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="J321" t="n">
-        <v>-25.1694</v>
+        <v>-23.0661</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.25</v>
       </c>
       <c r="I322" t="n">
-        <v>0.6098</v>
+        <v>0.5767</v>
       </c>
       <c r="J322" t="n">
-        <v>14.6352</v>
+        <v>13.8408</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.04</v>
       </c>
       <c r="I323" t="n">
-        <v>0.1687</v>
+        <v>0.163</v>
       </c>
       <c r="J323" t="n">
-        <v>4.0488</v>
+        <v>3.912</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.74</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2762</v>
+        <v>-0.2934</v>
       </c>
       <c r="J324" t="n">
-        <v>-6.6288</v>
+        <v>-7.0416</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.71</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3049</v>
+        <v>-0.3214</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.3176</v>
+        <v>-7.7136</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.4</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.592</v>
+        <v>-0.5936</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.208</v>
+        <v>-14.2464</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.84</v>
       </c>
       <c r="I327" t="n">
-        <v>1.5551</v>
+        <v>1.5433</v>
       </c>
       <c r="J327" t="n">
-        <v>37.3224</v>
+        <v>37.0392</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.62</v>
       </c>
       <c r="I328" t="n">
-        <v>1.2865</v>
+        <v>1.2603</v>
       </c>
       <c r="J328" t="n">
-        <v>30.876</v>
+        <v>30.2472</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>1.13</v>
       </c>
       <c r="I329" t="n">
-        <v>0.3793</v>
+        <v>0.3821</v>
       </c>
       <c r="J329" t="n">
-        <v>9.103199999999999</v>
+        <v>9.170400000000001</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.79</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.7064</v>
+        <v>-0.6521</v>
       </c>
       <c r="J330" t="n">
-        <v>-16.9536</v>
+        <v>-15.6504</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.832</v>
+        <v>-0.763</v>
       </c>
       <c r="J331" t="n">
-        <v>-19.968</v>
+        <v>-18.312</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.07</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1985</v>
+        <v>0.2024</v>
       </c>
       <c r="J332" t="n">
-        <v>5.7565</v>
+        <v>5.8696</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.07</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1985</v>
+        <v>0.2024</v>
       </c>
       <c r="J333" t="n">
-        <v>5.7565</v>
+        <v>5.8696</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.89</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1388</v>
+        <v>-0.1533</v>
       </c>
       <c r="J334" t="n">
-        <v>-4.0252</v>
+        <v>-4.4457</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.85</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1812</v>
+        <v>-0.1962</v>
       </c>
       <c r="J335" t="n">
-        <v>-5.2548</v>
+        <v>-5.6898</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2018</v>
+        <v>-0.2169</v>
       </c>
       <c r="J336" t="n">
-        <v>-5.8522</v>
+        <v>-6.2901</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.33</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9366</v>
+        <v>0.8665</v>
       </c>
       <c r="J337" t="n">
-        <v>27.1614</v>
+        <v>25.1285</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.19</v>
       </c>
       <c r="I338" t="n">
-        <v>0.5881</v>
+        <v>0.5594</v>
       </c>
       <c r="J338" t="n">
-        <v>17.0549</v>
+        <v>16.2226</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.99</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0567</v>
+        <v>-0.0609</v>
       </c>
       <c r="J339" t="n">
-        <v>-1.6443</v>
+        <v>-1.7661</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.85</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4932</v>
+        <v>-0.4722</v>
       </c>
       <c r="J340" t="n">
-        <v>-14.3028</v>
+        <v>-13.6938</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.72</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.829</v>
+        <v>-0.7693</v>
       </c>
       <c r="J341" t="n">
-        <v>-24.041</v>
+        <v>-22.3097</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2504</v>
+        <v>1.2171</v>
       </c>
       <c r="J342" t="n">
-        <v>35.0112</v>
+        <v>34.0788</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.13</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3977</v>
+        <v>0.3947</v>
       </c>
       <c r="J343" t="n">
-        <v>11.1356</v>
+        <v>11.0516</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>1.04</v>
       </c>
       <c r="I344" t="n">
-        <v>0.1361</v>
+        <v>0.1495</v>
       </c>
       <c r="J344" t="n">
-        <v>3.8108</v>
+        <v>4.186</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>1.02</v>
       </c>
       <c r="I345" t="n">
-        <v>0.0646</v>
+        <v>0.0796</v>
       </c>
       <c r="J345" t="n">
-        <v>1.8088</v>
+        <v>2.2288</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.9</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3859</v>
+        <v>-0.3678</v>
       </c>
       <c r="J346" t="n">
-        <v>-10.8052</v>
+        <v>-10.2984</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.3</v>
       </c>
       <c r="I347" t="n">
-        <v>0.6865</v>
+        <v>0.6486</v>
       </c>
       <c r="J347" t="n">
-        <v>19.222</v>
+        <v>18.1608</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>0.92</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1126</v>
       </c>
       <c r="J348" t="n">
-        <v>-2.7216</v>
+        <v>-3.1528</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>0.85</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1719</v>
+        <v>-0.1891</v>
       </c>
       <c r="J349" t="n">
-        <v>-4.8132</v>
+        <v>-5.2948</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.72</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2992</v>
+        <v>-0.3151</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.377599999999999</v>
+        <v>-8.822800000000001</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.49</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5135</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J351" t="n">
-        <v>-14.378</v>
+        <v>-14.5516</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.51</v>
       </c>
       <c r="I352" t="n">
-        <v>1.1237</v>
+        <v>1.0911</v>
       </c>
       <c r="J352" t="n">
-        <v>24.7214</v>
+        <v>24.0042</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.5</v>
       </c>
       <c r="I353" t="n">
-        <v>1.1114</v>
+        <v>1.0778</v>
       </c>
       <c r="J353" t="n">
-        <v>24.4508</v>
+        <v>23.7116</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.28</v>
       </c>
       <c r="I354" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.6939</v>
       </c>
       <c r="J354" t="n">
-        <v>15.8466</v>
+        <v>15.2658</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.28</v>
       </c>
       <c r="I355" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.6939</v>
       </c>
       <c r="J355" t="n">
-        <v>15.8466</v>
+        <v>15.2658</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>1.18</v>
       </c>
       <c r="I356" t="n">
-        <v>0.4809</v>
+        <v>0.4802</v>
       </c>
       <c r="J356" t="n">
-        <v>10.5798</v>
+        <v>10.5644</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.3</v>
       </c>
       <c r="I357" t="n">
-        <v>0.9346</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="J357" t="n">
-        <v>20.5612</v>
+        <v>18.3744</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>0.65</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.3274</v>
+        <v>-0.3497</v>
       </c>
       <c r="J358" t="n">
-        <v>-7.2028</v>
+        <v>-7.6934</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.43</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.5305</v>
+        <v>-0.5412</v>
       </c>
       <c r="J359" t="n">
-        <v>-11.671</v>
+        <v>-11.9064</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.34</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.6169</v>
+        <v>-0.6207</v>
       </c>
       <c r="J360" t="n">
-        <v>-13.5718</v>
+        <v>-13.6554</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.26</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.6913</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.2702</v>
+        <v>-15.2086</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.13</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3426</v>
+        <v>0.3362</v>
       </c>
       <c r="J362" t="n">
-        <v>9.9354</v>
+        <v>9.7498</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.05</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1686</v>
+        <v>0.1692</v>
       </c>
       <c r="J363" t="n">
-        <v>4.8894</v>
+        <v>4.9068</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>0.82</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2059</v>
+        <v>-0.2223</v>
       </c>
       <c r="J364" t="n">
-        <v>-5.9711</v>
+        <v>-6.4467</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.2159</v>
+        <v>-0.2323</v>
       </c>
       <c r="J365" t="n">
-        <v>-6.2611</v>
+        <v>-6.7367</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.65</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.3704</v>
+        <v>-0.383</v>
       </c>
       <c r="J366" t="n">
-        <v>-10.7416</v>
+        <v>-11.107</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.7831</v>
+        <v>0.7372</v>
       </c>
       <c r="J367" t="n">
-        <v>22.7099</v>
+        <v>21.3788</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.18</v>
       </c>
       <c r="I368" t="n">
-        <v>0.5356</v>
+        <v>0.5177</v>
       </c>
       <c r="J368" t="n">
-        <v>15.5324</v>
+        <v>15.0133</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.13</v>
       </c>
       <c r="I369" t="n">
-        <v>0.4053</v>
+        <v>0.3998</v>
       </c>
       <c r="J369" t="n">
-        <v>11.7537</v>
+        <v>11.5942</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.96</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1882</v>
+        <v>-0.1852</v>
       </c>
       <c r="J370" t="n">
-        <v>-5.4578</v>
+        <v>-5.3708</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.9</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3745</v>
+        <v>-0.3598</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.8605</v>
+        <v>-10.4342</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.39</v>
       </c>
       <c r="I372" t="n">
-        <v>1.034</v>
+        <v>0.972</v>
       </c>
       <c r="J372" t="n">
-        <v>35.156</v>
+        <v>33.048</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.13</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4151</v>
+        <v>0.4065</v>
       </c>
       <c r="J373" t="n">
-        <v>14.1134</v>
+        <v>13.821</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.97</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.1437</v>
+        <v>-0.1448</v>
       </c>
       <c r="J374" t="n">
-        <v>-4.8858</v>
+        <v>-4.9232</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.92</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.3053</v>
+        <v>-0.2982</v>
       </c>
       <c r="J375" t="n">
-        <v>-10.3802</v>
+        <v>-10.1388</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.86</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.477</v>
+        <v>-0.4553</v>
       </c>
       <c r="J376" t="n">
-        <v>-16.218</v>
+        <v>-15.4802</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.21</v>
       </c>
       <c r="I377" t="n">
-        <v>0.5102</v>
+        <v>0.4898</v>
       </c>
       <c r="J377" t="n">
-        <v>17.3468</v>
+        <v>16.6532</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1106</v>
+        <v>-0.1259</v>
       </c>
       <c r="J378" t="n">
-        <v>-3.7604</v>
+        <v>-4.2806</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.86</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1631</v>
+        <v>-0.1798</v>
       </c>
       <c r="J379" t="n">
-        <v>-5.5454</v>
+        <v>-6.1132</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.72</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3011</v>
+        <v>-0.3166</v>
       </c>
       <c r="J380" t="n">
-        <v>-10.2374</v>
+        <v>-10.7644</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.65</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3676</v>
+        <v>-0.3807</v>
       </c>
       <c r="J381" t="n">
-        <v>-12.4984</v>
+        <v>-12.9438</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.62</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2729</v>
+        <v>1.2482</v>
       </c>
       <c r="J382" t="n">
-        <v>30.5496</v>
+        <v>29.9568</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.5</v>
       </c>
       <c r="I383" t="n">
-        <v>1.1242</v>
+        <v>1.0891</v>
       </c>
       <c r="J383" t="n">
-        <v>26.9808</v>
+        <v>26.1384</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.26</v>
       </c>
       <c r="I384" t="n">
-        <v>0.6877</v>
+        <v>0.6622</v>
       </c>
       <c r="J384" t="n">
-        <v>16.5048</v>
+        <v>15.8928</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>1.11</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3123</v>
+        <v>0.3234</v>
       </c>
       <c r="J385" t="n">
-        <v>7.4952</v>
+        <v>7.7616</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.9</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.4221</v>
+        <v>-0.3932</v>
       </c>
       <c r="J386" t="n">
-        <v>-10.1304</v>
+        <v>-9.4368</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>0.86</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.1347</v>
+        <v>-0.1579</v>
       </c>
       <c r="J387" t="n">
-        <v>-3.2328</v>
+        <v>-3.7896</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>0.75</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.2508</v>
+        <v>-0.272</v>
       </c>
       <c r="J388" t="n">
-        <v>-6.0192</v>
+        <v>-6.528</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>0.71</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.2887</v>
+        <v>-0.3089</v>
       </c>
       <c r="J389" t="n">
-        <v>-6.9288</v>
+        <v>-7.4136</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.68</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3152</v>
+        <v>-0.3348</v>
       </c>
       <c r="J390" t="n">
-        <v>-7.5648</v>
+        <v>-8.0352</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.5</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.4828</v>
+        <v>-0.494</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.5872</v>
+        <v>-11.856</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.6</v>
       </c>
       <c r="I392" t="n">
-        <v>1.271</v>
+        <v>1.2421</v>
       </c>
       <c r="J392" t="n">
-        <v>27.962</v>
+        <v>27.3262</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.2</v>
       </c>
       <c r="I393" t="n">
-        <v>0.5614</v>
+        <v>0.546</v>
       </c>
       <c r="J393" t="n">
-        <v>12.3508</v>
+        <v>12.012</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I394" t="n">
-        <v>0.4391</v>
+        <v>0.435</v>
       </c>
       <c r="J394" t="n">
-        <v>9.6602</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>1.09</v>
       </c>
       <c r="I395" t="n">
-        <v>0.2764</v>
+        <v>0.2855</v>
       </c>
       <c r="J395" t="n">
-        <v>6.0808</v>
+        <v>6.281</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.91</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3717</v>
+        <v>-0.3514</v>
       </c>
       <c r="J396" t="n">
-        <v>-8.1774</v>
+        <v>-7.7308</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.18</v>
       </c>
       <c r="I397" t="n">
-        <v>0.4923</v>
+        <v>0.4661</v>
       </c>
       <c r="J397" t="n">
-        <v>10.8306</v>
+        <v>10.2542</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>0.97</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.0216</v>
+        <v>-0.0362</v>
       </c>
       <c r="J398" t="n">
-        <v>-0.4752</v>
+        <v>-0.7964</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>0.79</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.2245</v>
+        <v>-0.2433</v>
       </c>
       <c r="J399" t="n">
-        <v>-4.939</v>
+        <v>-5.3526</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.58</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4228</v>
+        <v>-0.4352</v>
       </c>
       <c r="J400" t="n">
-        <v>-9.301600000000001</v>
+        <v>-9.574400000000001</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.46</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.5336</v>
+        <v>-0.5396</v>
       </c>
       <c r="J401" t="n">
-        <v>-11.7392</v>
+        <v>-11.8712</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.86</v>
       </c>
       <c r="I402" t="n">
-        <v>1.6262</v>
+        <v>1.6105</v>
       </c>
       <c r="J402" t="n">
-        <v>43.9074</v>
+        <v>43.4835</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3489</v>
+        <v>0.3486</v>
       </c>
       <c r="J403" t="n">
-        <v>9.420299999999999</v>
+        <v>9.4122</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.03</v>
       </c>
       <c r="I404" t="n">
-        <v>0.108</v>
+        <v>0.1205</v>
       </c>
       <c r="J404" t="n">
-        <v>2.916</v>
+        <v>3.2535</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.7029</v>
+        <v>-0.6543</v>
       </c>
       <c r="J405" t="n">
-        <v>-18.9783</v>
+        <v>-17.6661</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.75</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.7788</v>
+        <v>-0.7212</v>
       </c>
       <c r="J406" t="n">
-        <v>-21.0276</v>
+        <v>-19.4724</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.08</v>
       </c>
       <c r="I407" t="n">
-        <v>0.2521</v>
+        <v>0.2468</v>
       </c>
       <c r="J407" t="n">
-        <v>6.8067</v>
+        <v>6.6636</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>0.88</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.1414</v>
+        <v>-0.158</v>
       </c>
       <c r="J408" t="n">
-        <v>-3.8178</v>
+        <v>-4.266</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>0.83</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.1915</v>
+        <v>-0.209</v>
       </c>
       <c r="J409" t="n">
-        <v>-5.1705</v>
+        <v>-5.643</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.8</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2212</v>
+        <v>-0.2386</v>
       </c>
       <c r="J410" t="n">
-        <v>-5.9724</v>
+        <v>-6.4422</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.68</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3371</v>
+        <v>-0.3518</v>
       </c>
       <c r="J411" t="n">
-        <v>-9.101699999999999</v>
+        <v>-9.4986</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.59</v>
       </c>
       <c r="I412" t="n">
-        <v>1.2856</v>
+        <v>1.2528</v>
       </c>
       <c r="J412" t="n">
-        <v>33.4256</v>
+        <v>32.5728</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.23</v>
       </c>
       <c r="I413" t="n">
-        <v>0.6563</v>
+        <v>0.6263</v>
       </c>
       <c r="J413" t="n">
-        <v>17.0638</v>
+        <v>16.2838</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.11</v>
       </c>
       <c r="I414" t="n">
-        <v>0.3492</v>
+        <v>0.3488</v>
       </c>
       <c r="J414" t="n">
-        <v>9.0792</v>
+        <v>9.0688</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.89</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.4071</v>
+        <v>-0.3889</v>
       </c>
       <c r="J415" t="n">
-        <v>-10.5846</v>
+        <v>-10.1114</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.7</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.902</v>
+        <v>-0.829</v>
       </c>
       <c r="J416" t="n">
-        <v>-23.452</v>
+        <v>-21.554</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.11</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3173</v>
+        <v>0.3089</v>
       </c>
       <c r="J417" t="n">
-        <v>8.2498</v>
+        <v>8.0314</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.04</v>
       </c>
       <c r="I418" t="n">
-        <v>0.1581</v>
+        <v>0.1551</v>
       </c>
       <c r="J418" t="n">
-        <v>4.1106</v>
+        <v>4.0326</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.8</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.2212</v>
+        <v>-0.2386</v>
       </c>
       <c r="J419" t="n">
-        <v>-5.7512</v>
+        <v>-6.2036</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.68</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3371</v>
+        <v>-0.3518</v>
       </c>
       <c r="J420" t="n">
-        <v>-8.7646</v>
+        <v>-9.146800000000001</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.64</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3748</v>
+        <v>-0.3881</v>
       </c>
       <c r="J421" t="n">
-        <v>-9.7448</v>
+        <v>-10.0906</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1617/event_1617_evp_summary.xlsx
+++ b/database/event/1617/event_1617_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.2863</v>
+        <v>6.2615</v>
       </c>
       <c r="C2" t="n">
-        <v>5.8962</v>
+        <v>5.8729</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2374</v>
+        <v>2.2466</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2863</v>
+        <v>6.2615</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0487</v>
+        <v>2.037</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2376</v>
+        <v>4.2246</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0487</v>
+        <v>2.037</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1015</v>
+        <v>2.0914</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2376</v>
+        <v>4.2246</v>
       </c>
       <c r="K2" t="n">
         <v>128</v>
@@ -529,7 +529,7 @@
         <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>6.3391</v>
+        <v>6.316</v>
       </c>
       <c r="N2" t="n">
         <v>279</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3897</v>
+        <v>5.3655</v>
       </c>
       <c r="C3" t="n">
-        <v>5.0552</v>
+        <v>5.0325</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8293</v>
+        <v>1.8385</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3897</v>
+        <v>5.3655</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3219</v>
+        <v>1.2723</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0678</v>
+        <v>4.0932</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3219</v>
+        <v>1.2723</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3219</v>
+        <v>1.2723</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0678</v>
+        <v>4.0932</v>
       </c>
       <c r="K3" t="n">
         <v>47</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3897</v>
+        <v>5.365500000000001</v>
       </c>
       <c r="N3" t="n">
         <v>261</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.1984</v>
+        <v>4.1048</v>
       </c>
       <c r="C4" t="n">
-        <v>3.9379</v>
+        <v>3.8501</v>
       </c>
       <c r="D4" t="n">
-        <v>1.287</v>
+        <v>1.2641</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1984</v>
+        <v>4.1048</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2177</v>
+        <v>2.2133</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9807</v>
+        <v>1.8916</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2177</v>
+        <v>2.2133</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2748</v>
+        <v>2.2724</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9807</v>
+        <v>1.8916</v>
       </c>
       <c r="K4" t="n">
         <v>130</v>
@@ -621,7 +621,7 @@
         <v>157</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2555</v>
+        <v>4.164</v>
       </c>
       <c r="N4" t="n">
         <v>287</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.8605</v>
+        <v>3.9053</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6209</v>
+        <v>3.663</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1332</v>
+        <v>1.1733</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8605</v>
+        <v>3.9053</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7594</v>
+        <v>1.745</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1011</v>
+        <v>2.1603</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7594</v>
+        <v>1.745</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7594</v>
+        <v>1.745</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1011</v>
+        <v>2.1603</v>
       </c>
       <c r="K5" t="n">
         <v>47</v>
@@ -667,7 +667,7 @@
         <v>214</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8605</v>
+        <v>3.9053</v>
       </c>
       <c r="N5" t="n">
         <v>261</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.706</v>
+        <v>3.7044</v>
       </c>
       <c r="C6" t="n">
-        <v>3.476</v>
+        <v>3.4745</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0628</v>
+        <v>1.0817</v>
       </c>
       <c r="E6" t="n">
-        <v>3.706</v>
+        <v>3.7044</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6488</v>
+        <v>1.6172</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0572</v>
+        <v>2.0872</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6488</v>
+        <v>1.6172</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6488</v>
+        <v>1.6172</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0572</v>
+        <v>2.0872</v>
       </c>
       <c r="K6" t="n">
         <v>47</v>
@@ -713,7 +713,7 @@
         <v>214</v>
       </c>
       <c r="M6" t="n">
-        <v>3.706</v>
+        <v>3.7044</v>
       </c>
       <c r="N6" t="n">
         <v>261</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8823</v>
+        <v>2.9482</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7034</v>
+        <v>2.7652</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6879</v>
+        <v>0.7373</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8823</v>
+        <v>2.9482</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8761</v>
+        <v>0.9221</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0062</v>
+        <v>2.0261</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8761</v>
+        <v>0.9221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8761</v>
+        <v>0.9221</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0062</v>
+        <v>2.0261</v>
       </c>
       <c r="K7" t="n">
         <v>47</v>
@@ -759,7 +759,7 @@
         <v>214</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8823</v>
+        <v>2.9482</v>
       </c>
       <c r="N7" t="n">
         <v>261</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8012</v>
+        <v>2.8009</v>
       </c>
       <c r="C8" t="n">
-        <v>2.6274</v>
+        <v>2.6271</v>
       </c>
       <c r="D8" t="n">
-        <v>0.651</v>
+        <v>0.6702</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8012</v>
+        <v>2.8009</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0684</v>
+        <v>2.0727</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7328</v>
+        <v>0.7282</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0684</v>
+        <v>2.0727</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0684</v>
+        <v>2.0727</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7328</v>
+        <v>0.7282</v>
       </c>
       <c r="K8" t="n">
         <v>57</v>
@@ -805,7 +805,7 @@
         <v>62</v>
       </c>
       <c r="M8" t="n">
-        <v>2.8012</v>
+        <v>2.8009</v>
       </c>
       <c r="N8" t="n">
         <v>119</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5243</v>
+        <v>2.465</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3677</v>
+        <v>2.312</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5249</v>
+        <v>0.5171</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5243</v>
+        <v>2.465</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3251</v>
+        <v>1.3063</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1992</v>
+        <v>1.1587</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3251</v>
+        <v>1.3063</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3251</v>
+        <v>1.3063</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1992</v>
+        <v>1.1587</v>
       </c>
       <c r="K9" t="n">
         <v>47</v>
@@ -851,7 +851,7 @@
         <v>214</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5243</v>
+        <v>2.465</v>
       </c>
       <c r="N9" t="n">
         <v>261</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4475</v>
+        <v>2.315</v>
       </c>
       <c r="C10" t="n">
-        <v>2.2956</v>
+        <v>2.1713</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4899</v>
+        <v>0.4488</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4475</v>
+        <v>2.315</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3182</v>
+        <v>2.2572</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1293</v>
+        <v>0.0578</v>
       </c>
       <c r="H10" t="n">
-        <v>2.349</v>
+        <v>2.2572</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4095</v>
+        <v>2.3175</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1293</v>
+        <v>0.0578</v>
       </c>
       <c r="K10" t="n">
         <v>105</v>
@@ -897,7 +897,7 @@
         <v>68</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5388</v>
+        <v>2.3753</v>
       </c>
       <c r="N10" t="n">
         <v>173</v>
@@ -906,231 +906,231 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0572</v>
+        <v>2.033</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9295</v>
+        <v>1.9068</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3123</v>
+        <v>0.3203</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0572</v>
+        <v>2.033</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3247</v>
+        <v>2.033</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2675</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3632</v>
+        <v>2.033</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4241</v>
+        <v>2.033</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2675</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="L11" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1566</v>
+        <v>2.033</v>
       </c>
       <c r="N11" t="n">
-        <v>173</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0127</v>
+        <v>1.9979</v>
       </c>
       <c r="C12" t="n">
-        <v>1.8878</v>
+        <v>1.8739</v>
       </c>
       <c r="D12" t="n">
-        <v>0.292</v>
+        <v>0.3044</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0127</v>
+        <v>1.9979</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0127</v>
+        <v>2.308</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.3101</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0127</v>
+        <v>2.339</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0127</v>
+        <v>2.4015</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.3101</v>
       </c>
       <c r="K12" t="n">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0127</v>
+        <v>2.0914</v>
       </c>
       <c r="N12" t="n">
-        <v>52</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9596</v>
+        <v>1.9615</v>
       </c>
       <c r="C13" t="n">
-        <v>1.838</v>
+        <v>1.8398</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2678</v>
+        <v>0.2878</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9596</v>
+        <v>1.9615</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2347</v>
+        <v>2.2449</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1943</v>
+        <v>-0.2834</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2347</v>
+        <v>2.2449</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2407</v>
+        <v>2.2449</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1943</v>
+        <v>-0.2834</v>
       </c>
       <c r="K13" t="n">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="L13" t="n">
-        <v>151</v>
+        <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9536</v>
+        <v>1.9615</v>
       </c>
       <c r="N13" t="n">
-        <v>279</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.9121</v>
+        <v>1.9224</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7934</v>
+        <v>1.8031</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2462</v>
+        <v>0.27</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9121</v>
+        <v>1.9224</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2314</v>
+        <v>2.2778</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3193</v>
+        <v>-0.3554</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2314</v>
+        <v>2.2778</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2314</v>
+        <v>2.2778</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3193</v>
+        <v>-0.3554</v>
       </c>
       <c r="K14" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9121</v>
+        <v>1.9224</v>
       </c>
       <c r="N14" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8655</v>
+        <v>1.8937</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7497</v>
+        <v>1.7762</v>
       </c>
       <c r="D15" t="n">
-        <v>0.225</v>
+        <v>0.2569</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8655</v>
+        <v>1.8937</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2586</v>
+        <v>-0.2528</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3931</v>
+        <v>2.1465</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2586</v>
+        <v>-0.2528</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2586</v>
+        <v>-0.2596</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3931</v>
+        <v>2.1465</v>
       </c>
       <c r="K15" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="L15" t="n">
-        <v>59</v>
+        <v>151</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8655</v>
+        <v>1.8869</v>
       </c>
       <c r="N15" t="n">
-        <v>115</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7571</v>
+        <v>1.6866</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6481</v>
+        <v>1.5819</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1757</v>
+        <v>0.1625</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7571</v>
+        <v>1.6866</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6381</v>
+        <v>2.6216</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.881</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>3.049</v>
+        <v>3.0578</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1276</v>
+        <v>3.1395</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.881</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>128</v>
@@ -1173,7 +1173,7 @@
         <v>151</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2466</v>
+        <v>2.2045</v>
       </c>
       <c r="N16" t="n">
         <v>279</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7444</v>
+        <v>1.6657</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6361</v>
+        <v>1.5623</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1699</v>
+        <v>0.153</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7444</v>
+        <v>1.6657</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7444</v>
+        <v>1.1011</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.5646</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7444</v>
+        <v>1.1011</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7444</v>
+        <v>1.1305</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.5646</v>
       </c>
       <c r="K17" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7444</v>
+        <v>1.6951</v>
       </c>
       <c r="N17" t="n">
-        <v>132</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6324</v>
+        <v>1.6567</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5311</v>
+        <v>1.5539</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1189</v>
+        <v>0.1489</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6324</v>
+        <v>1.6567</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0133</v>
+        <v>1.6567</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6191</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0133</v>
+        <v>1.6567</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0394</v>
+        <v>1.6567</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6191</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="L18" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6585</v>
+        <v>1.6567</v>
       </c>
       <c r="N18" t="n">
-        <v>287</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.579</v>
+        <v>1.5259</v>
       </c>
       <c r="C19" t="n">
-        <v>1.481</v>
+        <v>1.4312</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0946</v>
+        <v>0.0893</v>
       </c>
       <c r="E19" t="n">
-        <v>1.579</v>
+        <v>1.5259</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6472</v>
+        <v>1.6038</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0682</v>
+        <v>-0.0779</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6472</v>
+        <v>1.6038</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6896</v>
+        <v>1.6467</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0682</v>
+        <v>-0.0779</v>
       </c>
       <c r="K19" t="n">
         <v>130</v>
@@ -1311,7 +1311,7 @@
         <v>157</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6214</v>
+        <v>1.5688</v>
       </c>
       <c r="N19" t="n">
         <v>287</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2619</v>
+        <v>1.2592</v>
       </c>
       <c r="C20" t="n">
-        <v>1.1836</v>
+        <v>1.1811</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0498</v>
+        <v>-0.0322</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2619</v>
+        <v>1.2592</v>
       </c>
       <c r="F20" t="n">
-        <v>2.8874</v>
+        <v>2.8527</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6255</v>
+        <v>-1.5935</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5948</v>
+        <v>3.5873</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6874</v>
+        <v>3.6832</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6255</v>
+        <v>-1.5935</v>
       </c>
       <c r="K20" t="n">
         <v>103</v>
@@ -1357,7 +1357,7 @@
         <v>91</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0619</v>
+        <v>2.0897</v>
       </c>
       <c r="N20" t="n">
         <v>194</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0709</v>
+        <v>1.0162</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0044</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1367</v>
+        <v>-0.1429</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0709</v>
+        <v>1.0162</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7366</v>
+        <v>1.7262</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6657</v>
+        <v>-0.71</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7366</v>
+        <v>1.7262</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7813</v>
+        <v>1.7723</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6657</v>
+        <v>-0.71</v>
       </c>
       <c r="K21" t="n">
         <v>103</v>
@@ -1403,7 +1403,7 @@
         <v>91</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1156</v>
+        <v>1.0623</v>
       </c>
       <c r="N21" t="n">
         <v>194</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WorldEdit</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0428</v>
+        <v>0.9879</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9781</v>
+        <v>0.9266</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1495</v>
+        <v>-0.1558</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0428</v>
+        <v>0.9879</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0428</v>
+        <v>0.9879</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0428</v>
+        <v>0.9879</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0428</v>
+        <v>0.9879</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0428</v>
+        <v>0.9879</v>
       </c>
       <c r="N22" t="n">
-        <v>46</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0427</v>
+        <v>0.9547</v>
       </c>
       <c r="C23" t="n">
-        <v>0.978</v>
+        <v>0.8955</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1495</v>
+        <v>-0.1709</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0427</v>
+        <v>0.9547</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0427</v>
+        <v>0.9547</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0427</v>
+        <v>0.9547</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0427</v>
+        <v>0.9547</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>99</v>
+        <v>132</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0427</v>
+        <v>0.9547</v>
       </c>
       <c r="N23" t="n">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>WorldEdit</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8781</v>
+        <v>0.9395</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8236</v>
+        <v>0.8812</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2245</v>
+        <v>-0.1778</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8781</v>
+        <v>0.9395</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8781</v>
+        <v>0.9395</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8781</v>
+        <v>0.9395</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8781</v>
+        <v>0.9395</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>132</v>
+        <v>46</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8781</v>
+        <v>0.9395</v>
       </c>
       <c r="N24" t="n">
-        <v>132</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8694</v>
+        <v>0.9244</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8154</v>
+        <v>0.867</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2284</v>
+        <v>-0.1847</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8694</v>
+        <v>0.9244</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2181</v>
+        <v>0.2848</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6513</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2181</v>
+        <v>0.2848</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2237</v>
+        <v>0.2924</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6513</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>103</v>
@@ -1587,7 +1587,7 @@
         <v>91</v>
       </c>
       <c r="M25" t="n">
-        <v>0.875</v>
+        <v>0.9319999999999999</v>
       </c>
       <c r="N25" t="n">
         <v>194</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8198</v>
+        <v>0.883</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7689</v>
+        <v>0.8282</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.251</v>
+        <v>-0.2035</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8198</v>
+        <v>0.883</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0858</v>
+        <v>1.1321</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.266</v>
+        <v>-0.2491</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0858</v>
+        <v>1.1321</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0858</v>
+        <v>1.1321</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.266</v>
+        <v>-0.2491</v>
       </c>
       <c r="K26" t="n">
         <v>57</v>
@@ -1633,7 +1633,7 @@
         <v>62</v>
       </c>
       <c r="M26" t="n">
-        <v>0.8198000000000001</v>
+        <v>0.8830000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>119</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.8693</v>
       </c>
       <c r="C27" t="n">
-        <v>0.72</v>
+        <v>0.8154</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.2748</v>
+        <v>-0.2098</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.8693</v>
       </c>
       <c r="F27" t="n">
-        <v>1.1198</v>
+        <v>1.1923</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.3522</v>
+        <v>-0.323</v>
       </c>
       <c r="H27" t="n">
-        <v>1.1198</v>
+        <v>1.1923</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1198</v>
+        <v>1.1923</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3522</v>
+        <v>-0.323</v>
       </c>
       <c r="K27" t="n">
         <v>44</v>
@@ -1679,7 +1679,7 @@
         <v>50</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7675999999999998</v>
+        <v>0.8693</v>
       </c>
       <c r="N27" t="n">
         <v>94</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5831</v>
+        <v>0.6482</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.608</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.3588</v>
+        <v>-0.3105</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5831</v>
+        <v>0.6482</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7187</v>
+        <v>-0.6677</v>
       </c>
       <c r="G28" t="n">
-        <v>1.3018</v>
+        <v>1.3159</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7187</v>
+        <v>-0.6677</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7372</v>
+        <v>-0.6855</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3018</v>
+        <v>1.3159</v>
       </c>
       <c r="K28" t="n">
         <v>128</v>
@@ -1725,7 +1725,7 @@
         <v>151</v>
       </c>
       <c r="M28" t="n">
-        <v>0.5646000000000001</v>
+        <v>0.6304000000000001</v>
       </c>
       <c r="N28" t="n">
         <v>279</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5652</v>
+        <v>0.5038</v>
       </c>
       <c r="C29" t="n">
-        <v>0.5301</v>
+        <v>0.4725</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.3669</v>
+        <v>-0.3763</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5652</v>
+        <v>0.5038</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5652</v>
+        <v>0.125</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.3788</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5652</v>
+        <v>0.125</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5652</v>
+        <v>0.1283</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.3788</v>
       </c>
       <c r="K29" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M29" t="n">
-        <v>0.5652</v>
+        <v>0.5071</v>
       </c>
       <c r="N29" t="n">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.553</v>
+        <v>0.4947</v>
       </c>
       <c r="C30" t="n">
-        <v>0.5187</v>
+        <v>0.464</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.3725</v>
+        <v>-0.3804</v>
       </c>
       <c r="E30" t="n">
-        <v>0.553</v>
+        <v>0.4947</v>
       </c>
       <c r="F30" t="n">
-        <v>0.553</v>
+        <v>0.4947</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.553</v>
+        <v>0.4947</v>
       </c>
       <c r="I30" t="n">
-        <v>0.553</v>
+        <v>0.4947</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.553</v>
+        <v>0.4947</v>
       </c>
       <c r="N30" t="n">
         <v>133</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5113</v>
+        <v>0.481</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4796</v>
+        <v>0.4512</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.3914</v>
+        <v>-0.3867</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5113</v>
+        <v>0.481</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5113</v>
+        <v>0.481</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5113</v>
+        <v>0.481</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5113</v>
+        <v>0.481</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.5113</v>
+        <v>0.481</v>
       </c>
       <c r="N31" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4649</v>
+        <v>0.4181</v>
       </c>
       <c r="C32" t="n">
-        <v>0.436</v>
+        <v>0.3922</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4126</v>
+        <v>-0.4153</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4649</v>
+        <v>0.4181</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1417</v>
+        <v>0.4181</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3232</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1417</v>
+        <v>0.4181</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1454</v>
+        <v>0.4181</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3232</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="L32" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.4686</v>
+        <v>0.4181</v>
       </c>
       <c r="N32" t="n">
-        <v>194</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4643</v>
+        <v>0.3884</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4355</v>
+        <v>0.3643</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.4128</v>
+        <v>-0.4289</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4643</v>
+        <v>0.3884</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3435</v>
+        <v>0.2949</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1208</v>
+        <v>0.0935</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3435</v>
+        <v>0.2949</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3435</v>
+        <v>0.2949</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1208</v>
+        <v>0.0935</v>
       </c>
       <c r="K33" t="n">
         <v>44</v>
@@ -1955,7 +1955,7 @@
         <v>50</v>
       </c>
       <c r="M33" t="n">
-        <v>0.4643</v>
+        <v>0.3884</v>
       </c>
       <c r="N33" t="n">
         <v>94</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.3787</v>
+        <v>0.3712</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3552</v>
+        <v>0.3482</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4518</v>
+        <v>-0.4367</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3787</v>
+        <v>0.3712</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3787</v>
+        <v>0.3712</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3787</v>
+        <v>0.3712</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3787</v>
+        <v>0.3712</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.3787</v>
+        <v>0.3712</v>
       </c>
       <c r="N34" t="n">
-        <v>132</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.3458</v>
+        <v>0.3587</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3243</v>
+        <v>0.3364</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.4668</v>
+        <v>-0.4424</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3458</v>
+        <v>0.3587</v>
       </c>
       <c r="F35" t="n">
-        <v>0.468</v>
+        <v>0.4844</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1222</v>
+        <v>-0.1257</v>
       </c>
       <c r="H35" t="n">
-        <v>0.468</v>
+        <v>0.4844</v>
       </c>
       <c r="I35" t="n">
-        <v>0.468</v>
+        <v>0.4844</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.1222</v>
+        <v>-0.1257</v>
       </c>
       <c r="K35" t="n">
         <v>57</v>
@@ -2047,7 +2047,7 @@
         <v>62</v>
       </c>
       <c r="M35" t="n">
-        <v>0.3458</v>
+        <v>0.3587</v>
       </c>
       <c r="N35" t="n">
         <v>119</v>
@@ -2056,139 +2056,139 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.3359</v>
+        <v>0.3402</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3151</v>
+        <v>0.3191</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.4713</v>
+        <v>-0.4508</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3359</v>
+        <v>0.3402</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3359</v>
+        <v>0.326</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.0142</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3359</v>
+        <v>0.326</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3359</v>
+        <v>0.3347</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.0142</v>
       </c>
       <c r="K36" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="M36" t="n">
-        <v>0.3359</v>
+        <v>0.3489</v>
       </c>
       <c r="N36" t="n">
-        <v>99</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.3232</v>
+        <v>0.3165</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3031</v>
+        <v>0.2969</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.4771</v>
+        <v>-0.4616</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3232</v>
+        <v>0.3165</v>
       </c>
       <c r="F37" t="n">
-        <v>0.297</v>
+        <v>0.3165</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0262</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.297</v>
+        <v>0.3165</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3047</v>
+        <v>0.3165</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0262</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L37" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.3309</v>
+        <v>0.3165</v>
       </c>
       <c r="N37" t="n">
-        <v>194</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.323</v>
+        <v>0.2836</v>
       </c>
       <c r="C38" t="n">
-        <v>0.303</v>
+        <v>0.266</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.4772</v>
+        <v>-0.4766</v>
       </c>
       <c r="E38" t="n">
-        <v>0.323</v>
+        <v>0.2836</v>
       </c>
       <c r="F38" t="n">
-        <v>0.493</v>
+        <v>0.2836</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.493</v>
+        <v>0.2836</v>
       </c>
       <c r="I38" t="n">
-        <v>0.493</v>
+        <v>0.2836</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>44</v>
+        <v>106</v>
       </c>
       <c r="L38" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.323</v>
+        <v>0.2836</v>
       </c>
       <c r="N38" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.268</v>
+        <v>0.2524</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2514</v>
+        <v>0.2367</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.5022</v>
+        <v>-0.4908</v>
       </c>
       <c r="E39" t="n">
-        <v>0.268</v>
+        <v>0.2524</v>
       </c>
       <c r="F39" t="n">
-        <v>0.604</v>
+        <v>0.5531</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.336</v>
+        <v>-0.3007</v>
       </c>
       <c r="H39" t="n">
-        <v>0.604</v>
+        <v>0.5531</v>
       </c>
       <c r="I39" t="n">
-        <v>0.604</v>
+        <v>0.5531</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.336</v>
+        <v>-0.3007</v>
       </c>
       <c r="K39" t="n">
         <v>44</v>
@@ -2231,7 +2231,7 @@
         <v>50</v>
       </c>
       <c r="M39" t="n">
-        <v>0.268</v>
+        <v>0.2524</v>
       </c>
       <c r="N39" t="n">
         <v>94</v>
@@ -2240,323 +2240,323 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.2565</v>
+        <v>0.2131</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2406</v>
+        <v>0.1999</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.5074</v>
+        <v>-0.5087</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2565</v>
+        <v>0.2131</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3944</v>
+        <v>0.4416</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1379</v>
+        <v>-0.2285</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3944</v>
+        <v>0.4416</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4046</v>
+        <v>0.4416</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1379</v>
+        <v>-0.2285</v>
       </c>
       <c r="K40" t="n">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="L40" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2667</v>
+        <v>0.2131</v>
       </c>
       <c r="N40" t="n">
-        <v>173</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>Maikelele</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.2554</v>
+        <v>0.1585</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2396</v>
+        <v>0.1487</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.5079</v>
+        <v>-0.5336</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2554</v>
+        <v>0.1585</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2554</v>
+        <v>1.406</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-1.2475</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2554</v>
+        <v>1.406</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2554</v>
+        <v>1.4435</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-1.2475</v>
       </c>
       <c r="K41" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M41" t="n">
-        <v>0.2554</v>
+        <v>0.196</v>
       </c>
       <c r="N41" t="n">
-        <v>106</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Maikelele</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.0882</v>
+        <v>0.068</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0827</v>
+        <v>0.0638</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5841</v>
+        <v>-0.5748</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0882</v>
+        <v>0.068</v>
       </c>
       <c r="F42" t="n">
-        <v>1.4563</v>
+        <v>0.3361</v>
       </c>
       <c r="G42" t="n">
-        <v>-1.3681</v>
+        <v>-0.2681</v>
       </c>
       <c r="H42" t="n">
-        <v>1.4563</v>
+        <v>0.3361</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4938</v>
+        <v>0.345</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.3681</v>
+        <v>-0.2681</v>
       </c>
       <c r="K42" t="n">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="L42" t="n">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1256999999999999</v>
+        <v>0.07689999999999997</v>
       </c>
       <c r="N42" t="n">
-        <v>287</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.0223</v>
+        <v>0.0289</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0209</v>
+        <v>0.0271</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.6141</v>
+        <v>-0.5926</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0223</v>
+        <v>0.0289</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0223</v>
+        <v>0.0289</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0223</v>
+        <v>0.0289</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0223</v>
+        <v>0.0289</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.0223</v>
+        <v>0.0289</v>
       </c>
       <c r="N43" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0066</v>
+        <v>-0.019</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0062</v>
+        <v>-0.0178</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6212</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0066</v>
+        <v>-0.019</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0066</v>
+        <v>-0.1693</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.1503</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0066</v>
+        <v>-0.1693</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0066</v>
+        <v>-0.1693</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.1503</v>
       </c>
       <c r="K44" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M44" t="n">
-        <v>0.0066</v>
+        <v>-0.01900000000000002</v>
       </c>
       <c r="N44" t="n">
-        <v>61</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-0.0032</v>
+        <v>-0.0304</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.003</v>
+        <v>-0.0285</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.6257</v>
+        <v>-0.6196</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.0032</v>
+        <v>-0.0304</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.1866</v>
+        <v>-0.0304</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1834</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.1866</v>
+        <v>-0.0304</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1866</v>
+        <v>-0.0304</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1834</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="L45" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.003199999999999981</v>
+        <v>-0.0304</v>
       </c>
       <c r="N45" t="n">
-        <v>115</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-0.0262</v>
+        <v>-0.0345</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0246</v>
+        <v>-0.0324</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6361</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.0262</v>
+        <v>-0.0345</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.0262</v>
+        <v>-0.0345</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.0262</v>
+        <v>-0.0345</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0262</v>
+        <v>-0.0345</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.0262</v>
+        <v>-0.0345</v>
       </c>
       <c r="N46" t="n">
-        <v>133</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.0362</v>
+        <v>-0.0601</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.034</v>
+        <v>-0.0564</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6407</v>
+        <v>-0.6332</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.0362</v>
+        <v>-0.0601</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.0362</v>
+        <v>-0.0601</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.0362</v>
+        <v>-0.0601</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.0362</v>
+        <v>-0.0601</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.0362</v>
+        <v>-0.0601</v>
       </c>
       <c r="N47" t="n">
         <v>55</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-0.0618</v>
+        <v>-0.0764</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.058</v>
+        <v>-0.0717</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.6523</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.0618</v>
+        <v>-0.0764</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.0618</v>
+        <v>-0.0764</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.0618</v>
+        <v>-0.0764</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.0618</v>
+        <v>-0.0764</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.0618</v>
+        <v>-0.0764</v>
       </c>
       <c r="N48" t="n">
         <v>55</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.6636</v>
+        <v>-0.6464</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="N49" t="n">
         <v>106</v>
@@ -2700,47 +2700,47 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pronax</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.1323</v>
+        <v>-0.1747</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.1241</v>
+        <v>-0.1639</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.6844</v>
+        <v>-0.6854</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.1323</v>
+        <v>-0.1747</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8677</v>
+        <v>-0.1747</v>
       </c>
       <c r="G50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8677</v>
+        <v>-0.1747</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8901</v>
+        <v>-0.1747</v>
       </c>
       <c r="J50" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L50" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.1099</v>
+        <v>-0.1747</v>
       </c>
       <c r="N50" t="n">
-        <v>173</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1609</v>
+        <v>-0.1787</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.1509</v>
+        <v>-0.1676</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.6974</v>
+        <v>-0.6872</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1609</v>
+        <v>-0.1787</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.1609</v>
+        <v>-0.1787</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.1609</v>
+        <v>-0.1787</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1609</v>
+        <v>-0.1787</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1609</v>
+        <v>-0.1787</v>
       </c>
       <c r="N51" t="n">
         <v>61</v>
@@ -2792,231 +2792,231 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>pronax</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.1715</v>
+        <v>-0.2162</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.1609</v>
+        <v>-0.2028</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.7023</v>
+        <v>-0.7043</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1715</v>
+        <v>-0.2162</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1715</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1715</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1715</v>
+        <v>0.8047</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K52" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1715</v>
+        <v>-0.1953</v>
       </c>
       <c r="N52" t="n">
-        <v>106</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>markeloff</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2722</v>
+        <v>-0.2403</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.2553</v>
+        <v>-0.2254</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.7481</v>
+        <v>-0.7153</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2722</v>
+        <v>-0.2403</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2722</v>
+        <v>-0.2403</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2722</v>
+        <v>-0.2403</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2722</v>
+        <v>-0.2403</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2722</v>
+        <v>-0.2403</v>
       </c>
       <c r="N53" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2728</v>
+        <v>-0.2487</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.2559</v>
+        <v>-0.2333</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.7484</v>
+        <v>-0.7191</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2728</v>
+        <v>-0.2487</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.2728</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.6046</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.2728</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2728</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>0.6046</v>
       </c>
       <c r="K54" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2728</v>
+        <v>-0.2486999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>61</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>markeloff</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2908</v>
+        <v>-0.2987</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2728</v>
+        <v>-0.2802</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.7566000000000001</v>
+        <v>-0.7419</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2908</v>
+        <v>-0.2987</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3663</v>
+        <v>-0.2987</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.6571</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3663</v>
+        <v>-0.2987</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3663</v>
+        <v>-0.2987</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.6571</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L55" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.2908</v>
+        <v>-0.2987</v>
       </c>
       <c r="N55" t="n">
-        <v>119</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2936</v>
+        <v>-0.3099</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.2754</v>
+        <v>-0.2907</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.7579</v>
+        <v>-0.747</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2936</v>
+        <v>-0.3099</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.9149</v>
+        <v>0.3302</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6213</v>
+        <v>-0.6401</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.9149</v>
+        <v>0.3302</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9149</v>
+        <v>0.3302</v>
       </c>
       <c r="J56" t="n">
-        <v>0.6213</v>
+        <v>-0.6401</v>
       </c>
       <c r="K56" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L56" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2936000000000001</v>
+        <v>-0.3099</v>
       </c>
       <c r="N56" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57">
@@ -3026,28 +3026,28 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3576</v>
+        <v>-0.3315</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3354</v>
+        <v>-0.3109</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.787</v>
+        <v>-0.7568</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3576</v>
+        <v>-0.3315</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3576</v>
+        <v>-0.3315</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3576</v>
+        <v>-0.3315</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3576</v>
+        <v>-0.3315</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3576</v>
+        <v>-0.3315</v>
       </c>
       <c r="N57" t="n">
         <v>46</v>
@@ -3072,28 +3072,28 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5048</v>
+        <v>-0.4763</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.4735</v>
+        <v>-0.4467</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.854</v>
+        <v>-0.8228</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5048</v>
+        <v>-0.4763</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5048</v>
+        <v>-0.4763</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5048</v>
+        <v>-0.4763</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5048</v>
+        <v>-0.4763</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5048</v>
+        <v>-0.4763</v>
       </c>
       <c r="N58" t="n">
         <v>52</v>
@@ -3114,78 +3114,78 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>rallen</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.5151</v>
+        <v>-0.5097</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.4831</v>
+        <v>-0.4781</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.8587</v>
+        <v>-0.838</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5151</v>
+        <v>-0.5097</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5151</v>
+        <v>-0.5097</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.5151</v>
+        <v>-0.5097</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.5151</v>
+        <v>-0.5097</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.5151</v>
+        <v>-0.5097</v>
       </c>
       <c r="N59" t="n">
-        <v>99</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rallen</t>
+          <t>peet</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.5414</v>
+        <v>-0.5127</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.5078</v>
+        <v>-0.4809</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.8707</v>
+        <v>-0.8393</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5414</v>
+        <v>-0.5127</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5414</v>
+        <v>-0.5127</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5414</v>
+        <v>-0.5127</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5414</v>
+        <v>-0.5127</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.5414</v>
+        <v>-0.5127</v>
       </c>
       <c r="N60" t="n">
         <v>55</v>
@@ -3206,308 +3206,308 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>peet</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.548</v>
+        <v>-0.5465</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.514</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.8737</v>
+        <v>-0.8547</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.548</v>
+        <v>-0.5465</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.548</v>
+        <v>-0.5465</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.548</v>
+        <v>-0.5465</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.548</v>
+        <v>-0.5465</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.548</v>
+        <v>-0.5465</v>
       </c>
       <c r="N61" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5766</v>
+        <v>-0.5745</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.8867</v>
+        <v>-0.8675</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5766</v>
+        <v>-0.5745</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5766</v>
+        <v>-0.5745</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5766</v>
+        <v>-0.5745</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5766</v>
+        <v>-0.5745</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5766</v>
+        <v>-0.5745</v>
       </c>
       <c r="N62" t="n">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6301</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.6481</v>
+        <v>-0.591</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.9388</v>
+        <v>-0.8928</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6301</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.7333</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>0.1032</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.7333</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.7529</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.1032</v>
       </c>
       <c r="K63" t="n">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>52</v>
+        <v>287</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7295</v>
+        <v>-0.6924</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.6842</v>
+        <v>-0.6494</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9563</v>
+        <v>-0.9212</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7295</v>
+        <v>-0.6924</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7295</v>
+        <v>-0.6924</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7295</v>
+        <v>-0.6924</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7295</v>
+        <v>-0.6924</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7295</v>
+        <v>-0.6924</v>
       </c>
       <c r="N64" t="n">
-        <v>99</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.7511</v>
+        <v>-0.7584</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.7045</v>
+        <v>-0.7113</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9661</v>
+        <v>-0.9513</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.7511</v>
+        <v>-0.7584</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8218</v>
+        <v>-0.7584</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0707</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8218</v>
+        <v>-0.7584</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.843</v>
+        <v>-0.7584</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0707</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="L65" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.7723</v>
+        <v>-0.7584</v>
       </c>
       <c r="N65" t="n">
-        <v>287</v>
+        <v>99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>DavCost</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8025</v>
+        <v>-0.8199</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.7527</v>
+        <v>-0.769</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9895</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8025</v>
+        <v>-0.8199</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8017</v>
+        <v>-0.8199</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8017</v>
+        <v>-0.8199</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8017</v>
+        <v>-0.8199</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L66" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8025</v>
+        <v>-0.8199</v>
       </c>
       <c r="N66" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DavCost</t>
+          <t>B1ad3</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.833</v>
+        <v>-0.8331</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.7813</v>
+        <v>-0.7814</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.0034</v>
+        <v>-0.9853</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.833</v>
+        <v>-0.8331</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.833</v>
+        <v>-0.8331</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.833</v>
+        <v>-0.8331</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.833</v>
+        <v>-0.8331</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.833</v>
+        <v>-0.8331</v>
       </c>
       <c r="N67" t="n">
         <v>46</v>
@@ -3528,277 +3528,277 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>B1ad3</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8369</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.785</v>
+        <v>-0.8003</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0052</v>
+        <v>-0.9945000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8369</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8369</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8369</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8369</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8369</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="N68" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8671</v>
+        <v>-0.8619</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.8133</v>
+        <v>-0.8084</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0189</v>
+        <v>-0.9984</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8671</v>
+        <v>-0.8619</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.8671</v>
+        <v>-0.8547</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.0072</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.8671</v>
+        <v>-0.8547</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.8671</v>
+        <v>-0.8547</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.0072</v>
       </c>
       <c r="K69" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.8671</v>
+        <v>-0.8619</v>
       </c>
       <c r="N69" t="n">
-        <v>52</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.0033</v>
+        <v>-0.9206</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.8635</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0809</v>
+        <v>-1.0252</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.0033</v>
+        <v>-0.9206</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.0033</v>
+        <v>-0.4222</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-0.4984</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.0033</v>
+        <v>-0.4222</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.0033</v>
+        <v>-0.4335</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-0.4984</v>
       </c>
       <c r="K70" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.0033</v>
+        <v>-0.9319</v>
       </c>
       <c r="N70" t="n">
-        <v>133</v>
+        <v>279</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0034</v>
+        <v>-0.948</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.9411</v>
+        <v>-0.8892</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.081</v>
+        <v>-1.0376</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0034</v>
+        <v>-0.948</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.0997</v>
+        <v>-0.948</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.0997</v>
+        <v>-0.948</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.0997</v>
+        <v>-0.948</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="L71" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.0034</v>
+        <v>-0.948</v>
       </c>
       <c r="N71" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.0446</v>
+        <v>-1.0075</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.9798</v>
+        <v>-0.945</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0997</v>
+        <v>-1.0648</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.0446</v>
+        <v>-1.0075</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.0446</v>
+        <v>-0.1055</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>-0.902</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.0446</v>
+        <v>-0.1055</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.0446</v>
+        <v>-0.1055</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>-0.902</v>
       </c>
       <c r="K72" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.0446</v>
+        <v>-1.0075</v>
       </c>
       <c r="N72" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0454</v>
+        <v>-1.0551</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.9805</v>
+        <v>-0.9896</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1001</v>
+        <v>-1.0864</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0454</v>
+        <v>-1.0551</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.4415</v>
+        <v>-1.0551</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.6039</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.4415</v>
+        <v>-1.0551</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.4529</v>
+        <v>-1.0551</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.6039</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L73" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0568</v>
+        <v>-1.0551</v>
       </c>
       <c r="N73" t="n">
-        <v>279</v>
+        <v>133</v>
       </c>
     </row>
     <row r="74">
@@ -3808,28 +3808,28 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.1836</v>
+        <v>-1.1086</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.1101</v>
+        <v>-1.0398</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.163</v>
+        <v>-1.1108</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.1836</v>
+        <v>-1.1086</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.1836</v>
+        <v>-1.1086</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.1836</v>
+        <v>-1.1086</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.1836</v>
+        <v>-1.1086</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.1836</v>
+        <v>-1.1086</v>
       </c>
       <c r="N74" t="n">
         <v>106</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.1946</v>
+        <v>-1.2245</v>
       </c>
       <c r="C75" t="n">
-        <v>-1.1205</v>
+        <v>-1.1485</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.168</v>
+        <v>-1.1636</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.1946</v>
+        <v>-1.2245</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.1946</v>
+        <v>-1.2245</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.1946</v>
+        <v>-1.2245</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.1946</v>
+        <v>-1.2245</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.1946</v>
+        <v>-1.2245</v>
       </c>
       <c r="N75" t="n">
         <v>52</v>
@@ -3900,31 +3900,31 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.2826</v>
+        <v>-1.2441</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.203</v>
+        <v>-1.1669</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2081</v>
+        <v>-1.1725</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.2826</v>
+        <v>-1.2441</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.1322</v>
+        <v>-1.06</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.1504</v>
+        <v>-0.1841</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.1322</v>
+        <v>-1.06</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1322</v>
+        <v>-1.06</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.1504</v>
+        <v>-0.1841</v>
       </c>
       <c r="K76" t="n">
         <v>57</v>
@@ -3933,7 +3933,7 @@
         <v>62</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.2826</v>
+        <v>-1.2441</v>
       </c>
       <c r="N76" t="n">
         <v>119</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.5552</v>
+        <v>-1.4957</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.4587</v>
+        <v>-1.4029</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.3322</v>
+        <v>-1.2872</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.5552</v>
+        <v>-1.4957</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.5552</v>
+        <v>-1.4957</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.5552</v>
+        <v>-1.4957</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.5552</v>
+        <v>-1.4957</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.5552</v>
+        <v>-1.4957</v>
       </c>
       <c r="N77" t="n">
         <v>99</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.5621</v>
+        <v>-1.5806</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.4652</v>
+        <v>-1.4825</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3353</v>
+        <v>-1.3258</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.5621</v>
+        <v>-1.5806</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.5621</v>
+        <v>-1.5806</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.5621</v>
+        <v>-1.5806</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.5621</v>
+        <v>-1.5806</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.5621</v>
+        <v>-1.5806</v>
       </c>
       <c r="N78" t="n">
         <v>132</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.81</v>
+        <v>-1.7626</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.6977</v>
+        <v>-1.6532</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4482</v>
+        <v>-1.4087</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.81</v>
+        <v>-1.7626</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.81</v>
+        <v>-1.7626</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.81</v>
+        <v>-1.7626</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.81</v>
+        <v>-1.7626</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.81</v>
+        <v>-1.7626</v>
       </c>
       <c r="N79" t="n">
         <v>132</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.0546</v>
+        <v>-2.1107</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.9271</v>
+        <v>-1.9797</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5595</v>
+        <v>-1.5673</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.0546</v>
+        <v>-2.1107</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.0546</v>
+        <v>-2.1107</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.0546</v>
+        <v>-2.1107</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.0546</v>
+        <v>-2.1107</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.0546</v>
+        <v>-2.1107</v>
       </c>
       <c r="N80" t="n">
         <v>133</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.7567</v>
+        <v>-2.6462</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.5856</v>
+        <v>-2.482</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8791</v>
+        <v>-1.8113</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.7567</v>
+        <v>-2.6462</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.7567</v>
+        <v>-1.6462</v>
       </c>
       <c r="G81" t="n">
         <v>-1</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.7567</v>
+        <v>-1.6462</v>
       </c>
       <c r="I81" t="n">
-        <v>-1.802</v>
+        <v>-1.6902</v>
       </c>
       <c r="J81" t="n">
         <v>-1</v>
@@ -4163,7 +4163,7 @@
         <v>68</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.802</v>
+        <v>-2.6902</v>
       </c>
       <c r="N81" t="n">
         <v>173</v>
@@ -4269,10 +4269,10 @@
         <v>1.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2191</v>
+        <v>1.2672</v>
       </c>
       <c r="J2" t="n">
-        <v>36.573</v>
+        <v>38.016</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.83</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4878</v>
+        <v>-0.4493</v>
       </c>
       <c r="J3" t="n">
-        <v>-14.634</v>
+        <v>-13.479</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.75</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6691</v>
+        <v>-0.6345</v>
       </c>
       <c r="J4" t="n">
-        <v>-20.073</v>
+        <v>-19.035</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.66</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8631</v>
+        <v>-0.8416</v>
       </c>
       <c r="J5" t="n">
-        <v>-25.893</v>
+        <v>-25.248</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9675</v>
+        <v>-0.9565</v>
       </c>
       <c r="J6" t="n">
-        <v>-29.025</v>
+        <v>-28.695</v>
       </c>
     </row>
     <row r="7">
@@ -4469,10 +4469,10 @@
         <v>1.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7829</v>
       </c>
       <c r="J7" t="n">
-        <v>25.086</v>
+        <v>23.487</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7504</v>
+        <v>0.6934</v>
       </c>
       <c r="J8" t="n">
-        <v>22.512</v>
+        <v>20.802</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0506</v>
+        <v>-0.0386</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.518</v>
+        <v>-1.158</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>0.98</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0506</v>
+        <v>-0.0386</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.518</v>
+        <v>-1.158</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3835</v>
+        <v>-0.3729</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.505</v>
+        <v>-11.187</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>2.01</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8453</v>
+        <v>1.8942</v>
       </c>
       <c r="J12" t="n">
-        <v>38.7513</v>
+        <v>39.7782</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.51</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1166</v>
+        <v>1.1252</v>
       </c>
       <c r="J13" t="n">
-        <v>23.4486</v>
+        <v>23.6292</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0092</v>
+        <v>1.008</v>
       </c>
       <c r="J14" t="n">
-        <v>21.1932</v>
+        <v>21.168</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0384</v>
+        <v>0.0203</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8064</v>
+        <v>0.4263</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.9</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4085</v>
+        <v>-0.3727</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.5785</v>
+        <v>-7.8267</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1557</v>
+        <v>0.1502</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2697</v>
+        <v>3.1542</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>0.72</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2928</v>
+        <v>-0.2805</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.1488</v>
+        <v>-5.8905</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.55</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4431</v>
+        <v>-0.4359</v>
       </c>
       <c r="J19" t="n">
-        <v>-9.305099999999999</v>
+        <v>-9.1539</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4871</v>
+        <v>-0.4838</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.2291</v>
+        <v>-10.1598</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.46</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5222</v>
+        <v>-0.5229</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.9662</v>
+        <v>-10.9809</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.382</v>
+        <v>0.3576</v>
       </c>
       <c r="J22" t="n">
-        <v>7.258</v>
+        <v>6.7944</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3223</v>
+        <v>-0.3104</v>
       </c>
       <c r="J23" t="n">
-        <v>-6.1237</v>
+        <v>-5.8976</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.66</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3486</v>
+        <v>-0.3371</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.6234</v>
+        <v>-6.4049</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4885</v>
+        <v>-0.4853</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.281499999999999</v>
+        <v>-9.220700000000001</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.34</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6283</v>
+        <v>-0.6453</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.9377</v>
+        <v>-12.2607</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>2.03</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5793</v>
+        <v>1.6058</v>
       </c>
       <c r="J27" t="n">
-        <v>30.0067</v>
+        <v>30.5102</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>1.98</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5203</v>
+        <v>1.5407</v>
       </c>
       <c r="J28" t="n">
-        <v>28.8857</v>
+        <v>29.2733</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5298</v>
+        <v>0.5272</v>
       </c>
       <c r="J29" t="n">
-        <v>10.0662</v>
+        <v>10.0168</v>
       </c>
     </row>
     <row r="30">
@@ -5389,10 +5389,10 @@
         <v>0.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3568</v>
+        <v>-0.3218</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.7792</v>
+        <v>-6.1142</v>
       </c>
     </row>
     <row r="31">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.1188</v>
+        <v>-10.5431</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>0.84</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.137</v>
+        <v>-0.1115</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.014</v>
+        <v>-2.453</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>0.61</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.378</v>
+        <v>-0.3717</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.316000000000001</v>
+        <v>-8.1774</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>0.57</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4137</v>
+        <v>-0.4087</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.1014</v>
+        <v>-8.991400000000001</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.54</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4383</v>
+        <v>-0.4339</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.6426</v>
+        <v>-9.5458</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.19</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7489</v>
+        <v>-0.7892</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.4758</v>
+        <v>-17.3624</v>
       </c>
     </row>
     <row r="37">
@@ -5669,10 +5669,10 @@
         <v>1.68</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1553</v>
+        <v>1.1496</v>
       </c>
       <c r="J37" t="n">
-        <v>25.4166</v>
+        <v>25.2912</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.62</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0795</v>
+        <v>1.071</v>
       </c>
       <c r="J38" t="n">
-        <v>23.749</v>
+        <v>23.562</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>1.46</v>
       </c>
       <c r="I39" t="n">
-        <v>0.872</v>
+        <v>0.861</v>
       </c>
       <c r="J39" t="n">
-        <v>19.184</v>
+        <v>18.942</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>1.13</v>
       </c>
       <c r="I40" t="n">
-        <v>0.3551</v>
+        <v>0.3229</v>
       </c>
       <c r="J40" t="n">
-        <v>7.8122</v>
+        <v>7.1038</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>1.09</v>
       </c>
       <c r="I41" t="n">
-        <v>0.2523</v>
+        <v>0.2206</v>
       </c>
       <c r="J41" t="n">
-        <v>5.5506</v>
+        <v>4.8532</v>
       </c>
     </row>
     <row r="42">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4628</v>
+        <v>0.4818</v>
       </c>
       <c r="J42" t="n">
-        <v>12.0328</v>
+        <v>12.5268</v>
       </c>
     </row>
     <row r="43">
@@ -5909,10 +5909,10 @@
         <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1144</v>
+        <v>0.0985</v>
       </c>
       <c r="J43" t="n">
-        <v>2.9744</v>
+        <v>2.561</v>
       </c>
     </row>
     <row r="44">
@@ -5949,10 +5949,10 @@
         <v>0.8</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2418</v>
+        <v>-0.2222</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.2868</v>
+        <v>-5.7772</v>
       </c>
     </row>
     <row r="45">
@@ -5989,10 +5989,10 @@
         <v>0.73</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3091</v>
+        <v>-0.2914</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.0366</v>
+        <v>-7.5764</v>
       </c>
     </row>
     <row r="46">
@@ -6029,10 +6029,10 @@
         <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.436</v>
+        <v>-0.4284</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.336</v>
+        <v>-11.1384</v>
       </c>
     </row>
     <row r="47">
@@ -6069,10 +6069,10 @@
         <v>1.54</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6155</v>
+        <v>0.5774</v>
       </c>
       <c r="J47" t="n">
-        <v>16.003</v>
+        <v>15.0124</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.42</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5229</v>
+        <v>0.4819</v>
       </c>
       <c r="J48" t="n">
-        <v>13.5954</v>
+        <v>12.5294</v>
       </c>
     </row>
     <row r="49">
@@ -6149,10 +6149,10 @@
         <v>0.98</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0529</v>
+        <v>-0.0407</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.3754</v>
+        <v>-1.0582</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1347</v>
+        <v>-0.1156</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.5022</v>
+        <v>-3.0056</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2538</v>
+        <v>-0.2348</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.5988</v>
+        <v>-6.1048</v>
       </c>
     </row>
     <row r="52">
@@ -6269,10 +6269,10 @@
         <v>1.14</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4319</v>
+        <v>0.392</v>
       </c>
       <c r="J52" t="n">
-        <v>19.8674</v>
+        <v>18.032</v>
       </c>
     </row>
     <row r="53">
@@ -6309,10 +6309,10 @@
         <v>1.13</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4091</v>
+        <v>0.3675</v>
       </c>
       <c r="J53" t="n">
-        <v>18.8186</v>
+        <v>16.905</v>
       </c>
     </row>
     <row r="54">
@@ -6349,10 +6349,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3845</v>
+        <v>0.3428</v>
       </c>
       <c r="J54" t="n">
-        <v>17.687</v>
+        <v>15.7688</v>
       </c>
     </row>
     <row r="55">
@@ -6389,10 +6389,10 @@
         <v>1.1</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3331</v>
+        <v>0.2928</v>
       </c>
       <c r="J55" t="n">
-        <v>15.3226</v>
+        <v>13.4688</v>
       </c>
     </row>
     <row r="56">
@@ -6429,10 +6429,10 @@
         <v>0.71</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.7957</v>
+        <v>-0.7708</v>
       </c>
       <c r="J56" t="n">
-        <v>-36.6022</v>
+        <v>-35.4568</v>
       </c>
     </row>
     <row r="57">
@@ -6469,10 +6469,10 @@
         <v>1.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4947</v>
+        <v>0.4553</v>
       </c>
       <c r="J57" t="n">
-        <v>22.7562</v>
+        <v>20.9438</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.04</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1233</v>
+        <v>0.0934</v>
       </c>
       <c r="J58" t="n">
-        <v>5.6718</v>
+        <v>4.2964</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0988</v>
+        <v>0.0732</v>
       </c>
       <c r="J59" t="n">
-        <v>4.5448</v>
+        <v>3.3672</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.97</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0589</v>
+        <v>-0.0461</v>
       </c>
       <c r="J60" t="n">
-        <v>-2.7094</v>
+        <v>-2.1206</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.76</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2923</v>
+        <v>-0.274</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.4458</v>
+        <v>-12.604</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.75</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2458</v>
+        <v>1.2446</v>
       </c>
       <c r="J62" t="n">
-        <v>28.6534</v>
+        <v>28.6258</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0568</v>
+        <v>1.0473</v>
       </c>
       <c r="J63" t="n">
-        <v>24.3064</v>
+        <v>24.0879</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1.53</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9549</v>
       </c>
       <c r="J64" t="n">
-        <v>22.2226</v>
+        <v>21.9627</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>1.25</v>
       </c>
       <c r="I65" t="n">
-        <v>0.5789</v>
+        <v>0.5755</v>
       </c>
       <c r="J65" t="n">
-        <v>13.3147</v>
+        <v>13.2365</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.76</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.7211</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.0522</v>
+        <v>-16.5853</v>
       </c>
     </row>
     <row r="67">
@@ -6869,10 +6869,10 @@
         <v>1.03</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1731</v>
+        <v>0.1473</v>
       </c>
       <c r="J67" t="n">
-        <v>3.9813</v>
+        <v>3.3879</v>
       </c>
     </row>
     <row r="68">
@@ -6909,10 +6909,10 @@
         <v>1.03</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1731</v>
+        <v>0.1473</v>
       </c>
       <c r="J68" t="n">
-        <v>3.9813</v>
+        <v>3.3879</v>
       </c>
     </row>
     <row r="69">
@@ -6949,10 +6949,10 @@
         <v>0.71</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3112</v>
+        <v>-0.2962</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.1576</v>
+        <v>-6.8126</v>
       </c>
     </row>
     <row r="70">
@@ -6989,10 +6989,10 @@
         <v>0.58</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4276</v>
+        <v>-0.4185</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.8348</v>
+        <v>-9.625500000000001</v>
       </c>
     </row>
     <row r="71">
@@ -7029,10 +7029,10 @@
         <v>0.31</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6613</v>
+        <v>-0.6859</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.2099</v>
+        <v>-15.7757</v>
       </c>
     </row>
     <row r="72">
@@ -7069,10 +7069,10 @@
         <v>1.53</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8227</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>24.681</v>
+        <v>23.724</v>
       </c>
     </row>
     <row r="73">
@@ -7109,10 +7109,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0484</v>
+        <v>0.0323</v>
       </c>
       <c r="J73" t="n">
-        <v>1.452</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="74">
@@ -7149,10 +7149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0961</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.883</v>
+        <v>-2.406</v>
       </c>
     </row>
     <row r="75">
@@ -7189,10 +7189,10 @@
         <v>0.91</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1321</v>
+        <v>-0.1137</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.963</v>
+        <v>-3.411</v>
       </c>
     </row>
     <row r="76">
@@ -7229,10 +7229,10 @@
         <v>0.41</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5951</v>
+        <v>-0.611</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.853</v>
+        <v>-18.33</v>
       </c>
     </row>
     <row r="77">
@@ -7269,10 +7269,10 @@
         <v>1.62</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1538</v>
+        <v>1.1532</v>
       </c>
       <c r="J77" t="n">
-        <v>34.614</v>
+        <v>34.596</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4449</v>
+        <v>0.4087</v>
       </c>
       <c r="J78" t="n">
-        <v>13.347</v>
+        <v>12.261</v>
       </c>
     </row>
     <row r="79">
@@ -7349,10 +7349,10 @@
         <v>0.93</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2753</v>
+        <v>-0.2351</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.259</v>
+        <v>-7.053</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3846</v>
+        <v>-0.3417</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.538</v>
+        <v>-10.251</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.82</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5575</v>
+        <v>-0.5177</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.725</v>
+        <v>-15.531</v>
       </c>
     </row>
     <row r="82">
@@ -7469,10 +7469,10 @@
         <v>1.1</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2795</v>
+        <v>0.2315</v>
       </c>
       <c r="J82" t="n">
-        <v>8.105499999999999</v>
+        <v>6.7135</v>
       </c>
     </row>
     <row r="83">
@@ -7509,10 +7509,10 @@
         <v>0.97</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0492</v>
+        <v>-0.0395</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.4268</v>
+        <v>-1.1455</v>
       </c>
     </row>
     <row r="84">
@@ -7549,10 +7549,10 @@
         <v>0.84</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2014</v>
+        <v>-0.182</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.8406</v>
+        <v>-5.278</v>
       </c>
     </row>
     <row r="85">
@@ -7589,10 +7589,10 @@
         <v>0.78</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.261</v>
+        <v>-0.2417</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.569</v>
+        <v>-7.0093</v>
       </c>
     </row>
     <row r="86">
@@ -7629,10 +7629,10 @@
         <v>0.73</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3086</v>
+        <v>-0.291</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.949400000000001</v>
+        <v>-8.439</v>
       </c>
     </row>
     <row r="87">
@@ -7669,10 +7669,10 @@
         <v>1.2</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5496</v>
+        <v>0.538</v>
       </c>
       <c r="J87" t="n">
-        <v>15.9384</v>
+        <v>15.602</v>
       </c>
     </row>
     <row r="88">
@@ -7709,10 +7709,10 @@
         <v>1.15</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4615</v>
+        <v>0.4273</v>
       </c>
       <c r="J88" t="n">
-        <v>13.3835</v>
+        <v>12.3917</v>
       </c>
     </row>
     <row r="89">
@@ -7749,10 +7749,10 @@
         <v>0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0582</v>
+        <v>-0.0425</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.6878</v>
+        <v>-1.2325</v>
       </c>
     </row>
     <row r="90">
@@ -7789,10 +7789,10 @@
         <v>0.87</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4185</v>
+        <v>-0.3756</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.1365</v>
+        <v>-10.8924</v>
       </c>
     </row>
     <row r="91">
@@ -7829,10 +7829,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6549</v>
+        <v>-0.6189</v>
       </c>
       <c r="J91" t="n">
-        <v>-18.9921</v>
+        <v>-17.9481</v>
       </c>
     </row>
     <row r="92">
@@ -7869,10 +7869,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3657</v>
+        <v>0.3118</v>
       </c>
       <c r="J92" t="n">
-        <v>9.5082</v>
+        <v>8.1068</v>
       </c>
     </row>
     <row r="93">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1179</v>
+        <v>-0.1012</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.0654</v>
+        <v>-2.6312</v>
       </c>
     </row>
     <row r="94">
@@ -7949,10 +7949,10 @@
         <v>0.91</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1292</v>
+        <v>-0.1118</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.3592</v>
+        <v>-2.9068</v>
       </c>
     </row>
     <row r="95">
@@ -7989,10 +7989,10 @@
         <v>0.87</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1732</v>
+        <v>-0.1537</v>
       </c>
       <c r="J95" t="n">
-        <v>-4.5032</v>
+        <v>-3.9962</v>
       </c>
     </row>
     <row r="96">
@@ -8029,10 +8029,10 @@
         <v>0.75</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2934</v>
+        <v>-0.275</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.6284</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="97">
@@ -8069,10 +8069,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1015</v>
+        <v>1.0975</v>
       </c>
       <c r="J97" t="n">
-        <v>28.639</v>
+        <v>28.535</v>
       </c>
     </row>
     <row r="98">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0485</v>
+        <v>0.0365</v>
       </c>
       <c r="J98" t="n">
-        <v>1.261</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="99">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1822</v>
+        <v>-0.1481</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.7372</v>
+        <v>-3.8506</v>
       </c>
     </row>
     <row r="100">
@@ -8189,10 +8189,10 @@
         <v>0.91</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3297</v>
+        <v>-0.2876</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.5722</v>
+        <v>-7.4776</v>
       </c>
     </row>
     <row r="101">
@@ -8229,10 +8229,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3297</v>
+        <v>-0.2876</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.5722</v>
+        <v>-7.4776</v>
       </c>
     </row>
     <row r="102">
@@ -8269,10 +8269,10 @@
         <v>1.08</v>
       </c>
       <c r="I102" t="n">
-        <v>0.25</v>
+        <v>0.206</v>
       </c>
       <c r="J102" t="n">
-        <v>6</v>
+        <v>4.944</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>0.96</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0588</v>
+        <v>-0.048</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.4112</v>
+        <v>-1.152</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>0.89</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1461</v>
+        <v>-0.1297</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.5064</v>
+        <v>-3.1128</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2181</v>
+        <v>-0.1995</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.2344</v>
+        <v>-4.788</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.47</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5357</v>
+        <v>-0.5403</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.8568</v>
+        <v>-12.9672</v>
       </c>
     </row>
     <row r="107">
@@ -8469,10 +8469,10 @@
         <v>1.75</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2923</v>
+        <v>1.2979</v>
       </c>
       <c r="J107" t="n">
-        <v>31.0152</v>
+        <v>31.1496</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.22</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5498</v>
+        <v>0.5421</v>
       </c>
       <c r="J108" t="n">
-        <v>13.1952</v>
+        <v>13.0104</v>
       </c>
     </row>
     <row r="109">
@@ -8549,10 +8549,10 @@
         <v>1.13</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3876</v>
+        <v>0.3529</v>
       </c>
       <c r="J109" t="n">
-        <v>9.3024</v>
+        <v>8.4696</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>1.09</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2858</v>
+        <v>0.2535</v>
       </c>
       <c r="J110" t="n">
-        <v>6.8592</v>
+        <v>6.084</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.75</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7091</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.6496</v>
+        <v>-17.0184</v>
       </c>
     </row>
     <row r="112">
@@ -8669,10 +8669,10 @@
         <v>1.67</v>
       </c>
       <c r="I112" t="n">
-        <v>1.001</v>
+        <v>0.9821</v>
       </c>
       <c r="J112" t="n">
-        <v>26.026</v>
+        <v>25.5346</v>
       </c>
     </row>
     <row r="113">
@@ -8709,10 +8709,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2014</v>
+        <v>-0.182</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.2364</v>
+        <v>-4.732</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>0.77</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2706</v>
+        <v>-0.2516</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.0356</v>
+        <v>-6.5416</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>0.64</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3912</v>
+        <v>-0.3791</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.1712</v>
+        <v>-9.8566</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5137</v>
+        <v>-0.5157</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.3562</v>
+        <v>-13.4082</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.96</v>
       </c>
       <c r="I117" t="n">
-        <v>1.5672</v>
+        <v>1.6043</v>
       </c>
       <c r="J117" t="n">
-        <v>40.7472</v>
+        <v>41.7118</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.19</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5042</v>
+        <v>0.4899</v>
       </c>
       <c r="J118" t="n">
-        <v>13.1092</v>
+        <v>12.7374</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0272</v>
+        <v>-0.0217</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1651</v>
+        <v>-0.1335</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.2926</v>
+        <v>-3.471</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.8217</v>
       </c>
       <c r="J121" t="n">
-        <v>-21.8192</v>
+        <v>-21.3642</v>
       </c>
     </row>
     <row r="122">
@@ -9069,10 +9069,10 @@
         <v>1.09</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2408</v>
+        <v>0.195</v>
       </c>
       <c r="J122" t="n">
-        <v>8.668799999999999</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="123">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.0563</v>
       </c>
       <c r="J123" t="n">
-        <v>2.8512</v>
+        <v>2.0268</v>
       </c>
     </row>
     <row r="124">
@@ -9149,10 +9149,10 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0046</v>
+        <v>0.0025</v>
       </c>
       <c r="J124" t="n">
-        <v>0.1656</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="125">
@@ -9189,10 +9189,10 @@
         <v>0.9</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1434</v>
+        <v>-0.1244</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.1624</v>
+        <v>-4.4784</v>
       </c>
     </row>
     <row r="126">
@@ -9229,10 +9229,10 @@
         <v>0.78</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2682</v>
+        <v>-0.2488</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.655200000000001</v>
+        <v>-8.956799999999999</v>
       </c>
     </row>
     <row r="127">
@@ -9269,10 +9269,10 @@
         <v>1.26</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6404</v>
+        <v>0.6262</v>
       </c>
       <c r="J127" t="n">
-        <v>23.0544</v>
+        <v>22.5432</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.15</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4539</v>
+        <v>0.4181</v>
       </c>
       <c r="J128" t="n">
-        <v>16.3404</v>
+        <v>15.0516</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2656</v>
+        <v>-0.2261</v>
       </c>
       <c r="J129" t="n">
-        <v>-9.5616</v>
+        <v>-8.1396</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2939</v>
+        <v>-0.2531</v>
       </c>
       <c r="J130" t="n">
-        <v>-10.5804</v>
+        <v>-9.111599999999999</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3484</v>
+        <v>-0.3059</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.5424</v>
+        <v>-11.0124</v>
       </c>
     </row>
     <row r="132">
@@ -9469,10 +9469,10 @@
         <v>1.13</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2814</v>
+        <v>0.2728</v>
       </c>
       <c r="J132" t="n">
-        <v>7.035</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="133">
@@ -9509,10 +9509,10 @@
         <v>1.04</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1286</v>
+        <v>0.1146</v>
       </c>
       <c r="J133" t="n">
-        <v>3.215</v>
+        <v>2.865</v>
       </c>
     </row>
     <row r="134">
@@ -9549,10 +9549,10 @@
         <v>0.83</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2071</v>
+        <v>-0.1893</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.1775</v>
+        <v>-4.7325</v>
       </c>
     </row>
     <row r="135">
@@ -9589,10 +9589,10 @@
         <v>0.67</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3577</v>
+        <v>-0.343</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.942500000000001</v>
+        <v>-8.574999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -9629,10 +9629,10 @@
         <v>0.45</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.5575</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.7725</v>
+        <v>-13.9375</v>
       </c>
     </row>
     <row r="137">
@@ -9669,10 +9669,10 @@
         <v>1.66</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.6601</v>
       </c>
       <c r="J137" t="n">
-        <v>17.6025</v>
+        <v>16.5025</v>
       </c>
     </row>
     <row r="138">
@@ -9709,10 +9709,10 @@
         <v>1.27</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3863</v>
+        <v>0.3244</v>
       </c>
       <c r="J138" t="n">
-        <v>9.657500000000001</v>
+        <v>8.109999999999999</v>
       </c>
     </row>
     <row r="139">
@@ -9749,10 +9749,10 @@
         <v>1.21</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3157</v>
+        <v>0.26</v>
       </c>
       <c r="J139" t="n">
-        <v>7.8925</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="140">
@@ -9789,10 +9789,10 @@
         <v>0.85</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2132</v>
+        <v>-0.1932</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.33</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="141">
@@ -9829,10 +9829,10 @@
         <v>0.7</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3588</v>
+        <v>-0.3463</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.970000000000001</v>
+        <v>-8.657500000000001</v>
       </c>
     </row>
     <row r="142">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8227</v>
+        <v>0.8079</v>
       </c>
       <c r="J142" t="n">
-        <v>20.5675</v>
+        <v>20.1975</v>
       </c>
     </row>
     <row r="143">
@@ -9909,10 +9909,10 @@
         <v>1.4</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8086</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>20.215</v>
+        <v>19.8475</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>1.3</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6536</v>
       </c>
       <c r="J144" t="n">
-        <v>16.62</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>1.23</v>
       </c>
       <c r="I145" t="n">
-        <v>0.5607</v>
+        <v>0.5548</v>
       </c>
       <c r="J145" t="n">
-        <v>14.0175</v>
+        <v>13.87</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.91</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3617</v>
+        <v>-0.3221</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.0425</v>
+        <v>-8.0525</v>
       </c>
     </row>
     <row r="147">
@@ -10069,10 +10069,10 @@
         <v>1.08</v>
       </c>
       <c r="I147" t="n">
-        <v>0.292</v>
+        <v>0.2549</v>
       </c>
       <c r="J147" t="n">
-        <v>7.3</v>
+        <v>6.3725</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.01</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1097</v>
+        <v>0.0934</v>
       </c>
       <c r="J148" t="n">
-        <v>2.7425</v>
+        <v>2.335</v>
       </c>
     </row>
     <row r="149">
@@ -10149,10 +10149,10 @@
         <v>0.58</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.4283</v>
+        <v>-0.4193</v>
       </c>
       <c r="J149" t="n">
-        <v>-10.7075</v>
+        <v>-10.4825</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.53</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4724</v>
+        <v>-0.4677</v>
       </c>
       <c r="J150" t="n">
-        <v>-11.81</v>
+        <v>-11.6925</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.49</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5074</v>
+        <v>-0.5069</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.685</v>
+        <v>-12.6725</v>
       </c>
     </row>
     <row r="152">
@@ -10269,10 +10269,10 @@
         <v>1.75</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2272</v>
+        <v>1.226</v>
       </c>
       <c r="J152" t="n">
-        <v>22.0896</v>
+        <v>22.068</v>
       </c>
     </row>
     <row r="153">
@@ -10309,10 +10309,10 @@
         <v>1.74</v>
       </c>
       <c r="I153" t="n">
-        <v>1.2151</v>
+        <v>1.2133</v>
       </c>
       <c r="J153" t="n">
-        <v>21.8718</v>
+        <v>21.8394</v>
       </c>
     </row>
     <row r="154">
@@ -10349,10 +10349,10 @@
         <v>1.61</v>
       </c>
       <c r="I154" t="n">
-        <v>1.0549</v>
+        <v>1.0478</v>
       </c>
       <c r="J154" t="n">
-        <v>18.9882</v>
+        <v>18.8604</v>
       </c>
     </row>
     <row r="155">
@@ -10389,10 +10389,10 @@
         <v>1.38</v>
       </c>
       <c r="I155" t="n">
-        <v>0.7581</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="J155" t="n">
-        <v>13.6458</v>
+        <v>13.527</v>
       </c>
     </row>
     <row r="156">
@@ -10429,10 +10429,10 @@
         <v>0.95</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2813</v>
+        <v>-0.2521</v>
       </c>
       <c r="J156" t="n">
-        <v>-5.0634</v>
+        <v>-4.5378</v>
       </c>
     </row>
     <row r="157">
@@ -10469,10 +10469,10 @@
         <v>0.59</v>
       </c>
       <c r="I157" t="n">
-        <v>-0.3667</v>
+        <v>-0.3596</v>
       </c>
       <c r="J157" t="n">
-        <v>-6.6006</v>
+        <v>-6.4728</v>
       </c>
     </row>
     <row r="158">
@@ -10509,10 +10509,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.397</v>
+        <v>-0.3934</v>
       </c>
       <c r="J158" t="n">
-        <v>-7.146</v>
+        <v>-7.0812</v>
       </c>
     </row>
     <row r="159">
@@ -10549,10 +10549,10 @@
         <v>0.45</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.4992</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.9856</v>
+        <v>-9.045</v>
       </c>
     </row>
     <row r="160">
@@ -10589,10 +10589,10 @@
         <v>0.43</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.5152</v>
+        <v>-0.5188</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.2736</v>
+        <v>-9.3384</v>
       </c>
     </row>
     <row r="161">
@@ -10629,10 +10629,10 @@
         <v>0.18</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.7456</v>
+        <v>-0.783</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.4208</v>
+        <v>-14.094</v>
       </c>
     </row>
     <row r="162">
@@ -10669,10 +10669,10 @@
         <v>1.2</v>
       </c>
       <c r="I162" t="n">
-        <v>0.4886</v>
+        <v>0.4378</v>
       </c>
       <c r="J162" t="n">
-        <v>12.215</v>
+        <v>10.945</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.08</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2553</v>
+        <v>0.2118</v>
       </c>
       <c r="J163" t="n">
-        <v>6.3825</v>
+        <v>5.295</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2459</v>
+        <v>-0.2275</v>
       </c>
       <c r="J164" t="n">
-        <v>-6.1475</v>
+        <v>-5.6875</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.66</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3672</v>
+        <v>-0.3532</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.18</v>
+        <v>-8.83</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.41</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.5851</v>
+        <v>-0.5974</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.6275</v>
+        <v>-14.935</v>
       </c>
     </row>
     <row r="167">
@@ -10869,10 +10869,10 @@
         <v>1.58</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2313</v>
+        <v>1.2495</v>
       </c>
       <c r="J167" t="n">
-        <v>30.7825</v>
+        <v>31.2375</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.19</v>
       </c>
       <c r="I168" t="n">
-        <v>0.5327</v>
+        <v>0.4947</v>
       </c>
       <c r="J168" t="n">
-        <v>13.3175</v>
+        <v>12.3675</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.08</v>
       </c>
       <c r="I169" t="n">
-        <v>0.268</v>
+        <v>0.2349</v>
       </c>
       <c r="J169" t="n">
-        <v>6.7</v>
+        <v>5.8725</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.98</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1223</v>
+        <v>-0.0951</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.0575</v>
+        <v>-2.3775</v>
       </c>
     </row>
     <row r="171">
@@ -11029,10 +11029,10 @@
         <v>0.82</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5666</v>
+        <v>-0.528</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.165</v>
+        <v>-13.2</v>
       </c>
     </row>
     <row r="172">
@@ -11069,10 +11069,10 @@
         <v>1.47</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5656</v>
       </c>
       <c r="J172" t="n">
-        <v>16.4736</v>
+        <v>14.7056</v>
       </c>
     </row>
     <row r="173">
@@ -11109,10 +11109,10 @@
         <v>1.31</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4543</v>
+        <v>0.3885</v>
       </c>
       <c r="J173" t="n">
-        <v>11.8118</v>
+        <v>10.101</v>
       </c>
     </row>
     <row r="174">
@@ -11149,10 +11149,10 @@
         <v>0.85</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.202</v>
+        <v>-0.1814</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.252</v>
+        <v>-4.7164</v>
       </c>
     </row>
     <row r="175">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3297</v>
+        <v>-0.3137</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.5722</v>
+        <v>-8.1562</v>
       </c>
     </row>
     <row r="176">
@@ -11229,10 +11229,10 @@
         <v>0.68</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3665</v>
+        <v>-0.3532</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.529</v>
+        <v>-9.183199999999999</v>
       </c>
     </row>
     <row r="177">
@@ -11269,10 +11269,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5561</v>
+        <v>0.5802</v>
       </c>
       <c r="J177" t="n">
-        <v>14.4586</v>
+        <v>15.0852</v>
       </c>
     </row>
     <row r="178">
@@ -11309,10 +11309,10 @@
         <v>1.02</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0704</v>
+        <v>0.0571</v>
       </c>
       <c r="J178" t="n">
-        <v>1.8304</v>
+        <v>1.4846</v>
       </c>
     </row>
     <row r="179">
@@ -11349,10 +11349,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.253</v>
+        <v>-0.2334</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.578</v>
+        <v>-6.0684</v>
       </c>
     </row>
     <row r="180">
@@ -11389,10 +11389,10 @@
         <v>0.74</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3011</v>
+        <v>-0.283</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.8286</v>
+        <v>-7.358</v>
       </c>
     </row>
     <row r="181">
@@ -11429,10 +11429,10 @@
         <v>0.61</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4197</v>
+        <v>-0.4105</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.9122</v>
+        <v>-10.673</v>
       </c>
     </row>
     <row r="182">
@@ -11469,10 +11469,10 @@
         <v>1.22</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5532</v>
+        <v>0.5109</v>
       </c>
       <c r="J182" t="n">
-        <v>13.2768</v>
+        <v>12.2616</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>0.93</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0873</v>
+        <v>-0.0736</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.0952</v>
+        <v>-1.7664</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>0.79</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2414</v>
+        <v>-0.225</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.7936</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>0.52</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.4847</v>
+        <v>-0.4816</v>
       </c>
       <c r="J185" t="n">
-        <v>-11.6328</v>
+        <v>-11.5584</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.38</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6052</v>
+        <v>-0.6199</v>
       </c>
       <c r="J186" t="n">
-        <v>-14.5248</v>
+        <v>-14.8776</v>
       </c>
     </row>
     <row r="187">
@@ -11669,10 +11669,10 @@
         <v>1.91</v>
       </c>
       <c r="I187" t="n">
-        <v>1.6302</v>
+        <v>1.6784</v>
       </c>
       <c r="J187" t="n">
-        <v>39.1248</v>
+        <v>40.2816</v>
       </c>
     </row>
     <row r="188">
@@ -11709,10 +11709,10 @@
         <v>1.14</v>
       </c>
       <c r="I188" t="n">
-        <v>0.406</v>
+        <v>0.3724</v>
       </c>
       <c r="J188" t="n">
-        <v>9.744</v>
+        <v>8.9376</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>1.11</v>
       </c>
       <c r="I189" t="n">
-        <v>0.3318</v>
+        <v>0.2991</v>
       </c>
       <c r="J189" t="n">
-        <v>7.9632</v>
+        <v>7.1784</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>1.09</v>
       </c>
       <c r="I190" t="n">
-        <v>0.2795</v>
+        <v>0.2481</v>
       </c>
       <c r="J190" t="n">
-        <v>6.708</v>
+        <v>5.9544</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.88</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4368</v>
+        <v>-0.3966</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.4832</v>
+        <v>-9.5184</v>
       </c>
     </row>
     <row r="192">
@@ -11869,10 +11869,10 @@
         <v>1.17</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5252</v>
+        <v>0.4838</v>
       </c>
       <c r="J192" t="n">
-        <v>15.756</v>
+        <v>14.514</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>1.03</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1403</v>
+        <v>0.1111</v>
       </c>
       <c r="J193" t="n">
-        <v>4.209</v>
+        <v>3.333</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.97</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1318</v>
+        <v>-0.1056</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.954</v>
+        <v>-3.168</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2258</v>
+        <v>-0.1904</v>
       </c>
       <c r="J195" t="n">
-        <v>-6.774</v>
+        <v>-5.712</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.76</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6726</v>
+        <v>-0.6374</v>
       </c>
       <c r="J196" t="n">
-        <v>-20.178</v>
+        <v>-19.122</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.59</v>
       </c>
       <c r="I197" t="n">
-        <v>0.9867</v>
+        <v>0.9489</v>
       </c>
       <c r="J197" t="n">
-        <v>29.601</v>
+        <v>28.467</v>
       </c>
     </row>
     <row r="198">
@@ -12109,10 +12109,10 @@
         <v>1.48</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8384</v>
+        <v>0.7854</v>
       </c>
       <c r="J198" t="n">
-        <v>25.152</v>
+        <v>23.562</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>0.89</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1666</v>
+        <v>-0.1463</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.998</v>
+        <v>-4.389</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.84</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2204</v>
+        <v>-0.2002</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.612</v>
+        <v>-6.006</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3649</v>
+        <v>-0.3525</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.947</v>
+        <v>-10.575</v>
       </c>
     </row>
     <row r="202">
@@ -12269,10 +12269,10 @@
         <v>2.17</v>
       </c>
       <c r="I202" t="n">
-        <v>1.8437</v>
+        <v>1.905</v>
       </c>
       <c r="J202" t="n">
-        <v>31.3429</v>
+        <v>32.385</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.65</v>
       </c>
       <c r="I203" t="n">
-        <v>1.241</v>
+        <v>1.2635</v>
       </c>
       <c r="J203" t="n">
-        <v>21.097</v>
+        <v>21.4795</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>1.59</v>
       </c>
       <c r="I204" t="n">
-        <v>1.1688</v>
+        <v>1.1902</v>
       </c>
       <c r="J204" t="n">
-        <v>19.8696</v>
+        <v>20.2334</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>1.41</v>
       </c>
       <c r="I205" t="n">
-        <v>0.913</v>
+        <v>0.9129</v>
       </c>
       <c r="J205" t="n">
-        <v>15.521</v>
+        <v>15.5193</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>1.13</v>
       </c>
       <c r="I206" t="n">
-        <v>0.3277</v>
+        <v>0.2924</v>
       </c>
       <c r="J206" t="n">
-        <v>5.5709</v>
+        <v>4.9708</v>
       </c>
     </row>
     <row r="207">
@@ -12469,10 +12469,10 @@
         <v>0.64</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.2805</v>
+        <v>-0.2536</v>
       </c>
       <c r="J207" t="n">
-        <v>-4.7685</v>
+        <v>-4.3112</v>
       </c>
     </row>
     <row r="208">
@@ -12509,10 +12509,10 @@
         <v>0.59</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.3375</v>
+        <v>-0.3219</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.7375</v>
+        <v>-5.4723</v>
       </c>
     </row>
     <row r="209">
@@ -12549,10 +12549,10 @@
         <v>0.43</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.5036</v>
+        <v>-0.5104</v>
       </c>
       <c r="J209" t="n">
-        <v>-8.561199999999999</v>
+        <v>-8.6768</v>
       </c>
     </row>
     <row r="210">
@@ -12589,10 +12589,10 @@
         <v>0.2</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.7456</v>
       </c>
       <c r="J210" t="n">
-        <v>-12.1754</v>
+        <v>-12.6752</v>
       </c>
     </row>
     <row r="211">
@@ -12629,10 +12629,10 @@
         <v>0.05</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.8681</v>
+        <v>-0.9391</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.7577</v>
+        <v>-15.9647</v>
       </c>
     </row>
     <row r="212">
@@ -12669,10 +12669,10 @@
         <v>1.38</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7442</v>
+        <v>0.6936</v>
       </c>
       <c r="J212" t="n">
-        <v>26.047</v>
+        <v>24.276</v>
       </c>
     </row>
     <row r="213">
@@ -12709,10 +12709,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3433</v>
+        <v>0.2902</v>
       </c>
       <c r="J213" t="n">
-        <v>12.0155</v>
+        <v>10.157</v>
       </c>
     </row>
     <row r="214">
@@ -12749,10 +12749,10 @@
         <v>0.79</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.2561</v>
+        <v>-0.2364</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.9635</v>
+        <v>-8.273999999999999</v>
       </c>
     </row>
     <row r="215">
@@ -12789,10 +12789,10 @@
         <v>0.74</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3042</v>
+        <v>-0.2863</v>
       </c>
       <c r="J215" t="n">
-        <v>-10.647</v>
+        <v>-10.0205</v>
       </c>
     </row>
     <row r="216">
@@ -12829,10 +12829,10 @@
         <v>0.62</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4139</v>
+        <v>-0.4044</v>
       </c>
       <c r="J216" t="n">
-        <v>-14.4865</v>
+        <v>-14.154</v>
       </c>
     </row>
     <row r="217">
@@ -12869,10 +12869,10 @@
         <v>1.42</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0184</v>
+        <v>1.0197</v>
       </c>
       <c r="J217" t="n">
-        <v>35.644</v>
+        <v>35.6895</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.37</v>
       </c>
       <c r="I218" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9135</v>
       </c>
       <c r="J218" t="n">
-        <v>32.4765</v>
+        <v>31.9725</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.03</v>
       </c>
       <c r="I219" t="n">
-        <v>0.1261</v>
+        <v>0.1024</v>
       </c>
       <c r="J219" t="n">
-        <v>4.4135</v>
+        <v>3.584</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>0.8</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6021</v>
+        <v>-0.5642</v>
       </c>
       <c r="J220" t="n">
-        <v>-21.0735</v>
+        <v>-19.747</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.74</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7368</v>
+        <v>-0.7076</v>
       </c>
       <c r="J221" t="n">
-        <v>-25.788</v>
+        <v>-24.766</v>
       </c>
     </row>
     <row r="222">
@@ -13069,10 +13069,10 @@
         <v>1.39</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5314</v>
+        <v>0.4623</v>
       </c>
       <c r="J222" t="n">
-        <v>14.8792</v>
+        <v>12.9444</v>
       </c>
     </row>
     <row r="223">
@@ -13109,10 +13109,10 @@
         <v>1.33</v>
       </c>
       <c r="I223" t="n">
-        <v>0.4646</v>
+        <v>0.3977</v>
       </c>
       <c r="J223" t="n">
-        <v>13.0088</v>
+        <v>11.1356</v>
       </c>
     </row>
     <row r="224">
@@ -13149,10 +13149,10 @@
         <v>1.02</v>
       </c>
       <c r="I224" t="n">
-        <v>0.0493</v>
+        <v>0.0343</v>
       </c>
       <c r="J224" t="n">
-        <v>1.3804</v>
+        <v>0.9604</v>
       </c>
     </row>
     <row r="225">
@@ -13189,10 +13189,10 @@
         <v>1.01</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0268</v>
+        <v>0.0177</v>
       </c>
       <c r="J225" t="n">
-        <v>0.7504</v>
+        <v>0.4956</v>
       </c>
     </row>
     <row r="226">
@@ -13229,10 +13229,10 @@
         <v>0.61</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4341</v>
+        <v>-0.4283</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.1548</v>
+        <v>-11.9924</v>
       </c>
     </row>
     <row r="227">
@@ -13269,10 +13269,10 @@
         <v>1.1</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2231</v>
+        <v>0.2086</v>
       </c>
       <c r="J227" t="n">
-        <v>6.2468</v>
+        <v>5.8408</v>
       </c>
     </row>
     <row r="228">
@@ -13309,10 +13309,10 @@
         <v>0.93</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1015</v>
+        <v>-0.0871</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.842</v>
+        <v>-2.4388</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.88</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.159</v>
+        <v>-0.1415</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.452</v>
+        <v>-3.962</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.78</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2592</v>
+        <v>-0.2401</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.2576</v>
+        <v>-6.7228</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.64</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3893</v>
+        <v>-0.3771</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.9004</v>
+        <v>-10.5588</v>
       </c>
     </row>
     <row r="232">
@@ -13469,10 +13469,10 @@
         <v>0.89</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.1015</v>
+        <v>-0.0806</v>
       </c>
       <c r="J232" t="n">
-        <v>-2.1315</v>
+        <v>-1.6926</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.85</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1495</v>
+        <v>-0.1306</v>
       </c>
       <c r="J233" t="n">
-        <v>-3.1395</v>
+        <v>-2.7426</v>
       </c>
     </row>
     <row r="234">
@@ -13549,10 +13549,10 @@
         <v>0.53</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.4567</v>
+        <v>-0.4509</v>
       </c>
       <c r="J234" t="n">
-        <v>-9.5907</v>
+        <v>-9.4689</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.52</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4655</v>
+        <v>-0.4604</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.775499999999999</v>
+        <v>-9.6684</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.31</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.6501</v>
+        <v>-0.6706</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.6521</v>
+        <v>-14.0826</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.65</v>
       </c>
       <c r="I237" t="n">
-        <v>1.271</v>
+        <v>1.2891</v>
       </c>
       <c r="J237" t="n">
-        <v>26.691</v>
+        <v>27.0711</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.57</v>
       </c>
       <c r="I238" t="n">
-        <v>1.1682</v>
+        <v>1.183</v>
       </c>
       <c r="J238" t="n">
-        <v>24.5322</v>
+        <v>24.843</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.38</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8837</v>
+        <v>0.8723</v>
       </c>
       <c r="J239" t="n">
-        <v>18.5577</v>
+        <v>18.3183</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.21</v>
       </c>
       <c r="I240" t="n">
-        <v>0.5456</v>
+        <v>0.5173</v>
       </c>
       <c r="J240" t="n">
-        <v>11.4576</v>
+        <v>10.8633</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.99</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1198</v>
+        <v>-0.1014</v>
       </c>
       <c r="J241" t="n">
-        <v>-2.5158</v>
+        <v>-2.1294</v>
       </c>
     </row>
     <row r="242">
@@ -13869,10 +13869,10 @@
         <v>0.91</v>
       </c>
       <c r="I242" t="n">
-        <v>-0.1186</v>
+        <v>-0.1039</v>
       </c>
       <c r="J242" t="n">
-        <v>-2.6092</v>
+        <v>-2.2858</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>0.91</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1186</v>
+        <v>-0.1039</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.6092</v>
+        <v>-2.2858</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>0.86</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.175</v>
+        <v>-0.1584</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.85</v>
+        <v>-3.4848</v>
       </c>
     </row>
     <row r="245">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2347</v>
+        <v>-0.217</v>
       </c>
       <c r="J245" t="n">
-        <v>-5.1634</v>
+        <v>-4.774</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4541</v>
+        <v>-0.4478</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.9902</v>
+        <v>-9.851599999999999</v>
       </c>
     </row>
     <row r="247">
@@ -14069,10 +14069,10 @@
         <v>1.63</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2869</v>
+        <v>1.3072</v>
       </c>
       <c r="J247" t="n">
-        <v>28.3118</v>
+        <v>28.7584</v>
       </c>
     </row>
     <row r="248">
@@ -14109,10 +14109,10 @@
         <v>1.38</v>
       </c>
       <c r="I248" t="n">
-        <v>0.9182</v>
+        <v>0.9024</v>
       </c>
       <c r="J248" t="n">
-        <v>20.2004</v>
+        <v>19.8528</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1.24</v>
       </c>
       <c r="I249" t="n">
-        <v>0.634</v>
+        <v>0.6004</v>
       </c>
       <c r="J249" t="n">
-        <v>13.948</v>
+        <v>13.2088</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.95</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2323</v>
+        <v>-0.1954</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.1106</v>
+        <v>-4.2988</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.66</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.9241</v>
+        <v>-0.916</v>
       </c>
       <c r="J251" t="n">
-        <v>-20.3302</v>
+        <v>-20.152</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>0.98</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0377</v>
+        <v>-0.0294</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.0556</v>
+        <v>-0.8232</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>0.96</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0678</v>
+        <v>-0.0556</v>
       </c>
       <c r="J253" t="n">
-        <v>-1.8984</v>
+        <v>-1.5568</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.95</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0813</v>
+        <v>-0.0677</v>
       </c>
       <c r="J254" t="n">
-        <v>-2.2764</v>
+        <v>-1.8956</v>
       </c>
     </row>
     <row r="255">
@@ -14389,10 +14389,10 @@
         <v>0.9</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1407</v>
+        <v>-0.1226</v>
       </c>
       <c r="J255" t="n">
-        <v>-3.9396</v>
+        <v>-3.4328</v>
       </c>
     </row>
     <row r="256">
@@ -14429,10 +14429,10 @@
         <v>0.83</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2152</v>
+        <v>-0.195</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.0256</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>1.36</v>
       </c>
       <c r="I257" t="n">
-        <v>0.9003</v>
+        <v>0.8823</v>
       </c>
       <c r="J257" t="n">
-        <v>25.2084</v>
+        <v>24.7044</v>
       </c>
     </row>
     <row r="258">
@@ -14509,10 +14509,10 @@
         <v>1.1</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3246</v>
+        <v>0.2873</v>
       </c>
       <c r="J258" t="n">
-        <v>9.088800000000001</v>
+        <v>8.0444</v>
       </c>
     </row>
     <row r="259">
@@ -14549,10 +14549,10 @@
         <v>1.06</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2168</v>
+        <v>0.1854</v>
       </c>
       <c r="J259" t="n">
-        <v>6.0704</v>
+        <v>5.1912</v>
       </c>
     </row>
     <row r="260">
@@ -14589,10 +14589,10 @@
         <v>1.03</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1222</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J260" t="n">
-        <v>3.4216</v>
+        <v>2.7888</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.93</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.278</v>
+        <v>-0.2377</v>
       </c>
       <c r="J261" t="n">
-        <v>-7.784</v>
+        <v>-6.6556</v>
       </c>
     </row>
     <row r="262">
@@ -14669,10 +14669,10 @@
         <v>1.48</v>
       </c>
       <c r="I262" t="n">
-        <v>1.0655</v>
+        <v>1.0736</v>
       </c>
       <c r="J262" t="n">
-        <v>26.6375</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.41</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9549</v>
+        <v>0.9458</v>
       </c>
       <c r="J263" t="n">
-        <v>23.8725</v>
+        <v>23.645</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.35</v>
       </c>
       <c r="I264" t="n">
-        <v>0.8417</v>
+        <v>0.8223</v>
       </c>
       <c r="J264" t="n">
-        <v>21.0425</v>
+        <v>20.5575</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.08</v>
       </c>
       <c r="I265" t="n">
-        <v>0.2473</v>
+        <v>0.2171</v>
       </c>
       <c r="J265" t="n">
-        <v>6.1825</v>
+        <v>5.4275</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.96</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.215</v>
+        <v>-0.1815</v>
       </c>
       <c r="J266" t="n">
-        <v>-5.375</v>
+        <v>-4.5375</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.13</v>
       </c>
       <c r="I267" t="n">
-        <v>0.3696</v>
+        <v>0.3225</v>
       </c>
       <c r="J267" t="n">
-        <v>9.24</v>
+        <v>8.0625</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.83</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.205</v>
+        <v>-0.1881</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.125</v>
+        <v>-4.7025</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.7</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3273</v>
+        <v>-0.3113</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.182499999999999</v>
+        <v>-7.7825</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.68</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3457</v>
+        <v>-0.3305</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.6425</v>
+        <v>-8.262499999999999</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.65</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3729</v>
+        <v>-0.3593</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.3225</v>
+        <v>-8.9825</v>
       </c>
     </row>
     <row r="272">
@@ -15069,10 +15069,10 @@
         <v>1.6</v>
       </c>
       <c r="I272" t="n">
-        <v>1.2306</v>
+        <v>1.2467</v>
       </c>
       <c r="J272" t="n">
-        <v>28.3038</v>
+        <v>28.6741</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.5</v>
       </c>
       <c r="I273" t="n">
-        <v>1.0964</v>
+        <v>1.1075</v>
       </c>
       <c r="J273" t="n">
-        <v>25.2172</v>
+        <v>25.4725</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.31</v>
       </c>
       <c r="I274" t="n">
-        <v>0.7662</v>
+        <v>0.7415</v>
       </c>
       <c r="J274" t="n">
-        <v>17.6226</v>
+        <v>17.0545</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.0402</v>
+        <v>-0.0348</v>
       </c>
       <c r="J275" t="n">
-        <v>-0.9246</v>
+        <v>-0.8004</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.78</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.6475</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.5687</v>
+        <v>-14.8925</v>
       </c>
     </row>
     <row r="277">
@@ -15269,10 +15269,10 @@
         <v>1.01</v>
       </c>
       <c r="I277" t="n">
-        <v>0.0851</v>
+        <v>0.066</v>
       </c>
       <c r="J277" t="n">
-        <v>1.9573</v>
+        <v>1.518</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.85</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.1851</v>
+        <v>-0.1684</v>
       </c>
       <c r="J278" t="n">
-        <v>-4.2573</v>
+        <v>-3.8732</v>
       </c>
     </row>
     <row r="279">
@@ -15349,10 +15349,10 @@
         <v>0.84</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1954</v>
+        <v>-0.1785</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.4942</v>
+        <v>-4.1055</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1954</v>
+        <v>-0.1785</v>
       </c>
       <c r="J280" t="n">
-        <v>-4.4942</v>
+        <v>-4.1055</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.48</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5232</v>
+        <v>-0.5256</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.0336</v>
+        <v>-12.0888</v>
       </c>
     </row>
     <row r="282">
@@ -15469,10 +15469,10 @@
         <v>1.79</v>
       </c>
       <c r="I282" t="n">
-        <v>1.4712</v>
+        <v>1.5027</v>
       </c>
       <c r="J282" t="n">
-        <v>32.3664</v>
+        <v>33.0594</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.43</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9893</v>
+        <v>0.9855</v>
       </c>
       <c r="J283" t="n">
-        <v>21.7646</v>
+        <v>21.681</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.02</v>
       </c>
       <c r="I284" t="n">
-        <v>0.058</v>
+        <v>0.0417</v>
       </c>
       <c r="J284" t="n">
-        <v>1.276</v>
+        <v>0.9174</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.02</v>
       </c>
       <c r="I285" t="n">
-        <v>0.058</v>
+        <v>0.0417</v>
       </c>
       <c r="J285" t="n">
-        <v>1.276</v>
+        <v>0.9174</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>1.02</v>
       </c>
       <c r="I286" t="n">
-        <v>0.058</v>
+        <v>0.0417</v>
       </c>
       <c r="J286" t="n">
-        <v>1.276</v>
+        <v>0.9174</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.19</v>
       </c>
       <c r="I287" t="n">
-        <v>0.5213</v>
+        <v>0.4849</v>
       </c>
       <c r="J287" t="n">
-        <v>11.4686</v>
+        <v>10.6678</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>0.8</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.2265</v>
+        <v>-0.2112</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.983</v>
+        <v>-4.6464</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>0.68</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.3375</v>
+        <v>-0.3233</v>
       </c>
       <c r="J289" t="n">
-        <v>-7.425</v>
+        <v>-7.1126</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.55</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4534</v>
+        <v>-0.4466</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.9748</v>
+        <v>-9.825200000000001</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.41</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5753</v>
+        <v>-0.5844</v>
       </c>
       <c r="J291" t="n">
-        <v>-12.6566</v>
+        <v>-12.8568</v>
       </c>
     </row>
     <row r="292">
@@ -15869,10 +15869,10 @@
         <v>1.24</v>
       </c>
       <c r="I292" t="n">
-        <v>0.5033</v>
+        <v>0.4444</v>
       </c>
       <c r="J292" t="n">
-        <v>14.5957</v>
+        <v>12.8876</v>
       </c>
     </row>
     <row r="293">
@@ -15909,10 +15909,10 @@
         <v>1.07</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1932</v>
+        <v>0.1529</v>
       </c>
       <c r="J293" t="n">
-        <v>5.6028</v>
+        <v>4.4341</v>
       </c>
     </row>
     <row r="294">
@@ -15949,10 +15949,10 @@
         <v>1.06</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1717</v>
+        <v>0.1341</v>
       </c>
       <c r="J294" t="n">
-        <v>4.9793</v>
+        <v>3.8889</v>
       </c>
     </row>
     <row r="295">
@@ -15989,10 +15989,10 @@
         <v>0.84</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.211</v>
+        <v>-0.1904</v>
       </c>
       <c r="J295" t="n">
-        <v>-6.119</v>
+        <v>-5.5216</v>
       </c>
     </row>
     <row r="296">
@@ -16029,10 +16029,10 @@
         <v>0.74</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3095</v>
+        <v>-0.2921</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.9755</v>
+        <v>-8.4709</v>
       </c>
     </row>
     <row r="297">
@@ -16069,10 +16069,10 @@
         <v>1.22</v>
       </c>
       <c r="I297" t="n">
-        <v>0.6481</v>
+        <v>0.6128</v>
       </c>
       <c r="J297" t="n">
-        <v>18.7949</v>
+        <v>17.7712</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.18</v>
       </c>
       <c r="I298" t="n">
-        <v>0.5546</v>
+        <v>0.5145</v>
       </c>
       <c r="J298" t="n">
-        <v>16.0834</v>
+        <v>14.9205</v>
       </c>
     </row>
     <row r="299">
@@ -16149,10 +16149,10 @@
         <v>0.95</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1937</v>
+        <v>-0.1617</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.6173</v>
+        <v>-4.6893</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>0.91</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3071</v>
+        <v>-0.2676</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.905900000000001</v>
+        <v>-7.7604</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>0.53</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.1503</v>
+        <v>-1.1657</v>
       </c>
       <c r="J301" t="n">
-        <v>-33.3587</v>
+        <v>-33.8053</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.73</v>
       </c>
       <c r="I302" t="n">
-        <v>1.1775</v>
+        <v>1.1767</v>
       </c>
       <c r="J302" t="n">
-        <v>35.325</v>
+        <v>35.301</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>0.96</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0703</v>
+        <v>-0.0569</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.109</v>
+        <v>-1.707</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>0.89</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.1551</v>
+        <v>-0.1356</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.653</v>
+        <v>-4.068</v>
       </c>
     </row>
     <row r="305">
@@ -16389,10 +16389,10 @@
         <v>0.72</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3259</v>
+        <v>-0.3093</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.776999999999999</v>
+        <v>-9.279</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.52</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5033</v>
+        <v>-0.5049</v>
       </c>
       <c r="J306" t="n">
-        <v>-15.099</v>
+        <v>-15.147</v>
       </c>
     </row>
     <row r="307">
@@ -16469,10 +16469,10 @@
         <v>1.36</v>
       </c>
       <c r="I307" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9402</v>
       </c>
       <c r="J307" t="n">
-        <v>28.413</v>
+        <v>28.206</v>
       </c>
     </row>
     <row r="308">
@@ -16509,10 +16509,10 @@
         <v>1.02</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1047</v>
+        <v>0.08</v>
       </c>
       <c r="J308" t="n">
-        <v>3.141</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="309">
@@ -16549,10 +16549,10 @@
         <v>0.98</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.096</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J309" t="n">
-        <v>-2.88</v>
+        <v>-2.247</v>
       </c>
     </row>
     <row r="310">
@@ -16589,10 +16589,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1315</v>
+        <v>-0.1055</v>
       </c>
       <c r="J310" t="n">
-        <v>-3.945</v>
+        <v>-3.165</v>
       </c>
     </row>
     <row r="311">
@@ -16629,10 +16629,10 @@
         <v>0.52</v>
       </c>
       <c r="I311" t="n">
-        <v>-1.1723</v>
+        <v>-1.1915</v>
       </c>
       <c r="J311" t="n">
-        <v>-35.169</v>
+        <v>-35.745</v>
       </c>
     </row>
     <row r="312">
@@ -16669,10 +16669,10 @@
         <v>1.15</v>
       </c>
       <c r="I312" t="n">
-        <v>0.3873</v>
+        <v>0.3356</v>
       </c>
       <c r="J312" t="n">
-        <v>10.4571</v>
+        <v>9.061199999999999</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.04</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1557</v>
+        <v>0.1215</v>
       </c>
       <c r="J313" t="n">
-        <v>4.2039</v>
+        <v>3.2805</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>0.89</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1469</v>
+        <v>-0.1303</v>
       </c>
       <c r="J314" t="n">
-        <v>-3.9663</v>
+        <v>-3.5181</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>0.63</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.3968</v>
+        <v>-0.3851</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.7136</v>
+        <v>-10.3977</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.55</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4675</v>
+        <v>-0.4631</v>
       </c>
       <c r="J316" t="n">
-        <v>-12.6225</v>
+        <v>-12.5037</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.52</v>
       </c>
       <c r="I317" t="n">
-        <v>1.1493</v>
+        <v>1.1634</v>
       </c>
       <c r="J317" t="n">
-        <v>31.0311</v>
+        <v>31.4118</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.39</v>
       </c>
       <c r="I318" t="n">
-        <v>0.9489</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="J318" t="n">
-        <v>25.6203</v>
+        <v>25.299</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.05</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1818</v>
+        <v>0.1541</v>
       </c>
       <c r="J319" t="n">
-        <v>4.9086</v>
+        <v>4.1607</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.99</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.0805</v>
+        <v>-0.0598</v>
       </c>
       <c r="J320" t="n">
-        <v>-2.1735</v>
+        <v>-1.6146</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.8373</v>
       </c>
       <c r="J321" t="n">
-        <v>-23.0661</v>
+        <v>-22.6071</v>
       </c>
     </row>
     <row r="322">
@@ -17069,10 +17069,10 @@
         <v>1.25</v>
       </c>
       <c r="I322" t="n">
-        <v>0.5767</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="J322" t="n">
-        <v>13.8408</v>
+        <v>12.6648</v>
       </c>
     </row>
     <row r="323">
@@ -17109,10 +17109,10 @@
         <v>1.04</v>
       </c>
       <c r="I323" t="n">
-        <v>0.163</v>
+        <v>0.129</v>
       </c>
       <c r="J323" t="n">
-        <v>3.912</v>
+        <v>3.096</v>
       </c>
     </row>
     <row r="324">
@@ -17149,10 +17149,10 @@
         <v>0.74</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2934</v>
+        <v>-0.2757</v>
       </c>
       <c r="J324" t="n">
-        <v>-7.0416</v>
+        <v>-6.6168</v>
       </c>
     </row>
     <row r="325">
@@ -17189,10 +17189,10 @@
         <v>0.71</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3214</v>
+        <v>-0.3047</v>
       </c>
       <c r="J325" t="n">
-        <v>-7.7136</v>
+        <v>-7.3128</v>
       </c>
     </row>
     <row r="326">
@@ -17229,10 +17229,10 @@
         <v>0.4</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5936</v>
+        <v>-0.6072</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.2464</v>
+        <v>-14.5728</v>
       </c>
     </row>
     <row r="327">
@@ -17269,10 +17269,10 @@
         <v>1.84</v>
       </c>
       <c r="I327" t="n">
-        <v>1.5433</v>
+        <v>1.5825</v>
       </c>
       <c r="J327" t="n">
-        <v>37.0392</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="328">
@@ -17309,10 +17309,10 @@
         <v>1.62</v>
       </c>
       <c r="I328" t="n">
-        <v>1.2603</v>
+        <v>1.278</v>
       </c>
       <c r="J328" t="n">
-        <v>30.2472</v>
+        <v>30.672</v>
       </c>
     </row>
     <row r="329">
@@ -17349,10 +17349,10 @@
         <v>1.13</v>
       </c>
       <c r="I329" t="n">
-        <v>0.3821</v>
+        <v>0.3486</v>
       </c>
       <c r="J329" t="n">
-        <v>9.170400000000001</v>
+        <v>8.366400000000001</v>
       </c>
     </row>
     <row r="330">
@@ -17389,10 +17389,10 @@
         <v>0.79</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.6521</v>
+        <v>-0.6206</v>
       </c>
       <c r="J330" t="n">
-        <v>-15.6504</v>
+        <v>-14.8944</v>
       </c>
     </row>
     <row r="331">
@@ -17429,10 +17429,10 @@
         <v>0.74</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.763</v>
+        <v>-0.74</v>
       </c>
       <c r="J331" t="n">
-        <v>-18.312</v>
+        <v>-17.76</v>
       </c>
     </row>
     <row r="332">
@@ -17469,10 +17469,10 @@
         <v>1.07</v>
       </c>
       <c r="I332" t="n">
-        <v>0.2024</v>
+        <v>0.1606</v>
       </c>
       <c r="J332" t="n">
-        <v>5.8696</v>
+        <v>4.6574</v>
       </c>
     </row>
     <row r="333">
@@ -17509,10 +17509,10 @@
         <v>1.07</v>
       </c>
       <c r="I333" t="n">
-        <v>0.2024</v>
+        <v>0.1606</v>
       </c>
       <c r="J333" t="n">
-        <v>5.8696</v>
+        <v>4.6574</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.89</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.1533</v>
+        <v>-0.1341</v>
       </c>
       <c r="J334" t="n">
-        <v>-4.4457</v>
+        <v>-3.8889</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.85</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.1962</v>
+        <v>-0.176</v>
       </c>
       <c r="J335" t="n">
-        <v>-5.6898</v>
+        <v>-5.104</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.83</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.2169</v>
+        <v>-0.1965</v>
       </c>
       <c r="J336" t="n">
-        <v>-6.2901</v>
+        <v>-5.6985</v>
       </c>
     </row>
     <row r="337">
@@ -17669,10 +17669,10 @@
         <v>1.33</v>
       </c>
       <c r="I337" t="n">
-        <v>0.8665</v>
+        <v>0.8468</v>
       </c>
       <c r="J337" t="n">
-        <v>25.1285</v>
+        <v>24.5572</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.19</v>
       </c>
       <c r="I338" t="n">
-        <v>0.5594</v>
+        <v>0.5189</v>
       </c>
       <c r="J338" t="n">
-        <v>16.2226</v>
+        <v>15.0481</v>
       </c>
     </row>
     <row r="339">
@@ -17749,10 +17749,10 @@
         <v>0.99</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.0609</v>
+        <v>-0.0439</v>
       </c>
       <c r="J339" t="n">
-        <v>-1.7661</v>
+        <v>-1.2731</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.85</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.4722</v>
+        <v>-0.4295</v>
       </c>
       <c r="J340" t="n">
-        <v>-13.6938</v>
+        <v>-12.4555</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.72</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.7693</v>
+        <v>-0.7416</v>
       </c>
       <c r="J341" t="n">
-        <v>-22.3097</v>
+        <v>-21.5064</v>
       </c>
     </row>
     <row r="342">
@@ -17869,10 +17869,10 @@
         <v>1.57</v>
       </c>
       <c r="I342" t="n">
-        <v>1.2171</v>
+        <v>1.2344</v>
       </c>
       <c r="J342" t="n">
-        <v>34.0788</v>
+        <v>34.5632</v>
       </c>
     </row>
     <row r="343">
@@ -17909,10 +17909,10 @@
         <v>1.13</v>
       </c>
       <c r="I343" t="n">
-        <v>0.3947</v>
+        <v>0.3572</v>
       </c>
       <c r="J343" t="n">
-        <v>11.0516</v>
+        <v>10.0016</v>
       </c>
     </row>
     <row r="344">
@@ -17949,10 +17949,10 @@
         <v>1.04</v>
       </c>
       <c r="I344" t="n">
-        <v>0.1495</v>
+        <v>0.1247</v>
       </c>
       <c r="J344" t="n">
-        <v>4.186</v>
+        <v>3.4916</v>
       </c>
     </row>
     <row r="345">
@@ -17989,10 +17989,10 @@
         <v>1.02</v>
       </c>
       <c r="I345" t="n">
-        <v>0.0796</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="J345" t="n">
-        <v>2.2288</v>
+        <v>1.7556</v>
       </c>
     </row>
     <row r="346">
@@ -18029,10 +18029,10 @@
         <v>0.9</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.3678</v>
+        <v>-0.3256</v>
       </c>
       <c r="J346" t="n">
-        <v>-10.2984</v>
+        <v>-9.1168</v>
       </c>
     </row>
     <row r="347">
@@ -18069,10 +18069,10 @@
         <v>1.3</v>
       </c>
       <c r="I347" t="n">
-        <v>0.6486</v>
+        <v>0.5997</v>
       </c>
       <c r="J347" t="n">
-        <v>18.1608</v>
+        <v>16.7916</v>
       </c>
     </row>
     <row r="348">
@@ -18109,10 +18109,10 @@
         <v>0.92</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.1126</v>
+        <v>-0.0977</v>
       </c>
       <c r="J348" t="n">
-        <v>-3.1528</v>
+        <v>-2.7356</v>
       </c>
     </row>
     <row r="349">
@@ -18149,10 +18149,10 @@
         <v>0.85</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1891</v>
+        <v>-0.1708</v>
       </c>
       <c r="J349" t="n">
-        <v>-5.2948</v>
+        <v>-4.7824</v>
       </c>
     </row>
     <row r="350">
@@ -18189,10 +18189,10 @@
         <v>0.72</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3151</v>
+        <v>-0.2979</v>
       </c>
       <c r="J350" t="n">
-        <v>-8.822800000000001</v>
+        <v>-8.341200000000001</v>
       </c>
     </row>
     <row r="351">
@@ -18229,10 +18229,10 @@
         <v>0.49</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5222</v>
       </c>
       <c r="J351" t="n">
-        <v>-14.5516</v>
+        <v>-14.6216</v>
       </c>
     </row>
     <row r="352">
@@ -18269,10 +18269,10 @@
         <v>1.51</v>
       </c>
       <c r="I352" t="n">
-        <v>1.0911</v>
+        <v>1.1036</v>
       </c>
       <c r="J352" t="n">
-        <v>24.0042</v>
+        <v>24.2792</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.5</v>
       </c>
       <c r="I353" t="n">
-        <v>1.0778</v>
+        <v>1.0892</v>
       </c>
       <c r="J353" t="n">
-        <v>23.7116</v>
+        <v>23.9624</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.28</v>
       </c>
       <c r="I354" t="n">
-        <v>0.6939</v>
+        <v>0.6714</v>
       </c>
       <c r="J354" t="n">
-        <v>15.2658</v>
+        <v>14.7708</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>1.28</v>
       </c>
       <c r="I355" t="n">
-        <v>0.6939</v>
+        <v>0.6714</v>
       </c>
       <c r="J355" t="n">
-        <v>15.2658</v>
+        <v>14.7708</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>1.18</v>
       </c>
       <c r="I356" t="n">
-        <v>0.4802</v>
+        <v>0.45</v>
       </c>
       <c r="J356" t="n">
-        <v>10.5644</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="357">
@@ -18469,10 +18469,10 @@
         <v>1.3</v>
       </c>
       <c r="I357" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.8704</v>
       </c>
       <c r="J357" t="n">
-        <v>18.3744</v>
+        <v>19.1488</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>0.65</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.3497</v>
+        <v>-0.3407</v>
       </c>
       <c r="J358" t="n">
-        <v>-7.6934</v>
+        <v>-7.4954</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.43</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.5412</v>
+        <v>-0.544</v>
       </c>
       <c r="J359" t="n">
-        <v>-11.9064</v>
+        <v>-11.968</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.34</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.6207</v>
+        <v>-0.6355</v>
       </c>
       <c r="J360" t="n">
-        <v>-13.6554</v>
+        <v>-13.981</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.26</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.6913</v>
+        <v>-0.7196</v>
       </c>
       <c r="J361" t="n">
-        <v>-15.2086</v>
+        <v>-15.8312</v>
       </c>
     </row>
     <row r="362">
@@ -18669,10 +18669,10 @@
         <v>1.13</v>
       </c>
       <c r="I362" t="n">
-        <v>0.3362</v>
+        <v>0.2845</v>
       </c>
       <c r="J362" t="n">
-        <v>9.7498</v>
+        <v>8.250500000000001</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.05</v>
       </c>
       <c r="I363" t="n">
-        <v>0.1692</v>
+        <v>0.1319</v>
       </c>
       <c r="J363" t="n">
-        <v>4.9068</v>
+        <v>3.8251</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>0.82</v>
       </c>
       <c r="I364" t="n">
-        <v>-0.2223</v>
+        <v>-0.2026</v>
       </c>
       <c r="J364" t="n">
-        <v>-6.4467</v>
+        <v>-5.8754</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.2323</v>
+        <v>-0.2126</v>
       </c>
       <c r="J365" t="n">
-        <v>-6.7367</v>
+        <v>-6.1654</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.65</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.383</v>
+        <v>-0.3703</v>
       </c>
       <c r="J366" t="n">
-        <v>-11.107</v>
+        <v>-10.7387</v>
       </c>
     </row>
     <row r="367">
@@ -18869,10 +18869,10 @@
         <v>1.28</v>
       </c>
       <c r="I367" t="n">
-        <v>0.7372</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="J367" t="n">
-        <v>21.3788</v>
+        <v>20.4769</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.18</v>
       </c>
       <c r="I368" t="n">
-        <v>0.5177</v>
+        <v>0.4778</v>
       </c>
       <c r="J368" t="n">
-        <v>15.0133</v>
+        <v>13.8562</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.13</v>
       </c>
       <c r="I369" t="n">
-        <v>0.3998</v>
+        <v>0.36</v>
       </c>
       <c r="J369" t="n">
-        <v>11.5942</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.96</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.1852</v>
+        <v>-0.1509</v>
       </c>
       <c r="J370" t="n">
-        <v>-5.3708</v>
+        <v>-4.3761</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.9</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3598</v>
+        <v>-0.3172</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.4342</v>
+        <v>-9.1988</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>1.39</v>
       </c>
       <c r="I372" t="n">
-        <v>0.972</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="J372" t="n">
-        <v>33.048</v>
+        <v>32.8168</v>
       </c>
     </row>
     <row r="373">
@@ -19109,10 +19109,10 @@
         <v>1.13</v>
       </c>
       <c r="I373" t="n">
-        <v>0.4065</v>
+        <v>0.365</v>
       </c>
       <c r="J373" t="n">
-        <v>13.821</v>
+        <v>12.41</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.97</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.1448</v>
+        <v>-0.1146</v>
       </c>
       <c r="J374" t="n">
-        <v>-4.9232</v>
+        <v>-3.8964</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.92</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.2982</v>
+        <v>-0.2571</v>
       </c>
       <c r="J375" t="n">
-        <v>-10.1388</v>
+        <v>-8.741400000000001</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.86</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4553</v>
+        <v>-0.4125</v>
       </c>
       <c r="J376" t="n">
-        <v>-15.4802</v>
+        <v>-14.025</v>
       </c>
     </row>
     <row r="377">
@@ -19269,10 +19269,10 @@
         <v>1.21</v>
       </c>
       <c r="I377" t="n">
-        <v>0.4898</v>
+        <v>0.4357</v>
       </c>
       <c r="J377" t="n">
-        <v>16.6532</v>
+        <v>14.8138</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>-0.1259</v>
+        <v>-0.11</v>
       </c>
       <c r="J378" t="n">
-        <v>-4.2806</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.86</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.1798</v>
+        <v>-0.1614</v>
       </c>
       <c r="J379" t="n">
-        <v>-6.1132</v>
+        <v>-5.4876</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.72</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3166</v>
+        <v>-0.2994</v>
       </c>
       <c r="J380" t="n">
-        <v>-10.7644</v>
+        <v>-10.1796</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.65</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.3807</v>
+        <v>-0.3678</v>
       </c>
       <c r="J381" t="n">
-        <v>-12.9438</v>
+        <v>-12.5052</v>
       </c>
     </row>
     <row r="382">
@@ -19469,10 +19469,10 @@
         <v>1.62</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2482</v>
+        <v>1.265</v>
       </c>
       <c r="J382" t="n">
-        <v>29.9568</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.5</v>
       </c>
       <c r="I383" t="n">
-        <v>1.0891</v>
+        <v>1.1</v>
       </c>
       <c r="J383" t="n">
-        <v>26.1384</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.26</v>
       </c>
       <c r="I384" t="n">
-        <v>0.6622</v>
+        <v>0.6351</v>
       </c>
       <c r="J384" t="n">
-        <v>15.8928</v>
+        <v>15.2424</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>1.11</v>
       </c>
       <c r="I385" t="n">
-        <v>0.3234</v>
+        <v>0.2914</v>
       </c>
       <c r="J385" t="n">
-        <v>7.7616</v>
+        <v>6.9936</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.9</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.3932</v>
+        <v>-0.3542</v>
       </c>
       <c r="J386" t="n">
-        <v>-9.4368</v>
+        <v>-8.5008</v>
       </c>
     </row>
     <row r="387">
@@ -19669,10 +19669,10 @@
         <v>0.86</v>
       </c>
       <c r="I387" t="n">
-        <v>-0.1579</v>
+        <v>-0.142</v>
       </c>
       <c r="J387" t="n">
-        <v>-3.7896</v>
+        <v>-3.408</v>
       </c>
     </row>
     <row r="388">
@@ -19709,10 +19709,10 @@
         <v>0.75</v>
       </c>
       <c r="I388" t="n">
-        <v>-0.272</v>
+        <v>-0.2578</v>
       </c>
       <c r="J388" t="n">
-        <v>-6.528</v>
+        <v>-6.1872</v>
       </c>
     </row>
     <row r="389">
@@ -19749,10 +19749,10 @@
         <v>0.71</v>
       </c>
       <c r="I389" t="n">
-        <v>-0.3089</v>
+        <v>-0.2951</v>
       </c>
       <c r="J389" t="n">
-        <v>-7.4136</v>
+        <v>-7.0824</v>
       </c>
     </row>
     <row r="390">
@@ -19789,10 +19789,10 @@
         <v>0.68</v>
       </c>
       <c r="I390" t="n">
-        <v>-0.3348</v>
+        <v>-0.3214</v>
       </c>
       <c r="J390" t="n">
-        <v>-8.0352</v>
+        <v>-7.7136</v>
       </c>
     </row>
     <row r="391">
@@ -19829,10 +19829,10 @@
         <v>0.5</v>
       </c>
       <c r="I391" t="n">
-        <v>-0.494</v>
+        <v>-0.4916</v>
       </c>
       <c r="J391" t="n">
-        <v>-11.856</v>
+        <v>-11.7984</v>
       </c>
     </row>
     <row r="392">
@@ -19869,10 +19869,10 @@
         <v>1.6</v>
       </c>
       <c r="I392" t="n">
-        <v>1.2421</v>
+        <v>1.2594</v>
       </c>
       <c r="J392" t="n">
-        <v>27.3262</v>
+        <v>27.7068</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.2</v>
       </c>
       <c r="I393" t="n">
-        <v>0.546</v>
+        <v>0.5114</v>
       </c>
       <c r="J393" t="n">
-        <v>12.012</v>
+        <v>11.2508</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1.15</v>
       </c>
       <c r="I394" t="n">
-        <v>0.435</v>
+        <v>0.3999</v>
       </c>
       <c r="J394" t="n">
-        <v>9.57</v>
+        <v>8.797800000000001</v>
       </c>
     </row>
     <row r="395">
@@ -19989,10 +19989,10 @@
         <v>1.09</v>
       </c>
       <c r="I395" t="n">
-        <v>0.2855</v>
+        <v>0.2532</v>
       </c>
       <c r="J395" t="n">
-        <v>6.281</v>
+        <v>5.5704</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.91</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3514</v>
+        <v>-0.3104</v>
       </c>
       <c r="J396" t="n">
-        <v>-7.7308</v>
+        <v>-6.8288</v>
       </c>
     </row>
     <row r="397">
@@ -20069,10 +20069,10 @@
         <v>1.18</v>
       </c>
       <c r="I397" t="n">
-        <v>0.4661</v>
+        <v>0.4183</v>
       </c>
       <c r="J397" t="n">
-        <v>10.2542</v>
+        <v>9.2026</v>
       </c>
     </row>
     <row r="398">
@@ -20109,10 +20109,10 @@
         <v>0.97</v>
       </c>
       <c r="I398" t="n">
-        <v>-0.0362</v>
+        <v>-0.0268</v>
       </c>
       <c r="J398" t="n">
-        <v>-0.7964</v>
+        <v>-0.5896</v>
       </c>
     </row>
     <row r="399">
@@ -20149,10 +20149,10 @@
         <v>0.79</v>
       </c>
       <c r="I399" t="n">
-        <v>-0.2433</v>
+        <v>-0.2259</v>
       </c>
       <c r="J399" t="n">
-        <v>-5.3526</v>
+        <v>-4.9698</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>0.58</v>
       </c>
       <c r="I400" t="n">
-        <v>-0.4352</v>
+        <v>-0.4268</v>
       </c>
       <c r="J400" t="n">
-        <v>-9.574400000000001</v>
+        <v>-9.3896</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>0.46</v>
       </c>
       <c r="I401" t="n">
-        <v>-0.5396</v>
+        <v>-0.5442</v>
       </c>
       <c r="J401" t="n">
-        <v>-11.8712</v>
+        <v>-11.9724</v>
       </c>
     </row>
     <row r="402">
@@ -20269,10 +20269,10 @@
         <v>1.86</v>
       </c>
       <c r="I402" t="n">
-        <v>1.6105</v>
+        <v>1.665</v>
       </c>
       <c r="J402" t="n">
-        <v>43.4835</v>
+        <v>44.955</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.11</v>
       </c>
       <c r="I403" t="n">
-        <v>0.3486</v>
+        <v>0.311</v>
       </c>
       <c r="J403" t="n">
-        <v>9.4122</v>
+        <v>8.397</v>
       </c>
     </row>
     <row r="404">
@@ -20349,10 +20349,10 @@
         <v>1.03</v>
       </c>
       <c r="I404" t="n">
-        <v>0.1205</v>
+        <v>0.0983</v>
       </c>
       <c r="J404" t="n">
-        <v>3.2535</v>
+        <v>2.6541</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.78</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.6543</v>
+        <v>-0.62</v>
       </c>
       <c r="J405" t="n">
-        <v>-17.6661</v>
+        <v>-16.74</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.75</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.7212</v>
+        <v>-0.6916</v>
       </c>
       <c r="J406" t="n">
-        <v>-19.4724</v>
+        <v>-18.6732</v>
       </c>
     </row>
     <row r="407">
@@ -20469,10 +20469,10 @@
         <v>1.08</v>
       </c>
       <c r="I407" t="n">
-        <v>0.2468</v>
+        <v>0.2026</v>
       </c>
       <c r="J407" t="n">
-        <v>6.6636</v>
+        <v>5.4702</v>
       </c>
     </row>
     <row r="408">
@@ -20509,10 +20509,10 @@
         <v>0.88</v>
       </c>
       <c r="I408" t="n">
-        <v>-0.158</v>
+        <v>-0.1409</v>
       </c>
       <c r="J408" t="n">
-        <v>-4.266</v>
+        <v>-3.8043</v>
       </c>
     </row>
     <row r="409">
@@ -20549,10 +20549,10 @@
         <v>0.83</v>
       </c>
       <c r="I409" t="n">
-        <v>-0.209</v>
+        <v>-0.1902</v>
       </c>
       <c r="J409" t="n">
-        <v>-5.643</v>
+        <v>-5.1354</v>
       </c>
     </row>
     <row r="410">
@@ -20589,10 +20589,10 @@
         <v>0.8</v>
       </c>
       <c r="I410" t="n">
-        <v>-0.2386</v>
+        <v>-0.2196</v>
       </c>
       <c r="J410" t="n">
-        <v>-6.4422</v>
+        <v>-5.9292</v>
       </c>
     </row>
     <row r="411">
@@ -20629,10 +20629,10 @@
         <v>0.68</v>
       </c>
       <c r="I411" t="n">
-        <v>-0.3518</v>
+        <v>-0.3367</v>
       </c>
       <c r="J411" t="n">
-        <v>-9.4986</v>
+        <v>-9.0909</v>
       </c>
     </row>
     <row r="412">
@@ -20669,10 +20669,10 @@
         <v>1.59</v>
       </c>
       <c r="I412" t="n">
-        <v>1.2528</v>
+        <v>1.2733</v>
       </c>
       <c r="J412" t="n">
-        <v>32.5728</v>
+        <v>33.1058</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.23</v>
       </c>
       <c r="I413" t="n">
-        <v>0.6263</v>
+        <v>0.5898</v>
       </c>
       <c r="J413" t="n">
-        <v>16.2838</v>
+        <v>15.3348</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.11</v>
       </c>
       <c r="I414" t="n">
-        <v>0.3488</v>
+        <v>0.311</v>
       </c>
       <c r="J414" t="n">
-        <v>9.0688</v>
+        <v>8.086</v>
       </c>
     </row>
     <row r="415">
@@ -20789,10 +20789,10 @@
         <v>0.89</v>
       </c>
       <c r="I415" t="n">
-        <v>-0.3889</v>
+        <v>-0.3461</v>
       </c>
       <c r="J415" t="n">
-        <v>-10.1114</v>
+        <v>-8.9986</v>
       </c>
     </row>
     <row r="416">
@@ -20829,10 +20829,10 @@
         <v>0.7</v>
       </c>
       <c r="I416" t="n">
-        <v>-0.829</v>
+        <v>-0.8088</v>
       </c>
       <c r="J416" t="n">
-        <v>-21.554</v>
+        <v>-21.0288</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.11</v>
       </c>
       <c r="I417" t="n">
-        <v>0.3089</v>
+        <v>0.2604</v>
       </c>
       <c r="J417" t="n">
-        <v>8.0314</v>
+        <v>6.7704</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.04</v>
       </c>
       <c r="I418" t="n">
-        <v>0.1551</v>
+        <v>0.1209</v>
       </c>
       <c r="J418" t="n">
-        <v>4.0326</v>
+        <v>3.1434</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.8</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.2386</v>
+        <v>-0.2196</v>
       </c>
       <c r="J419" t="n">
-        <v>-6.2036</v>
+        <v>-5.7096</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.68</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3518</v>
+        <v>-0.3367</v>
       </c>
       <c r="J420" t="n">
-        <v>-9.146800000000001</v>
+        <v>-8.754200000000001</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.64</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3881</v>
+        <v>-0.3756</v>
       </c>
       <c r="J421" t="n">
-        <v>-10.0906</v>
+        <v>-9.765599999999999</v>
       </c>
     </row>
   </sheetData>
